--- a/4-Indian-Brook-House-Tracker.xlsx
+++ b/4-Indian-Brook-House-Tracker.xlsx
@@ -671,7 +671,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2nd Floor Flooring</t>
@@ -679,7 +679,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>First project. Compare the 3 Floor &amp; Decor plank options, pick one in 'Selected option' (yellow cell), and the budget fills in automatically. Log payments in the cost log at the bottom — actuals and the Basis Tracker update themselves.</t>
+          <t>First project. Compare the 3 Floor &amp; Decor plank options (incl. underlayment, stair nose &amp; risers, 5% contractor discount, est. tax, and Footprints labor), pick one in 'Selected option' (yellow cell), and the budget fills in automatically. Log payments in the cost log at the bottom — actuals and the Basis Tracker update themselves.</t>
         </is>
       </c>
     </row>
@@ -691,11 +691,11 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>For the next project: right-click the tab &gt; Duplicate, rename it, fill in your options/quotes, then add a row in the Basis Tracker improvements table pointing at the new tab's cell C37 (its Actual total).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
+          <t>For the next project: right-click the tab &gt; Duplicate, rename it, fill in your options/quotes, then add a row in the Basis Tracker improvements table pointing at the new tab's cell C43 (its Actual total).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Sources</t>
@@ -703,7 +703,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Labor: Footprints Floors of Central MA proposal #25584 (6/30/2026) — $9,057.60, materials excluded. Materials: Floor &amp; Decor Waltham cart — Sapelo Shore / Big Sur / Gunstock Oak + Sentinel underlayment.</t>
+          <t>Labor: Footprints Floors of Central MA proposal #25584 (6/30/2026) — $9,057.60, materials excluded. Materials: Floor &amp; Decor Waltham cart (7/2026) — Sapelo Shore / Big Sur / Gunstock Oak + Sentinel underlayment, plus 7 stair noses @ $29.99 and 13 risers @ $20; 5% contractor discount on materials.</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="E21" s="14">
-        <f>'2nd Floor Flooring'!C37</f>
+        <f>'2nd Floor Flooring'!C43</f>
         <v/>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor, Waltham MA (cart priced 7/2026)</t>
+          <t>Floor &amp; Decor, Waltham MA (cart re-priced 7/2026); 5% materials discount through flooring contractor</t>
         </is>
       </c>
     </row>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="B16" s="29" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C16" s="29" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E16" s="12" t="n"/>
     </row>
@@ -1434,24 +1434,24 @@
     <row r="19">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>Est. sales tax (6.25% MA, materials)</t>
+          <t>Stair nose trim</t>
         </is>
       </c>
       <c r="B19" s="28">
-        <f>(B17+B18)*0.0625</f>
+        <f>7*29.99</f>
         <v/>
       </c>
       <c r="C19" s="28">
-        <f>(C17+C18)*0.0625</f>
+        <f>7*29.99</f>
         <v/>
       </c>
       <c r="D19" s="28">
-        <f>(D17+D18)*0.0625</f>
+        <f>7*29.99</f>
         <v/>
       </c>
       <c r="E19" s="27" t="inlineStr">
         <is>
-          <t>Estimate on materials only; replace with the actual receipt tax when purchased.</t>
+          <t>7 stair noses x $29.99.</t>
         </is>
       </c>
       <c r="F19" s="10" t="n"/>
@@ -1460,21 +1460,24 @@
     <row r="20">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>Labor — demo &amp; disposal</t>
-        </is>
-      </c>
-      <c r="B20" s="28" t="n">
-        <v>2642.3</v>
-      </c>
-      <c r="C20" s="28" t="n">
-        <v>2642.3</v>
-      </c>
-      <c r="D20" s="28" t="n">
-        <v>2642.3</v>
+          <t>Stair risers</t>
+        </is>
+      </c>
+      <c r="B20" s="28">
+        <f>13*20</f>
+        <v/>
+      </c>
+      <c r="C20" s="28">
+        <f>13*20</f>
+        <v/>
+      </c>
+      <c r="D20" s="28">
+        <f>13*20</f>
+        <v/>
       </c>
       <c r="E20" s="27" t="inlineStr">
         <is>
-          <t>Footprints: demo carpet, remove &amp; return baseboards, trash removal.</t>
+          <t>13 risers x $20.00.</t>
         </is>
       </c>
       <c r="F20" s="10" t="n"/>
@@ -1483,21 +1486,24 @@
     <row r="21">
       <c r="A21" s="25" t="inlineStr">
         <is>
-          <t>Labor — install</t>
-        </is>
-      </c>
-      <c r="B21" s="28" t="n">
-        <v>4535.3</v>
-      </c>
-      <c r="C21" s="28" t="n">
-        <v>4535.3</v>
-      </c>
-      <c r="D21" s="28" t="n">
-        <v>4535.3</v>
+          <t>Contractor discount on materials (5%)</t>
+        </is>
+      </c>
+      <c r="B21" s="28">
+        <f>-0.05*SUM(B17:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="28">
+        <f>-0.05*SUM(C17:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="28">
+        <f>-0.05*SUM(D17:D20)</f>
+        <v/>
       </c>
       <c r="E21" s="27" t="inlineStr">
         <is>
-          <t>Footprints: install click-lock floating floor.</t>
+          <t>5% off all materials through the flooring contractor.</t>
         </is>
       </c>
       <c r="F21" s="10" t="n"/>
@@ -1506,170 +1512,173 @@
     <row r="22">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>Labor — stairs (treads &amp; risers)</t>
-        </is>
-      </c>
-      <c r="B22" s="28" t="n">
-        <v>1880</v>
-      </c>
-      <c r="C22" s="28" t="n">
-        <v>1880</v>
-      </c>
-      <c r="D22" s="28" t="n">
-        <v>1880</v>
-      </c>
-      <c r="E22" s="27" t="inlineStr">
-        <is>
-          <t>Footprints: treads (open 1 side) + risers.</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="11" t="n"/>
+          <t>Est. sales tax (6.25% MA, materials)</t>
+        </is>
+      </c>
+      <c r="B22" s="28">
+        <f>SUM(B17:B21)*0.0625</f>
+        <v/>
+      </c>
+      <c r="C22" s="28">
+        <f>SUM(C17:C21)*0.0625</f>
+        <v/>
+      </c>
+      <c r="D22" s="28">
+        <f>SUM(D17:D21)*0.0625</f>
+        <v/>
+      </c>
+      <c r="E22" s="12" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="inlineStr">
-        <is>
-          <t>TOTAL ESTIMATED</t>
-        </is>
-      </c>
-      <c r="B23" s="31">
-        <f>SUM(B17:B22)</f>
-        <v/>
-      </c>
-      <c r="C23" s="31">
-        <f>SUM(C17:C22)</f>
-        <v/>
-      </c>
-      <c r="D23" s="31">
-        <f>SUM(D17:D22)</f>
-        <v/>
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>Labor — demo &amp; disposal</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="n">
+        <v>2642.3</v>
+      </c>
+      <c r="C23" s="28" t="n">
+        <v>2642.3</v>
+      </c>
+      <c r="D23" s="28" t="n">
+        <v>2642.3</v>
       </c>
       <c r="E23" s="27" t="inlineStr">
         <is>
-          <t>Labor $9,057.60 is identical across options, so the spread comes entirely from the plank you pick.</t>
+          <t>Footprints: demo carpet, remove &amp; return baseboards, trash removal.</t>
         </is>
       </c>
       <c r="F23" s="10" t="n"/>
       <c r="G23" s="11" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>Labor — install</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="n">
+        <v>4535.3</v>
+      </c>
+      <c r="C24" s="28" t="n">
+        <v>4535.3</v>
+      </c>
+      <c r="D24" s="28" t="n">
+        <v>4535.3</v>
+      </c>
+      <c r="E24" s="27" t="inlineStr">
+        <is>
+          <t>Footprints: install click-lock floating floor.</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="11" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Labor — stairs (treads &amp; risers)</t>
+        </is>
+      </c>
+      <c r="B25" s="28" t="n">
+        <v>1880</v>
+      </c>
+      <c r="C25" s="28" t="n">
+        <v>1880</v>
+      </c>
+      <c r="D25" s="28" t="n">
+        <v>1880</v>
+      </c>
+      <c r="E25" s="12" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>TOTAL ESTIMATED</t>
+        </is>
+      </c>
+      <c r="B26" s="31">
+        <f>SUM(B17:B25)</f>
+        <v/>
+      </c>
+      <c r="C26" s="31">
+        <f>SUM(C17:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="31">
+        <f>SUM(D17:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="27" t="inlineStr">
+        <is>
+          <t>Labor $9,057.60 is identical across options, so the spread comes entirely from the plank you pick.</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="11" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>Premium vs. cheapest option</t>
         </is>
       </c>
-      <c r="B24" s="33">
-        <f>B23-MIN($B$23:$D$23)</f>
-        <v/>
-      </c>
-      <c r="C24" s="33">
-        <f>C23-MIN($B$23:$D$23)</f>
-        <v/>
-      </c>
-      <c r="D24" s="33">
-        <f>D23-MIN($B$23:$D$23)</f>
-        <v/>
-      </c>
-      <c r="E24" s="12" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="B27" s="33">
+        <f>B26-MIN($B$26:$D$26)</f>
+        <v/>
+      </c>
+      <c r="C27" s="33">
+        <f>C26-MIN($B$26:$D$26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="33">
+        <f>D26-MIN($B$26:$D$26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="12" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>STEP 2 — BUDGET vs. ACTUAL  (budget auto-fills from the selected option)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Actual (from cost log)</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Flooring materials</t>
-        </is>
-      </c>
-      <c r="B28" s="14">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$23,5,FALSE))</f>
-        <v/>
-      </c>
-      <c r="C28" s="14">
-        <f>SUMIF($D$42:$D$140,$A28,$E$42:$E$140)</f>
-        <v/>
-      </c>
-      <c r="D28" s="14">
-        <f>IF(B28="","",B28-C28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Underlayment &amp; supplies</t>
-        </is>
-      </c>
-      <c r="B29" s="14">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$23,6,FALSE))</f>
-        <v/>
-      </c>
-      <c r="C29" s="14">
-        <f>SUMIF($D$42:$D$140,$A29,$E$42:$E$140)</f>
-        <v/>
-      </c>
-      <c r="D29" s="14">
-        <f>IF(B29="","",B29-C29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Sales tax</t>
-        </is>
-      </c>
-      <c r="B30" s="14">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$23,7,FALSE))</f>
-        <v/>
-      </c>
-      <c r="C30" s="14">
-        <f>SUMIF($D$42:$D$140,$A30,$E$42:$E$140)</f>
-        <v/>
-      </c>
-      <c r="D30" s="14">
-        <f>IF(B30="","",B30-C30)</f>
-        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Labor — demo &amp; disposal</t>
+          <t>Flooring materials</t>
         </is>
       </c>
       <c r="B31" s="14">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$23,8,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,5,FALSE))</f>
         <v/>
       </c>
       <c r="C31" s="14">
-        <f>SUMIF($D$42:$D$140,$A31,$E$42:$E$140)</f>
+        <f>SUMIF($D$48:$D$147,$A31,$E$48:$E$147)</f>
         <v/>
       </c>
       <c r="D31" s="14">
@@ -1680,15 +1689,15 @@
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Labor — install</t>
+          <t>Underlayment &amp; supplies</t>
         </is>
       </c>
       <c r="B32" s="14">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$23,9,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,6,FALSE))</f>
         <v/>
       </c>
       <c r="C32" s="14">
-        <f>SUMIF($D$42:$D$140,$A32,$E$42:$E$140)</f>
+        <f>SUMIF($D$48:$D$147,$A32,$E$48:$E$147)</f>
         <v/>
       </c>
       <c r="D32" s="14">
@@ -1699,15 +1708,15 @@
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Labor — stairs</t>
+          <t>Stair nose trim</t>
         </is>
       </c>
       <c r="B33" s="14">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$23,10,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,7,FALSE))</f>
         <v/>
       </c>
       <c r="C33" s="14">
-        <f>SUMIF($D$42:$D$140,$A33,$E$42:$E$140)</f>
+        <f>SUMIF($D$48:$D$147,$A33,$E$48:$E$147)</f>
         <v/>
       </c>
       <c r="D33" s="14">
@@ -1718,12 +1727,15 @@
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Permits &amp; fees</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="n"/>
+          <t>Stair risers</t>
+        </is>
+      </c>
+      <c r="B34" s="14">
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,8,FALSE))</f>
+        <v/>
+      </c>
       <c r="C34" s="14">
-        <f>SUMIF($D$42:$D$140,$A34,$E$42:$E$140)</f>
+        <f>SUMIF($D$48:$D$147,$A34,$E$48:$E$147)</f>
         <v/>
       </c>
       <c r="D34" s="14">
@@ -1734,12 +1746,15 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="n"/>
+          <t>Contractor discount</t>
+        </is>
+      </c>
+      <c r="B35" s="14">
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,9,FALSE))</f>
+        <v/>
+      </c>
       <c r="C35" s="14">
-        <f>SUMIF($D$42:$D$140,$A35,$E$42:$E$140)</f>
+        <f>SUMIF($D$48:$D$147,$A35,$E$48:$E$147)</f>
         <v/>
       </c>
       <c r="D35" s="14">
@@ -1750,142 +1765,196 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
+          <t>Sales tax</t>
+        </is>
+      </c>
+      <c r="B36" s="14">
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,10,FALSE))</f>
+        <v/>
+      </c>
+      <c r="C36" s="14">
+        <f>SUMIF($D$48:$D$147,$A36,$E$48:$E$147)</f>
+        <v/>
+      </c>
+      <c r="D36" s="14">
+        <f>IF(B36="","",B36-C36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Labor — demo &amp; disposal</t>
+        </is>
+      </c>
+      <c r="B37" s="14">
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,11,FALSE))</f>
+        <v/>
+      </c>
+      <c r="C37" s="14">
+        <f>SUMIF($D$48:$D$147,$A37,$E$48:$E$147)</f>
+        <v/>
+      </c>
+      <c r="D37" s="14">
+        <f>IF(B37="","",B37-C37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Labor — install</t>
+        </is>
+      </c>
+      <c r="B38" s="14">
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,12,FALSE))</f>
+        <v/>
+      </c>
+      <c r="C38" s="14">
+        <f>SUMIF($D$48:$D$147,$A38,$E$48:$E$147)</f>
+        <v/>
+      </c>
+      <c r="D38" s="14">
+        <f>IF(B38="","",B38-C38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Labor — stairs</t>
+        </is>
+      </c>
+      <c r="B39" s="14">
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,13,FALSE))</f>
+        <v/>
+      </c>
+      <c r="C39" s="14">
+        <f>SUMIF($D$48:$D$147,$A39,$E$48:$E$147)</f>
+        <v/>
+      </c>
+      <c r="D39" s="14">
+        <f>IF(B39="","",B39-C39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Permits &amp; fees</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="14">
+        <f>SUMIF($D$48:$D$147,$A40,$E$48:$E$147)</f>
+        <v/>
+      </c>
+      <c r="D40" s="14">
+        <f>IF(B40="","",B40-C40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="14">
+        <f>SUMIF($D$48:$D$147,$A41,$E$48:$E$147)</f>
+        <v/>
+      </c>
+      <c r="D41" s="14">
+        <f>IF(B41="","",B41-C41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
           <t>Contingency</t>
         </is>
       </c>
-      <c r="B36" s="14">
-        <f>SUM(B28:B35)*$B$9</f>
-        <v/>
-      </c>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="14">
-        <f>B36-C36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="30" t="inlineStr">
+      <c r="B42" s="14">
+        <f>SUM(B31:B41)*$B$9</f>
+        <v/>
+      </c>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14">
+        <f>B42-C42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="30" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B37" s="34">
-        <f>SUM(B28:B36)</f>
-        <v/>
-      </c>
-      <c r="C37" s="34">
-        <f>SUM(C28:C36)</f>
-        <v/>
-      </c>
-      <c r="D37" s="34">
-        <f>B37-C37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>The Actual total (C37) is what feeds the Basis Tracker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="B43" s="34">
+        <f>SUM(B31:B42)</f>
+        <v/>
+      </c>
+      <c r="C43" s="34">
+        <f>SUM(C31:C42)</f>
+        <v/>
+      </c>
+      <c r="D43" s="34">
+        <f>B43-C43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>The Actual total (C43) is what feeds the Basis Tracker. Log receipts net of discount, or log the discount as a negative amount under 'Contractor discount'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>STEP 3 — COST LOG  (record every payment; Actuals above update automatically)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D47" s="9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F47" s="9" t="inlineStr">
         <is>
           <t>Payment method</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="n"/>
-      <c r="B42" s="12" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="12" t="n"/>
-      <c r="E42" s="14" t="n"/>
-      <c r="F42" s="12" t="n"/>
-      <c r="G42" s="12" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="n"/>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="12" t="n"/>
-      <c r="E43" s="14" t="n"/>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="12" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="n"/>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="14" t="n"/>
-      <c r="F44" s="12" t="n"/>
-      <c r="G44" s="12" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="n"/>
-      <c r="B45" s="12" t="n"/>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="12" t="n"/>
-      <c r="E45" s="14" t="n"/>
-      <c r="F45" s="12" t="n"/>
-      <c r="G45" s="12" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="n"/>
-      <c r="B46" s="12" t="n"/>
-      <c r="C46" s="12" t="n"/>
-      <c r="D46" s="12" t="n"/>
-      <c r="E46" s="14" t="n"/>
-      <c r="F46" s="12" t="n"/>
-      <c r="G46" s="12" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="n"/>
-      <c r="B47" s="12" t="n"/>
-      <c r="C47" s="12" t="n"/>
-      <c r="D47" s="12" t="n"/>
-      <c r="E47" s="14" t="n"/>
-      <c r="F47" s="12" t="n"/>
-      <c r="G47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n"/>
@@ -2724,25 +2793,89 @@
       <c r="F140" s="12" t="n"/>
       <c r="G140" s="12" t="n"/>
     </row>
+    <row r="141">
+      <c r="A141" s="8" t="n"/>
+      <c r="B141" s="12" t="n"/>
+      <c r="C141" s="12" t="n"/>
+      <c r="D141" s="12" t="n"/>
+      <c r="E141" s="14" t="n"/>
+      <c r="F141" s="12" t="n"/>
+      <c r="G141" s="12" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="8" t="n"/>
+      <c r="B142" s="12" t="n"/>
+      <c r="C142" s="12" t="n"/>
+      <c r="D142" s="12" t="n"/>
+      <c r="E142" s="14" t="n"/>
+      <c r="F142" s="12" t="n"/>
+      <c r="G142" s="12" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="n"/>
+      <c r="B143" s="12" t="n"/>
+      <c r="C143" s="12" t="n"/>
+      <c r="D143" s="12" t="n"/>
+      <c r="E143" s="14" t="n"/>
+      <c r="F143" s="12" t="n"/>
+      <c r="G143" s="12" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="8" t="n"/>
+      <c r="B144" s="12" t="n"/>
+      <c r="C144" s="12" t="n"/>
+      <c r="D144" s="12" t="n"/>
+      <c r="E144" s="14" t="n"/>
+      <c r="F144" s="12" t="n"/>
+      <c r="G144" s="12" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="n"/>
+      <c r="B145" s="12" t="n"/>
+      <c r="C145" s="12" t="n"/>
+      <c r="D145" s="12" t="n"/>
+      <c r="E145" s="14" t="n"/>
+      <c r="F145" s="12" t="n"/>
+      <c r="G145" s="12" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="8" t="n"/>
+      <c r="B146" s="12" t="n"/>
+      <c r="C146" s="12" t="n"/>
+      <c r="D146" s="12" t="n"/>
+      <c r="E146" s="14" t="n"/>
+      <c r="F146" s="12" t="n"/>
+      <c r="G146" s="12" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="8" t="n"/>
+      <c r="B147" s="12" t="n"/>
+      <c r="C147" s="12" t="n"/>
+      <c r="D147" s="12" t="n"/>
+      <c r="E147" s="14" t="n"/>
+      <c r="F147" s="12" t="n"/>
+      <c r="G147" s="12" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="E26:G26"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="E22:G22"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E21:G21"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="E24:G24"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="E23:G23"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A26:G26"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E20:G20"/>
   </mergeCells>
@@ -2753,8 +2886,8 @@
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=$B$13:$D$13</formula1>
     </dataValidation>
-    <dataValidation sqref="D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 D52 D53 D54 D55 D56 D57 D58 D59 D60 D61 D62 D63 D64 D65 D66 D67 D68 D69 D70 D71 D72 D73 D74 D75 D76 D77 D78 D79 D80 D81 D82 D83 D84 D85 D86 D87 D88 D89 D90 D91 D92 D93 D94 D95 D96 D97 D98 D99 D100 D101 D102 D103 D104 D105 D106 D107 D108 D109 D110 D111 D112 D113 D114 D115 D116 D117 D118 D119 D120 D121 D122 D123 D124 D125 D126 D127 D128 D129 D130 D131 D132 D133 D134 D135 D136 D137 D138 D139 D140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=$A$28:$A$35</formula1>
+    <dataValidation sqref="D48 D49 D50 D51 D52 D53 D54 D55 D56 D57 D58 D59 D60 D61 D62 D63 D64 D65 D66 D67 D68 D69 D70 D71 D72 D73 D74 D75 D76 D77 D78 D79 D80 D81 D82 D83 D84 D85 D86 D87 D88 D89 D90 D91 D92 D93 D94 D95 D96 D97 D98 D99 D100 D101 D102 D103 D104 D105 D106 D107 D108 D109 D110 D111 D112 D113 D114 D115 D116 D117 D118 D119 D120 D121 D122 D123 D124 D125 D126 D127 D128 D129 D130 D131 D132 D133 D134 D135 D136 D137 D138 D139 D140 D141 D142 D143 D144 D145 D146 D147" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=$A$31:$A$41</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2768,7 +2901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2790,7 +2923,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How to use: right-click the tab &gt; Duplicate. Rename it, fill in options &amp; quotes, then add one row for it in the Basis Tracker improvements table pointing at the new tab's Actual total (cell C37).</t>
+          <t>How to use: right-click the tab &gt; Duplicate. Rename it, fill in options &amp; quotes, then add one row for it in the Basis Tracker improvements table pointing at the new tab's Actual total (cell C43).</t>
         </is>
       </c>
     </row>
@@ -2956,27 +3089,24 @@
     <row r="19">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>Est. sales tax (6.25% MA, materials)</t>
-        </is>
-      </c>
-      <c r="B19" s="28">
-        <f>(B17+B18)*0.0625</f>
-        <v/>
-      </c>
-      <c r="C19" s="28">
-        <f>(C17+C18)*0.0625</f>
-        <v/>
-      </c>
-      <c r="D19" s="28">
-        <f>(D17+D18)*0.0625</f>
-        <v/>
-      </c>
-      <c r="E19" s="12" t="n"/>
+          <t>Stair nose trim</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr"/>
+      <c r="C19" s="28" t="inlineStr"/>
+      <c r="D19" s="28" t="inlineStr"/>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>Rename these two rows for whatever extra materials the project needs.</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>Labor — demo &amp; disposal</t>
+          <t>Stair risers</t>
         </is>
       </c>
       <c r="B20" s="28" t="inlineStr"/>
@@ -2987,169 +3117,163 @@
     <row r="21">
       <c r="A21" s="25" t="inlineStr">
         <is>
-          <t>Labor — install</t>
-        </is>
-      </c>
-      <c r="B21" s="28" t="inlineStr"/>
-      <c r="C21" s="28" t="inlineStr"/>
-      <c r="D21" s="28" t="inlineStr"/>
+          <t>Contractor discount on materials (0%)</t>
+        </is>
+      </c>
+      <c r="B21" s="28">
+        <f>-0.0*SUM(B17:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="28">
+        <f>-0.0*SUM(C17:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="28">
+        <f>-0.0*SUM(D17:D20)</f>
+        <v/>
+      </c>
       <c r="E21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="25" t="inlineStr">
         <is>
+          <t>Est. sales tax (6.25% MA, materials)</t>
+        </is>
+      </c>
+      <c r="B22" s="28">
+        <f>SUM(B17:B21)*0.0625</f>
+        <v/>
+      </c>
+      <c r="C22" s="28">
+        <f>SUM(C17:C21)*0.0625</f>
+        <v/>
+      </c>
+      <c r="D22" s="28">
+        <f>SUM(D17:D21)*0.0625</f>
+        <v/>
+      </c>
+      <c r="E22" s="12" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>Labor — demo &amp; disposal</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="inlineStr"/>
+      <c r="C23" s="28" t="inlineStr"/>
+      <c r="D23" s="28" t="inlineStr"/>
+      <c r="E23" s="12" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>Labor — install</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="inlineStr"/>
+      <c r="C24" s="28" t="inlineStr"/>
+      <c r="D24" s="28" t="inlineStr"/>
+      <c r="E24" s="12" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
           <t>Labor — stairs (treads &amp; risers)</t>
         </is>
       </c>
-      <c r="B22" s="28" t="inlineStr"/>
-      <c r="C22" s="28" t="inlineStr"/>
-      <c r="D22" s="28" t="inlineStr"/>
-      <c r="E22" s="12" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr"/>
+      <c r="C25" s="28" t="inlineStr"/>
+      <c r="D25" s="28" t="inlineStr"/>
+      <c r="E25" s="12" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>TOTAL ESTIMATED</t>
         </is>
       </c>
-      <c r="B23" s="31">
-        <f>SUM(B17:B22)</f>
-        <v/>
-      </c>
-      <c r="C23" s="31">
-        <f>SUM(C17:C22)</f>
-        <v/>
-      </c>
-      <c r="D23" s="31">
-        <f>SUM(D17:D22)</f>
-        <v/>
-      </c>
-      <c r="E23" s="27" t="inlineStr">
+      <c r="B26" s="31">
+        <f>SUM(B17:B25)</f>
+        <v/>
+      </c>
+      <c r="C26" s="31">
+        <f>SUM(C17:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="31">
+        <f>SUM(D17:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="27" t="inlineStr">
         <is>
           <t>Compare options here, pick one in 'Selected option' above, and the budget below fills itself in.</t>
         </is>
       </c>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="11" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="11" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>Premium vs. cheapest option</t>
         </is>
       </c>
-      <c r="B24" s="33">
-        <f>B23-MIN($B$23:$D$23)</f>
-        <v/>
-      </c>
-      <c r="C24" s="33">
-        <f>C23-MIN($B$23:$D$23)</f>
-        <v/>
-      </c>
-      <c r="D24" s="33">
-        <f>D23-MIN($B$23:$D$23)</f>
-        <v/>
-      </c>
-      <c r="E24" s="12" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="B27" s="33">
+        <f>B26-MIN($B$26:$D$26)</f>
+        <v/>
+      </c>
+      <c r="C27" s="33">
+        <f>C26-MIN($B$26:$D$26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="33">
+        <f>D26-MIN($B$26:$D$26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="12" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>STEP 2 — BUDGET vs. ACTUAL  (budget auto-fills from the selected option)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Actual (from cost log)</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Flooring materials</t>
-        </is>
-      </c>
-      <c r="B28" s="14">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$23,5,FALSE))</f>
-        <v/>
-      </c>
-      <c r="C28" s="14">
-        <f>SUMIF($D$42:$D$140,$A28,$E$42:$E$140)</f>
-        <v/>
-      </c>
-      <c r="D28" s="14">
-        <f>IF(B28="","",B28-C28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Underlayment &amp; supplies</t>
-        </is>
-      </c>
-      <c r="B29" s="14">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$23,6,FALSE))</f>
-        <v/>
-      </c>
-      <c r="C29" s="14">
-        <f>SUMIF($D$42:$D$140,$A29,$E$42:$E$140)</f>
-        <v/>
-      </c>
-      <c r="D29" s="14">
-        <f>IF(B29="","",B29-C29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Sales tax</t>
-        </is>
-      </c>
-      <c r="B30" s="14">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$23,7,FALSE))</f>
-        <v/>
-      </c>
-      <c r="C30" s="14">
-        <f>SUMIF($D$42:$D$140,$A30,$E$42:$E$140)</f>
-        <v/>
-      </c>
-      <c r="D30" s="14">
-        <f>IF(B30="","",B30-C30)</f>
-        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Labor — demo &amp; disposal</t>
+          <t>Flooring materials</t>
         </is>
       </c>
       <c r="B31" s="14">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$23,8,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,5,FALSE))</f>
         <v/>
       </c>
       <c r="C31" s="14">
-        <f>SUMIF($D$42:$D$140,$A31,$E$42:$E$140)</f>
+        <f>SUMIF($D$48:$D$147,$A31,$E$48:$E$147)</f>
         <v/>
       </c>
       <c r="D31" s="14">
@@ -3160,15 +3284,15 @@
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Labor — install</t>
+          <t>Underlayment &amp; supplies</t>
         </is>
       </c>
       <c r="B32" s="14">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$23,9,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,6,FALSE))</f>
         <v/>
       </c>
       <c r="C32" s="14">
-        <f>SUMIF($D$42:$D$140,$A32,$E$42:$E$140)</f>
+        <f>SUMIF($D$48:$D$147,$A32,$E$48:$E$147)</f>
         <v/>
       </c>
       <c r="D32" s="14">
@@ -3179,15 +3303,15 @@
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Labor — stairs</t>
+          <t>Stair nose trim</t>
         </is>
       </c>
       <c r="B33" s="14">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$23,10,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,7,FALSE))</f>
         <v/>
       </c>
       <c r="C33" s="14">
-        <f>SUMIF($D$42:$D$140,$A33,$E$42:$E$140)</f>
+        <f>SUMIF($D$48:$D$147,$A33,$E$48:$E$147)</f>
         <v/>
       </c>
       <c r="D33" s="14">
@@ -3198,12 +3322,15 @@
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Permits &amp; fees</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="n"/>
+          <t>Stair risers</t>
+        </is>
+      </c>
+      <c r="B34" s="14">
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,8,FALSE))</f>
+        <v/>
+      </c>
       <c r="C34" s="14">
-        <f>SUMIF($D$42:$D$140,$A34,$E$42:$E$140)</f>
+        <f>SUMIF($D$48:$D$147,$A34,$E$48:$E$147)</f>
         <v/>
       </c>
       <c r="D34" s="14">
@@ -3214,12 +3341,15 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="n"/>
+          <t>Contractor discount</t>
+        </is>
+      </c>
+      <c r="B35" s="14">
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,9,FALSE))</f>
+        <v/>
+      </c>
       <c r="C35" s="14">
-        <f>SUMIF($D$42:$D$140,$A35,$E$42:$E$140)</f>
+        <f>SUMIF($D$48:$D$147,$A35,$E$48:$E$147)</f>
         <v/>
       </c>
       <c r="D35" s="14">
@@ -3230,142 +3360,196 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
+          <t>Sales tax</t>
+        </is>
+      </c>
+      <c r="B36" s="14">
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,10,FALSE))</f>
+        <v/>
+      </c>
+      <c r="C36" s="14">
+        <f>SUMIF($D$48:$D$147,$A36,$E$48:$E$147)</f>
+        <v/>
+      </c>
+      <c r="D36" s="14">
+        <f>IF(B36="","",B36-C36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Labor — demo &amp; disposal</t>
+        </is>
+      </c>
+      <c r="B37" s="14">
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,11,FALSE))</f>
+        <v/>
+      </c>
+      <c r="C37" s="14">
+        <f>SUMIF($D$48:$D$147,$A37,$E$48:$E$147)</f>
+        <v/>
+      </c>
+      <c r="D37" s="14">
+        <f>IF(B37="","",B37-C37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Labor — install</t>
+        </is>
+      </c>
+      <c r="B38" s="14">
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,12,FALSE))</f>
+        <v/>
+      </c>
+      <c r="C38" s="14">
+        <f>SUMIF($D$48:$D$147,$A38,$E$48:$E$147)</f>
+        <v/>
+      </c>
+      <c r="D38" s="14">
+        <f>IF(B38="","",B38-C38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Labor — stairs</t>
+        </is>
+      </c>
+      <c r="B39" s="14">
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,13,FALSE))</f>
+        <v/>
+      </c>
+      <c r="C39" s="14">
+        <f>SUMIF($D$48:$D$147,$A39,$E$48:$E$147)</f>
+        <v/>
+      </c>
+      <c r="D39" s="14">
+        <f>IF(B39="","",B39-C39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Permits &amp; fees</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="14">
+        <f>SUMIF($D$48:$D$147,$A40,$E$48:$E$147)</f>
+        <v/>
+      </c>
+      <c r="D40" s="14">
+        <f>IF(B40="","",B40-C40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="14">
+        <f>SUMIF($D$48:$D$147,$A41,$E$48:$E$147)</f>
+        <v/>
+      </c>
+      <c r="D41" s="14">
+        <f>IF(B41="","",B41-C41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
           <t>Contingency</t>
         </is>
       </c>
-      <c r="B36" s="14">
-        <f>SUM(B28:B35)*$B$9</f>
-        <v/>
-      </c>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="14">
-        <f>B36-C36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="30" t="inlineStr">
+      <c r="B42" s="14">
+        <f>SUM(B31:B41)*$B$9</f>
+        <v/>
+      </c>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14">
+        <f>B42-C42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="30" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B37" s="34">
-        <f>SUM(B28:B36)</f>
-        <v/>
-      </c>
-      <c r="C37" s="34">
-        <f>SUM(C28:C36)</f>
-        <v/>
-      </c>
-      <c r="D37" s="34">
-        <f>B37-C37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>The Actual total (C37) is what feeds the Basis Tracker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="B43" s="34">
+        <f>SUM(B31:B42)</f>
+        <v/>
+      </c>
+      <c r="C43" s="34">
+        <f>SUM(C31:C42)</f>
+        <v/>
+      </c>
+      <c r="D43" s="34">
+        <f>B43-C43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>The Actual total (C43) is what feeds the Basis Tracker. Log receipts net of discount, or log the discount as a negative amount under 'Contractor discount'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>STEP 3 — COST LOG  (record every payment; Actuals above update automatically)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D47" s="9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F47" s="9" t="inlineStr">
         <is>
           <t>Payment method</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="n"/>
-      <c r="B42" s="12" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="12" t="n"/>
-      <c r="E42" s="14" t="n"/>
-      <c r="F42" s="12" t="n"/>
-      <c r="G42" s="12" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="n"/>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="12" t="n"/>
-      <c r="E43" s="14" t="n"/>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="12" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="n"/>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="14" t="n"/>
-      <c r="F44" s="12" t="n"/>
-      <c r="G44" s="12" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="n"/>
-      <c r="B45" s="12" t="n"/>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="12" t="n"/>
-      <c r="E45" s="14" t="n"/>
-      <c r="F45" s="12" t="n"/>
-      <c r="G45" s="12" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="n"/>
-      <c r="B46" s="12" t="n"/>
-      <c r="C46" s="12" t="n"/>
-      <c r="D46" s="12" t="n"/>
-      <c r="E46" s="14" t="n"/>
-      <c r="F46" s="12" t="n"/>
-      <c r="G46" s="12" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="n"/>
-      <c r="B47" s="12" t="n"/>
-      <c r="C47" s="12" t="n"/>
-      <c r="D47" s="12" t="n"/>
-      <c r="E47" s="14" t="n"/>
-      <c r="F47" s="12" t="n"/>
-      <c r="G47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n"/>
@@ -4204,21 +4388,85 @@
       <c r="F140" s="12" t="n"/>
       <c r="G140" s="12" t="n"/>
     </row>
+    <row r="141">
+      <c r="A141" s="8" t="n"/>
+      <c r="B141" s="12" t="n"/>
+      <c r="C141" s="12" t="n"/>
+      <c r="D141" s="12" t="n"/>
+      <c r="E141" s="14" t="n"/>
+      <c r="F141" s="12" t="n"/>
+      <c r="G141" s="12" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="8" t="n"/>
+      <c r="B142" s="12" t="n"/>
+      <c r="C142" s="12" t="n"/>
+      <c r="D142" s="12" t="n"/>
+      <c r="E142" s="14" t="n"/>
+      <c r="F142" s="12" t="n"/>
+      <c r="G142" s="12" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="n"/>
+      <c r="B143" s="12" t="n"/>
+      <c r="C143" s="12" t="n"/>
+      <c r="D143" s="12" t="n"/>
+      <c r="E143" s="14" t="n"/>
+      <c r="F143" s="12" t="n"/>
+      <c r="G143" s="12" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="8" t="n"/>
+      <c r="B144" s="12" t="n"/>
+      <c r="C144" s="12" t="n"/>
+      <c r="D144" s="12" t="n"/>
+      <c r="E144" s="14" t="n"/>
+      <c r="F144" s="12" t="n"/>
+      <c r="G144" s="12" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="n"/>
+      <c r="B145" s="12" t="n"/>
+      <c r="C145" s="12" t="n"/>
+      <c r="D145" s="12" t="n"/>
+      <c r="E145" s="14" t="n"/>
+      <c r="F145" s="12" t="n"/>
+      <c r="G145" s="12" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="8" t="n"/>
+      <c r="B146" s="12" t="n"/>
+      <c r="C146" s="12" t="n"/>
+      <c r="D146" s="12" t="n"/>
+      <c r="E146" s="14" t="n"/>
+      <c r="F146" s="12" t="n"/>
+      <c r="G146" s="12" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="8" t="n"/>
+      <c r="B147" s="12" t="n"/>
+      <c r="C147" s="12" t="n"/>
+      <c r="D147" s="12" t="n"/>
+      <c r="E147" s="14" t="n"/>
+      <c r="F147" s="12" t="n"/>
+      <c r="G147" s="12" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="E19:G19"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="E23:G23"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="E26:G26"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A29:G29"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -4227,8 +4475,8 @@
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=$B$13:$D$13</formula1>
     </dataValidation>
-    <dataValidation sqref="D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 D52 D53 D54 D55 D56 D57 D58 D59 D60 D61 D62 D63 D64 D65 D66 D67 D68 D69 D70 D71 D72 D73 D74 D75 D76 D77 D78 D79 D80 D81 D82 D83 D84 D85 D86 D87 D88 D89 D90 D91 D92 D93 D94 D95 D96 D97 D98 D99 D100 D101 D102 D103 D104 D105 D106 D107 D108 D109 D110 D111 D112 D113 D114 D115 D116 D117 D118 D119 D120 D121 D122 D123 D124 D125 D126 D127 D128 D129 D130 D131 D132 D133 D134 D135 D136 D137 D138 D139 D140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=$A$28:$A$35</formula1>
+    <dataValidation sqref="D48 D49 D50 D51 D52 D53 D54 D55 D56 D57 D58 D59 D60 D61 D62 D63 D64 D65 D66 D67 D68 D69 D70 D71 D72 D73 D74 D75 D76 D77 D78 D79 D80 D81 D82 D83 D84 D85 D86 D87 D88 D89 D90 D91 D92 D93 D94 D95 D96 D97 D98 D99 D100 D101 D102 D103 D104 D105 D106 D107 D108 D109 D110 D111 D112 D113 D114 D115 D116 D117 D118 D119 D120 D121 D122 D123 D124 D125 D126 D127 D128 D129 D130 D131 D132 D133 D134 D135 D136 D137 D138 D139 D140 D141 D142 D143 D144 D145 D146 D147" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=$A$31:$A$41</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/4-Indian-Brook-House-Tracker.xlsx
+++ b/4-Indian-Brook-House-Tracker.xlsx
@@ -192,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -222,7 +222,6 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -735,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -790,7 +789,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>1 — ACQUISITION COSTS  (purchase price + closing costs added to basis)</t>
+          <t>ACQUISITION COSTS</t>
         </is>
       </c>
     </row>
@@ -835,11 +834,7 @@
         </is>
       </c>
       <c r="B11" s="14" t="n"/>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>From the closing disclosure</t>
-        </is>
-      </c>
+      <c r="C11" s="13" t="inlineStr"/>
       <c r="D11" s="10" t="n"/>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="11" t="n"/>
@@ -887,11 +882,7 @@
         </is>
       </c>
       <c r="B15" s="14" t="n"/>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>In MA the seller usually pays deed stamps</t>
-        </is>
-      </c>
+      <c r="C15" s="13" t="inlineStr"/>
       <c r="D15" s="10" t="n"/>
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="11" t="n"/>
@@ -922,7 +913,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2 — CAPITAL IMPROVEMENTS  (auto-fed from each project tab's Actual total)</t>
+          <t>CAPITAL IMPROVEMENTS</t>
         </is>
       </c>
     </row>
@@ -1131,39 +1122,15 @@
       </c>
       <c r="E43" s="11" t="n"/>
     </row>
-    <row r="45">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t>• Only capital improvements (things that add value or extend the property's life) add to basis — new floors yes, repainting a room no.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="19" t="inlineStr">
-        <is>
-          <t>• Set Capital? to N for repairs you still want to track; they'll be listed but excluded from the basis total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="19" t="inlineStr">
-        <is>
-          <t>• Keep receipts and contracts for everything on this sheet. This is a tracking aid, not tax advice.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="15">
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C9:F9"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="D43:E43"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C15:F15"/>
@@ -1228,7 +1195,7 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Quoting</t>
         </is>
@@ -1240,7 +1207,7 @@
           <t>Contractor / quote</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Footprints Floors of Central MA (ACS Custom Solutions Inc.) — Proposal #25584, 6/30/2026. Labor only; 50% deposit ($4,528.80) before work, balance on completion.</t>
         </is>
@@ -1252,7 +1219,7 @@
           <t>Materials source</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Floor &amp; Decor, Waltham MA (cart re-priced 7/2026); 5% materials discount through flooring contractor</t>
         </is>
@@ -1264,7 +1231,7 @@
           <t>Selected option</t>
         </is>
       </c>
-      <c r="B8" s="21" t="n"/>
+      <c r="B8" s="20" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1272,7 +1239,7 @@
           <t>Contingency %</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="21" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1282,7 +1249,7 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Labor quote excludes materials. Subfloor leveling/remediation not included and may add cost once carpet is removed. 3% fee on credit card payments (max $3,000/card per project).</t>
         </is>
@@ -1291,7 +1258,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>STEP 1 — COMPARE OPTIONS  (estimated all-in cost per option)</t>
+          <t>OPTION COMPARISON</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1268,17 @@
           <t>Cost component</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>Sapelo Shore</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Big Sur</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>Gunstock Oak</t>
         </is>
@@ -1323,27 +1290,27 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Item # / SKU</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>101128890</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>101069698</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>101068104</t>
         </is>
       </c>
-      <c r="E14" s="27" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t>All Floor &amp; Decor. Sapelo Shore &amp; Big Sur: waterproof hybrid resilient plank w/ cork pad, 8mm 7"x51". Gunstock Oak: waterproof rigid core LVP.</t>
         </is>
@@ -1352,104 +1319,104 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Price per box</t>
         </is>
       </c>
-      <c r="B15" s="28" t="n">
+      <c r="B15" s="27" t="n">
         <v>61.71</v>
       </c>
-      <c r="C15" s="28" t="n">
+      <c r="C15" s="27" t="n">
         <v>97.08</v>
       </c>
-      <c r="D15" s="28" t="n">
+      <c r="D15" s="27" t="n">
         <v>75.56999999999999</v>
       </c>
       <c r="E15" s="12" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>Boxes needed</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="28" t="n">
         <v>66</v>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="28" t="n">
         <v>60</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="28" t="n">
         <v>64</v>
       </c>
       <c r="E16" s="12" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Flooring material</t>
         </is>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="27">
         <f>B15*B16</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="27">
         <f>C15*C16</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="27">
         <f>D15*D16</f>
         <v/>
       </c>
       <c r="E17" s="12" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Underlayment &amp; supplies</t>
         </is>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="27">
         <f>13*59.99</f>
         <v/>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="27">
         <f>13*59.99</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="27">
         <f>13*59.99</f>
         <v/>
       </c>
-      <c r="E18" s="27" t="inlineStr">
-        <is>
-          <t>Sentinel Protect Plus underlayment — 13 rolls x $59.99 (100 sqft each), same for every option.</t>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>Sentinel Protect Plus underlayment — 13 rolls x $59.99 (100 sqft each).</t>
         </is>
       </c>
       <c r="F18" s="10" t="n"/>
       <c r="G18" s="11" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>Stair nose trim</t>
         </is>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="27">
         <f>7*29.99</f>
         <v/>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="27">
         <f>7*29.99</f>
         <v/>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="27">
         <f>7*29.99</f>
         <v/>
       </c>
-      <c r="E19" s="27" t="inlineStr">
+      <c r="E19" s="26" t="inlineStr">
         <is>
           <t>7 stair noses x $29.99.</t>
         </is>
@@ -1458,24 +1425,24 @@
       <c r="G19" s="11" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>Stair risers</t>
         </is>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="27">
         <f>13*20</f>
         <v/>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="27">
         <f>13*20</f>
         <v/>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="27">
         <f>13*20</f>
         <v/>
       </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t>13 risers x $20.00.</t>
         </is>
@@ -1484,24 +1451,24 @@
       <c r="G20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Contractor discount on materials (5%)</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="27">
         <f>-0.05*SUM(B17:B20)</f>
         <v/>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="27">
         <f>-0.05*SUM(C17:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="27">
         <f>-0.05*SUM(D17:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="27" t="inlineStr">
+      <c r="E21" s="26" t="inlineStr">
         <is>
           <t>5% off all materials through the flooring contractor.</t>
         </is>
@@ -1510,41 +1477,41 @@
       <c r="G21" s="11" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>Est. sales tax (6.25% MA, materials)</t>
         </is>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="27">
         <f>SUM(B17:B21)*0.0625</f>
         <v/>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="27">
         <f>SUM(C17:C21)*0.0625</f>
         <v/>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="27">
         <f>SUM(D17:D21)*0.0625</f>
         <v/>
       </c>
       <c r="E22" s="12" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>Labor — demo &amp; disposal</t>
         </is>
       </c>
-      <c r="B23" s="28" t="n">
+      <c r="B23" s="27" t="n">
         <v>2642.3</v>
       </c>
-      <c r="C23" s="28" t="n">
+      <c r="C23" s="27" t="n">
         <v>2642.3</v>
       </c>
-      <c r="D23" s="28" t="n">
+      <c r="D23" s="27" t="n">
         <v>2642.3</v>
       </c>
-      <c r="E23" s="27" t="inlineStr">
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>Footprints: demo carpet, remove &amp; return baseboards, trash removal.</t>
         </is>
@@ -1553,21 +1520,21 @@
       <c r="G23" s="11" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>Labor — install</t>
         </is>
       </c>
-      <c r="B24" s="28" t="n">
+      <c r="B24" s="27" t="n">
         <v>4535.3</v>
       </c>
-      <c r="C24" s="28" t="n">
+      <c r="C24" s="27" t="n">
         <v>4535.3</v>
       </c>
-      <c r="D24" s="28" t="n">
+      <c r="D24" s="27" t="n">
         <v>4535.3</v>
       </c>
-      <c r="E24" s="27" t="inlineStr">
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>Footprints: install click-lock floating floor.</t>
         </is>
@@ -1576,63 +1543,57 @@
       <c r="G24" s="11" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>Labor — stairs (treads &amp; risers)</t>
         </is>
       </c>
-      <c r="B25" s="28" t="n">
+      <c r="B25" s="27" t="n">
         <v>1880</v>
       </c>
-      <c r="C25" s="28" t="n">
+      <c r="C25" s="27" t="n">
         <v>1880</v>
       </c>
-      <c r="D25" s="28" t="n">
+      <c r="D25" s="27" t="n">
         <v>1880</v>
       </c>
       <c r="E25" s="12" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>TOTAL ESTIMATED</t>
         </is>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="30">
         <f>SUM(B17:B25)</f>
         <v/>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="30">
         <f>SUM(C17:C25)</f>
         <v/>
       </c>
-      <c r="D26" s="31">
+      <c r="D26" s="30">
         <f>SUM(D17:D25)</f>
         <v/>
       </c>
-      <c r="E26" s="27" t="inlineStr">
-        <is>
-          <t>Labor $9,057.60 is identical across options, so the spread comes entirely from the plank you pick.</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="11" t="n"/>
+      <c r="E26" s="12" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>Premium vs. cheapest option</t>
         </is>
       </c>
-      <c r="B27" s="33">
+      <c r="B27" s="32">
         <f>B26-MIN($B$26:$D$26)</f>
         <v/>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="32">
         <f>C26-MIN($B$26:$D$26)</f>
         <v/>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="32">
         <f>D26-MIN($B$26:$D$26)</f>
         <v/>
       </c>
@@ -1641,7 +1602,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>STEP 2 — BUDGET vs. ACTUAL  (budget auto-fills from the selected option)</t>
+          <t>BUDGET vs. ACTUAL</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1619,7 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Actual (from cost log)</t>
+          <t>Actual</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -1887,35 +1848,28 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30" t="inlineStr">
+      <c r="A43" s="29" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B43" s="34">
+      <c r="B43" s="33">
         <f>SUM(B31:B42)</f>
         <v/>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="33">
         <f>SUM(C31:C42)</f>
         <v/>
       </c>
-      <c r="D43" s="34">
+      <c r="D43" s="33">
         <f>B43-C43</f>
         <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="19" t="inlineStr">
-        <is>
-          <t>The Actual total (C43) is what feeds the Basis Tracker. Log receipts net of discount, or log the discount as a negative amount under 'Contractor discount'.</t>
-        </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>STEP 3 — COST LOG  (record every payment; Actuals above update automatically)</t>
+          <t>COST LOG</t>
         </is>
       </c>
     </row>
@@ -2857,12 +2811,11 @@
       <c r="G147" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="19">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A29:G29"/>
-    <mergeCell ref="E26:G26"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B10:F10"/>
@@ -2916,16 +2869,12 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PROJECT TEMPLATE — (duplicate this tab for each new project)</t>
+          <t>PROJECT TEMPLATE</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>How to use: right-click the tab &gt; Duplicate. Rename it, fill in options &amp; quotes, then add one row for it in the Basis Tracker improvements table pointing at the new tab's Actual total (cell C43).</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -2940,7 +2889,7 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
@@ -2952,7 +2901,7 @@
           <t>Contractor / quote</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
+      <c r="B6" s="19" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -2960,7 +2909,7 @@
           <t>Materials source</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr"/>
+      <c r="B7" s="19" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2968,7 +2917,7 @@
           <t>Selected option</t>
         </is>
       </c>
-      <c r="B8" s="21" t="n"/>
+      <c r="B8" s="20" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -2976,7 +2925,7 @@
           <t>Contingency %</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="21" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2986,12 +2935,12 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr"/>
+      <c r="B10" s="22" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>STEP 1 — COMPARE OPTIONS  (estimated all-in cost per option)</t>
+          <t>OPTION COMPARISON</t>
         </is>
       </c>
     </row>
@@ -3001,17 +2950,17 @@
           <t>Cost component</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>Option A</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Option B</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>Option C</t>
         </is>
@@ -3023,211 +2972,199 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Item # / SKU</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n"/>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="26" t="n"/>
+      <c r="B14" s="25" t="n"/>
+      <c r="C14" s="25" t="n"/>
+      <c r="D14" s="25" t="n"/>
       <c r="E14" s="12" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Unit price</t>
         </is>
       </c>
-      <c r="B15" s="28" t="n"/>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="28" t="n"/>
+      <c r="B15" s="27" t="n"/>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
       <c r="E15" s="12" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n"/>
-      <c r="C16" s="29" t="n"/>
-      <c r="D16" s="29" t="n"/>
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="28" t="n"/>
       <c r="E16" s="12" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Flooring material</t>
         </is>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="27">
         <f>B15*B16</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="27">
         <f>C15*C16</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="27">
         <f>D15*D16</f>
         <v/>
       </c>
       <c r="E17" s="12" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Underlayment &amp; supplies</t>
         </is>
       </c>
-      <c r="B18" s="28" t="inlineStr"/>
-      <c r="C18" s="28" t="inlineStr"/>
-      <c r="D18" s="28" t="inlineStr"/>
+      <c r="B18" s="27" t="inlineStr"/>
+      <c r="C18" s="27" t="inlineStr"/>
+      <c r="D18" s="27" t="inlineStr"/>
       <c r="E18" s="12" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>Stair nose trim</t>
         </is>
       </c>
-      <c r="B19" s="28" t="inlineStr"/>
-      <c r="C19" s="28" t="inlineStr"/>
-      <c r="D19" s="28" t="inlineStr"/>
-      <c r="E19" s="27" t="inlineStr">
-        <is>
-          <t>Rename these two rows for whatever extra materials the project needs.</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="11" t="n"/>
+      <c r="B19" s="27" t="inlineStr"/>
+      <c r="C19" s="27" t="inlineStr"/>
+      <c r="D19" s="27" t="inlineStr"/>
+      <c r="E19" s="12" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>Stair risers</t>
         </is>
       </c>
-      <c r="B20" s="28" t="inlineStr"/>
-      <c r="C20" s="28" t="inlineStr"/>
-      <c r="D20" s="28" t="inlineStr"/>
+      <c r="B20" s="27" t="inlineStr"/>
+      <c r="C20" s="27" t="inlineStr"/>
+      <c r="D20" s="27" t="inlineStr"/>
       <c r="E20" s="12" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Contractor discount on materials (0%)</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="27">
         <f>-0.0*SUM(B17:B20)</f>
         <v/>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="27">
         <f>-0.0*SUM(C17:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="27">
         <f>-0.0*SUM(D17:D20)</f>
         <v/>
       </c>
       <c r="E21" s="12" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>Est. sales tax (6.25% MA, materials)</t>
         </is>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="27">
         <f>SUM(B17:B21)*0.0625</f>
         <v/>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="27">
         <f>SUM(C17:C21)*0.0625</f>
         <v/>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="27">
         <f>SUM(D17:D21)*0.0625</f>
         <v/>
       </c>
       <c r="E22" s="12" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>Labor — demo &amp; disposal</t>
         </is>
       </c>
-      <c r="B23" s="28" t="inlineStr"/>
-      <c r="C23" s="28" t="inlineStr"/>
-      <c r="D23" s="28" t="inlineStr"/>
+      <c r="B23" s="27" t="inlineStr"/>
+      <c r="C23" s="27" t="inlineStr"/>
+      <c r="D23" s="27" t="inlineStr"/>
       <c r="E23" s="12" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>Labor — install</t>
         </is>
       </c>
-      <c r="B24" s="28" t="inlineStr"/>
-      <c r="C24" s="28" t="inlineStr"/>
-      <c r="D24" s="28" t="inlineStr"/>
+      <c r="B24" s="27" t="inlineStr"/>
+      <c r="C24" s="27" t="inlineStr"/>
+      <c r="D24" s="27" t="inlineStr"/>
       <c r="E24" s="12" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>Labor — stairs (treads &amp; risers)</t>
         </is>
       </c>
-      <c r="B25" s="28" t="inlineStr"/>
-      <c r="C25" s="28" t="inlineStr"/>
-      <c r="D25" s="28" t="inlineStr"/>
+      <c r="B25" s="27" t="inlineStr"/>
+      <c r="C25" s="27" t="inlineStr"/>
+      <c r="D25" s="27" t="inlineStr"/>
       <c r="E25" s="12" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>TOTAL ESTIMATED</t>
         </is>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="30">
         <f>SUM(B17:B25)</f>
         <v/>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="30">
         <f>SUM(C17:C25)</f>
         <v/>
       </c>
-      <c r="D26" s="31">
+      <c r="D26" s="30">
         <f>SUM(D17:D25)</f>
         <v/>
       </c>
-      <c r="E26" s="27" t="inlineStr">
-        <is>
-          <t>Compare options here, pick one in 'Selected option' above, and the budget below fills itself in.</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="11" t="n"/>
+      <c r="E26" s="12" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>Premium vs. cheapest option</t>
         </is>
       </c>
-      <c r="B27" s="33">
+      <c r="B27" s="32">
         <f>B26-MIN($B$26:$D$26)</f>
         <v/>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="32">
         <f>C26-MIN($B$26:$D$26)</f>
         <v/>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="32">
         <f>D26-MIN($B$26:$D$26)</f>
         <v/>
       </c>
@@ -3236,7 +3173,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>STEP 2 — BUDGET vs. ACTUAL  (budget auto-fills from the selected option)</t>
+          <t>BUDGET vs. ACTUAL</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3190,7 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Actual (from cost log)</t>
+          <t>Actual</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -3482,35 +3419,28 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30" t="inlineStr">
+      <c r="A43" s="29" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B43" s="34">
+      <c r="B43" s="33">
         <f>SUM(B31:B42)</f>
         <v/>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="33">
         <f>SUM(C31:C42)</f>
         <v/>
       </c>
-      <c r="D43" s="34">
+      <c r="D43" s="33">
         <f>B43-C43</f>
         <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="19" t="inlineStr">
-        <is>
-          <t>The Actual total (C43) is what feeds the Basis Tracker. Log receipts net of discount, or log the discount as a negative amount under 'Contractor discount'.</t>
-        </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>STEP 3 — COST LOG  (record every payment; Actuals above update automatically)</t>
+          <t>COST LOG</t>
         </is>
       </c>
     </row>
@@ -4452,16 +4382,14 @@
       <c r="G147" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="12">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="E19:G19"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="E26:G26"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="B8:F8"/>

--- a/4-Indian-Brook-House-Tracker.xlsx
+++ b/4-Indian-Brook-House-Tracker.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Basis Tracker" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2nd Floor Flooring" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Basis Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2nd Floor Flooring" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Project Estimates" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Project Template" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Read Me" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,10 +46,6 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
@@ -60,6 +57,10 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -198,26 +199,22 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
@@ -234,14 +231,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -250,15 +247,19 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -621,115 +622,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>4 INDIAN BROOK ROAD — HOUSE TRACKER</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Purchase &amp; improvement history</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>What this is</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>One workbook that tracks what the house cost and every project that adds to it. Share it in Google Drive so both of you can edit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Basis Tracker</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Purchase price ($1,060,000, closing 7/17/2026) + closing costs + capital improvements = adjusted cost basis. Each project tab feeds one row of the improvements table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2nd Floor Flooring</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>First project. Compare the 3 Floor &amp; Decor plank options (incl. underlayment, stair nose &amp; risers, 5% contractor discount, est. tax, and Footprints labor), pick one in 'Selected option' (yellow cell), and the budget fills in automatically. Log payments in the cost log at the bottom — actuals and the Basis Tracker update themselves.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Project Template</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>For the next project: right-click the tab &gt; Duplicate, rename it, fill in your options/quotes, then add a row in the Basis Tracker improvements table pointing at the new tab's cell C43 (its Actual total).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Sources</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Labor: Footprints Floors of Central MA proposal #25584 (6/30/2026) — $9,057.60, materials excluded. Materials: Floor &amp; Decor Waltham cart (7/2026) — Sapelo Shore / Big Sur / Gunstock Oak + Sentinel underlayment, plus 7 stair noses @ $29.99 and 13 risers @ $20; 5% contractor discount on materials.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>In Google Sheets everything here — dropdowns, cross-tab formulas, formatting — survives File &gt; Import. Use 'Replace spreadsheet' when importing so tab references stay intact.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
     <tabColor rgb="00BF9000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -760,367 +652,367 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>PROPERTY</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Purchase price</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="5" t="n">
         <v>1060000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Closing date</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="6" t="n">
         <v>46220</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>ACQUISITION COSTS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="11" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="9" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Purchase price</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="5" t="n">
         <v>1060000</v>
       </c>
-      <c r="C10" s="13" t="inlineStr"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="11" t="n"/>
+      <c r="C10" s="11" t="inlineStr"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="9" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Attorney / legal fees</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="13" t="inlineStr"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="11" t="n"/>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="11" t="inlineStr"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="9" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Owner's title insurance</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="13" t="inlineStr"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="11" t="n"/>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="11" t="inlineStr"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="9" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Recording fees</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n"/>
-      <c r="C13" s="13" t="inlineStr"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="11" t="n"/>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="11" t="inlineStr"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="9" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Survey / plot plan</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="13" t="inlineStr"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="11" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="11" t="inlineStr"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="9" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Transfer taxes paid by buyer (if any)</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="13" t="inlineStr"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="11" t="n"/>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="11" t="inlineStr"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="9" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Other closing costs added to basis</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="13" t="inlineStr"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="11" t="n"/>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="11" t="inlineStr"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="9" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Subtotal — acquisition basis</t>
         </is>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="14">
         <f>SUM(B10:B16)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>CAPITAL IMPROVEMENTS</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Date completed</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Where tracked</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Capital? (Y/N)</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Second floor flooring</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Tab: 2nd Floor Flooring</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="12">
         <f>'2nd Floor Flooring'!C43</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="14" t="n"/>
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="12" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n"/>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="14" t="n"/>
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="12" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="14" t="n"/>
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="12" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n"/>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="14" t="n"/>
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="12" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n"/>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="14" t="n"/>
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="12" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n"/>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="14" t="n"/>
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="12" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n"/>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="14" t="n"/>
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="12" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n"/>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="14" t="n"/>
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="12" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n"/>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="14" t="n"/>
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="12" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n"/>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="14" t="n"/>
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="12" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n"/>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="14" t="n"/>
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="12" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n"/>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="12" t="n"/>
-      <c r="E33" s="14" t="n"/>
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="12" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="n"/>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n"/>
-      <c r="E34" s="14" t="n"/>
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="12" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="n"/>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="14" t="n"/>
+      <c r="A35" s="6" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="12" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n"/>
-      <c r="B36" s="12" t="n"/>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="12" t="n"/>
-      <c r="E36" s="14" t="n"/>
+      <c r="A36" s="6" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="12" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="n"/>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="14" t="n"/>
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="12" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="n"/>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="14" t="n"/>
+      <c r="A38" s="6" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="12" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="n"/>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="14" t="n"/>
+      <c r="A39" s="6" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="12" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="n"/>
-      <c r="B40" s="12" t="n"/>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="12" t="n"/>
-      <c r="E40" s="14" t="n"/>
+      <c r="A40" s="6" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="12" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>Subtotal — capital improvements</t>
         </is>
       </c>
-      <c r="E41" s="16">
+      <c r="E41" s="14">
         <f>SUMIF(D21:D40,"Y",E21:E40)</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>ADJUSTED COST BASIS</t>
         </is>
       </c>
-      <c r="D43" s="18">
+      <c r="D43" s="16">
         <f>B17+E41</f>
         <v/>
       </c>
-      <c r="E43" s="11" t="n"/>
+      <c r="E43" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1149,7 +1041,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F3864"/>
@@ -1183,1632 +1075,1632 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>PROJECT INFO</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Quoting</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Contractor / quote</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Footprints Floors of Central MA (ACS Custom Solutions Inc.) — Proposal #25584, 6/30/2026. Labor only; 50% deposit ($4,528.80) before work, balance on completion.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Materials source</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Floor &amp; Decor, Waltham MA (cart re-priced 7/2026); 5% materials discount through flooring contractor</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Selected option</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n"/>
+      <c r="B8" s="18" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Contingency %</t>
         </is>
       </c>
-      <c r="B9" s="21" t="n">
+      <c r="B9" s="19" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Labor quote excludes materials. Subfloor leveling/remediation not included and may add cost once carpet is removed. 3% fee on credit card payments (max $3,000/card per project).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>OPTION COMPARISON</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Cost component</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>Sapelo Shore</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>Big Sur</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>Gunstock Oak</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Item # / SKU</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>101128890</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>101069698</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>101068104</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>All Floor &amp; Decor. Sapelo Shore &amp; Big Sur: waterproof hybrid resilient plank w/ cork pad, 8mm 7"x51". Gunstock Oak: waterproof rigid core LVP.</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="9" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Price per box</t>
         </is>
       </c>
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="25" t="n">
         <v>61.71</v>
       </c>
-      <c r="C15" s="27" t="n">
+      <c r="C15" s="25" t="n">
         <v>97.08</v>
       </c>
-      <c r="D15" s="27" t="n">
+      <c r="D15" s="25" t="n">
         <v>75.56999999999999</v>
       </c>
-      <c r="E15" s="12" t="n"/>
+      <c r="E15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>Boxes needed</t>
         </is>
       </c>
-      <c r="B16" s="28" t="n">
+      <c r="B16" s="26" t="n">
         <v>66</v>
       </c>
-      <c r="C16" s="28" t="n">
+      <c r="C16" s="26" t="n">
         <v>60</v>
       </c>
-      <c r="D16" s="28" t="n">
+      <c r="D16" s="26" t="n">
         <v>64</v>
       </c>
-      <c r="E16" s="12" t="n"/>
+      <c r="E16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>Flooring material</t>
         </is>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="25">
         <f>B15*B16</f>
         <v/>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="25">
         <f>C15*C16</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="25">
         <f>D15*D16</f>
         <v/>
       </c>
-      <c r="E17" s="12" t="n"/>
+      <c r="E17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Underlayment &amp; supplies</t>
         </is>
       </c>
-      <c r="B18" s="27">
-        <f>13*59.99</f>
-        <v/>
-      </c>
-      <c r="C18" s="27">
-        <f>13*59.99</f>
-        <v/>
-      </c>
-      <c r="D18" s="27">
-        <f>13*59.99</f>
-        <v/>
-      </c>
-      <c r="E18" s="26" t="inlineStr">
-        <is>
-          <t>Sentinel Protect Plus underlayment — 13 rolls x $59.99 (100 sqft each).</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="11" t="n"/>
+      <c r="B18" s="25">
+        <f>15*59.99</f>
+        <v/>
+      </c>
+      <c r="C18" s="25">
+        <f>15*59.99</f>
+        <v/>
+      </c>
+      <c r="D18" s="25">
+        <f>15*59.99</f>
+        <v/>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>Sentinel Protect Plus underlayment — 15 rolls x $59.99 (100 sqft each).</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="9" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>Stair nose trim</t>
         </is>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="25">
         <f>7*29.99</f>
         <v/>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="25">
         <f>7*29.99</f>
         <v/>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="25">
         <f>7*29.99</f>
         <v/>
       </c>
-      <c r="E19" s="26" t="inlineStr">
+      <c r="E19" s="24" t="inlineStr">
         <is>
           <t>7 stair noses x $29.99.</t>
         </is>
       </c>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="11" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="9" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>Stair risers</t>
         </is>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="25">
         <f>13*20</f>
         <v/>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="25">
         <f>13*20</f>
         <v/>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="25">
         <f>13*20</f>
         <v/>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>13 risers x $20.00.</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="11" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="9" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>Contractor discount on materials (5%)</t>
         </is>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="25">
         <f>-0.05*SUM(B17:B20)</f>
         <v/>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="25">
         <f>-0.05*SUM(C17:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="25">
         <f>-0.05*SUM(D17:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="26" t="inlineStr">
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>5% off all materials through the flooring contractor.</t>
         </is>
       </c>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="11" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="9" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>Est. sales tax (6.25% MA, materials)</t>
         </is>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="25">
         <f>SUM(B17:B21)*0.0625</f>
         <v/>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="25">
         <f>SUM(C17:C21)*0.0625</f>
         <v/>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="25">
         <f>SUM(D17:D21)*0.0625</f>
         <v/>
       </c>
-      <c r="E22" s="12" t="n"/>
+      <c r="E22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>Labor — demo &amp; disposal</t>
         </is>
       </c>
-      <c r="B23" s="27" t="n">
+      <c r="B23" s="25" t="n">
         <v>2642.3</v>
       </c>
-      <c r="C23" s="27" t="n">
+      <c r="C23" s="25" t="n">
         <v>2642.3</v>
       </c>
-      <c r="D23" s="27" t="n">
+      <c r="D23" s="25" t="n">
         <v>2642.3</v>
       </c>
-      <c r="E23" s="26" t="inlineStr">
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>Footprints: demo carpet, remove &amp; return baseboards, trash removal.</t>
         </is>
       </c>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="11" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>Labor — install</t>
         </is>
       </c>
-      <c r="B24" s="27" t="n">
+      <c r="B24" s="25" t="n">
         <v>4535.3</v>
       </c>
-      <c r="C24" s="27" t="n">
+      <c r="C24" s="25" t="n">
         <v>4535.3</v>
       </c>
-      <c r="D24" s="27" t="n">
+      <c r="D24" s="25" t="n">
         <v>4535.3</v>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>Footprints: install click-lock floating floor.</t>
         </is>
       </c>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="11" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="9" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>Labor — stairs (treads &amp; risers)</t>
         </is>
       </c>
-      <c r="B25" s="27" t="n">
+      <c r="B25" s="25" t="n">
         <v>1880</v>
       </c>
-      <c r="C25" s="27" t="n">
+      <c r="C25" s="25" t="n">
         <v>1880</v>
       </c>
-      <c r="D25" s="27" t="n">
+      <c r="D25" s="25" t="n">
         <v>1880</v>
       </c>
-      <c r="E25" s="12" t="n"/>
+      <c r="E25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>TOTAL ESTIMATED</t>
         </is>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="28">
         <f>SUM(B17:B25)</f>
         <v/>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="28">
         <f>SUM(C17:C25)</f>
         <v/>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="28">
         <f>SUM(D17:D25)</f>
         <v/>
       </c>
-      <c r="E26" s="12" t="n"/>
+      <c r="E26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>Premium vs. cheapest option</t>
         </is>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="30">
         <f>B26-MIN($B$26:$D$26)</f>
         <v/>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="30">
         <f>C26-MIN($B$26:$D$26)</f>
         <v/>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="30">
         <f>D26-MIN($B$26:$D$26)</f>
         <v/>
       </c>
-      <c r="E27" s="12" t="n"/>
+      <c r="E27" s="10" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>BUDGET vs. ACTUAL</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Flooring materials</t>
         </is>
       </c>
-      <c r="B31" s="14">
+      <c r="B31" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,5,FALSE))</f>
         <v/>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="12">
         <f>SUMIF($D$48:$D$147,$A31,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="12">
         <f>IF(B31="","",B31-C31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Underlayment &amp; supplies</t>
         </is>
       </c>
-      <c r="B32" s="14">
+      <c r="B32" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,6,FALSE))</f>
         <v/>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="12">
         <f>SUMIF($D$48:$D$147,$A32,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="12">
         <f>IF(B32="","",B32-C32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Stair nose trim</t>
         </is>
       </c>
-      <c r="B33" s="14">
+      <c r="B33" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,7,FALSE))</f>
         <v/>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="12">
         <f>SUMIF($D$48:$D$147,$A33,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="12">
         <f>IF(B33="","",B33-C33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>Stair risers</t>
         </is>
       </c>
-      <c r="B34" s="14">
+      <c r="B34" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,8,FALSE))</f>
         <v/>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="12">
         <f>SUMIF($D$48:$D$147,$A34,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="12">
         <f>IF(B34="","",B34-C34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>Contractor discount</t>
         </is>
       </c>
-      <c r="B35" s="14">
+      <c r="B35" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,9,FALSE))</f>
         <v/>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="12">
         <f>SUMIF($D$48:$D$147,$A35,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="12">
         <f>IF(B35="","",B35-C35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>Sales tax</t>
         </is>
       </c>
-      <c r="B36" s="14">
+      <c r="B36" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,10,FALSE))</f>
         <v/>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="12">
         <f>SUMIF($D$48:$D$147,$A36,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="12">
         <f>IF(B36="","",B36-C36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>Labor — demo &amp; disposal</t>
         </is>
       </c>
-      <c r="B37" s="14">
+      <c r="B37" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,11,FALSE))</f>
         <v/>
       </c>
-      <c r="C37" s="14">
+      <c r="C37" s="12">
         <f>SUMIF($D$48:$D$147,$A37,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="12">
         <f>IF(B37="","",B37-C37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Labor — install</t>
         </is>
       </c>
-      <c r="B38" s="14">
+      <c r="B38" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,12,FALSE))</f>
         <v/>
       </c>
-      <c r="C38" s="14">
+      <c r="C38" s="12">
         <f>SUMIF($D$48:$D$147,$A38,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="12">
         <f>IF(B38="","",B38-C38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Labor — stairs</t>
         </is>
       </c>
-      <c r="B39" s="14">
+      <c r="B39" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,13,FALSE))</f>
         <v/>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="12">
         <f>SUMIF($D$48:$D$147,$A39,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D39" s="14">
+      <c r="D39" s="12">
         <f>IF(B39="","",B39-C39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Permits &amp; fees</t>
         </is>
       </c>
-      <c r="B40" s="14" t="n"/>
-      <c r="C40" s="14">
+      <c r="B40" s="12" t="n"/>
+      <c r="C40" s="12">
         <f>SUMIF($D$48:$D$147,$A40,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="12">
         <f>IF(B40="","",B40-C40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B41" s="14" t="n"/>
-      <c r="C41" s="14">
+      <c r="B41" s="12" t="n"/>
+      <c r="C41" s="12">
         <f>SUMIF($D$48:$D$147,$A41,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D41" s="14">
+      <c r="D41" s="12">
         <f>IF(B41="","",B41-C41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Contingency</t>
         </is>
       </c>
-      <c r="B42" s="14">
+      <c r="B42" s="12">
         <f>SUM(B31:B41)*$B$9</f>
         <v/>
       </c>
-      <c r="C42" s="14" t="n"/>
-      <c r="D42" s="14">
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12">
         <f>B42-C42</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="27" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B43" s="33">
+      <c r="B43" s="31">
         <f>SUM(B31:B42)</f>
         <v/>
       </c>
-      <c r="C43" s="33">
+      <c r="C43" s="31">
         <f>SUM(C31:C42)</f>
         <v/>
       </c>
-      <c r="D43" s="33">
+      <c r="D43" s="31">
         <f>B43-C43</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>COST LOG</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>Payment method</t>
         </is>
       </c>
-      <c r="G47" s="9" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="n"/>
-      <c r="B48" s="12" t="n"/>
-      <c r="C48" s="12" t="n"/>
-      <c r="D48" s="12" t="n"/>
-      <c r="E48" s="14" t="n"/>
-      <c r="F48" s="12" t="n"/>
-      <c r="G48" s="12" t="n"/>
+      <c r="A48" s="6" t="n"/>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="n"/>
-      <c r="B49" s="12" t="n"/>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="12" t="n"/>
-      <c r="E49" s="14" t="n"/>
-      <c r="F49" s="12" t="n"/>
-      <c r="G49" s="12" t="n"/>
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="n"/>
-      <c r="B50" s="12" t="n"/>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="12" t="n"/>
-      <c r="E50" s="14" t="n"/>
-      <c r="F50" s="12" t="n"/>
-      <c r="G50" s="12" t="n"/>
+      <c r="A50" s="6" t="n"/>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="n"/>
-      <c r="B51" s="12" t="n"/>
-      <c r="C51" s="12" t="n"/>
-      <c r="D51" s="12" t="n"/>
-      <c r="E51" s="14" t="n"/>
-      <c r="F51" s="12" t="n"/>
-      <c r="G51" s="12" t="n"/>
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="n"/>
-      <c r="B52" s="12" t="n"/>
-      <c r="C52" s="12" t="n"/>
-      <c r="D52" s="12" t="n"/>
-      <c r="E52" s="14" t="n"/>
-      <c r="F52" s="12" t="n"/>
-      <c r="G52" s="12" t="n"/>
+      <c r="A52" s="6" t="n"/>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="n"/>
-      <c r="B53" s="12" t="n"/>
-      <c r="C53" s="12" t="n"/>
-      <c r="D53" s="12" t="n"/>
-      <c r="E53" s="14" t="n"/>
-      <c r="F53" s="12" t="n"/>
-      <c r="G53" s="12" t="n"/>
+      <c r="A53" s="6" t="n"/>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="12" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="n"/>
-      <c r="B54" s="12" t="n"/>
-      <c r="C54" s="12" t="n"/>
-      <c r="D54" s="12" t="n"/>
-      <c r="E54" s="14" t="n"/>
-      <c r="F54" s="12" t="n"/>
-      <c r="G54" s="12" t="n"/>
+      <c r="A54" s="6" t="n"/>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="12" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="n"/>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="12" t="n"/>
-      <c r="D55" s="12" t="n"/>
-      <c r="E55" s="14" t="n"/>
-      <c r="F55" s="12" t="n"/>
-      <c r="G55" s="12" t="n"/>
+      <c r="A55" s="6" t="n"/>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="12" t="n"/>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="n"/>
-      <c r="B56" s="12" t="n"/>
-      <c r="C56" s="12" t="n"/>
-      <c r="D56" s="12" t="n"/>
-      <c r="E56" s="14" t="n"/>
-      <c r="F56" s="12" t="n"/>
-      <c r="G56" s="12" t="n"/>
+      <c r="A56" s="6" t="n"/>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="12" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="n"/>
-      <c r="B57" s="12" t="n"/>
-      <c r="C57" s="12" t="n"/>
-      <c r="D57" s="12" t="n"/>
-      <c r="E57" s="14" t="n"/>
-      <c r="F57" s="12" t="n"/>
-      <c r="G57" s="12" t="n"/>
+      <c r="A57" s="6" t="n"/>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="12" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="n"/>
-      <c r="B58" s="12" t="n"/>
-      <c r="C58" s="12" t="n"/>
-      <c r="D58" s="12" t="n"/>
-      <c r="E58" s="14" t="n"/>
-      <c r="F58" s="12" t="n"/>
-      <c r="G58" s="12" t="n"/>
+      <c r="A58" s="6" t="n"/>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="n"/>
-      <c r="B59" s="12" t="n"/>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="12" t="n"/>
-      <c r="E59" s="14" t="n"/>
-      <c r="F59" s="12" t="n"/>
-      <c r="G59" s="12" t="n"/>
+      <c r="A59" s="6" t="n"/>
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="12" t="n"/>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="n"/>
-      <c r="B60" s="12" t="n"/>
-      <c r="C60" s="12" t="n"/>
-      <c r="D60" s="12" t="n"/>
-      <c r="E60" s="14" t="n"/>
-      <c r="F60" s="12" t="n"/>
-      <c r="G60" s="12" t="n"/>
+      <c r="A60" s="6" t="n"/>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="12" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="n"/>
-      <c r="B61" s="12" t="n"/>
-      <c r="C61" s="12" t="n"/>
-      <c r="D61" s="12" t="n"/>
-      <c r="E61" s="14" t="n"/>
-      <c r="F61" s="12" t="n"/>
-      <c r="G61" s="12" t="n"/>
+      <c r="A61" s="6" t="n"/>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="12" t="n"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="n"/>
-      <c r="B62" s="12" t="n"/>
-      <c r="C62" s="12" t="n"/>
-      <c r="D62" s="12" t="n"/>
-      <c r="E62" s="14" t="n"/>
-      <c r="F62" s="12" t="n"/>
-      <c r="G62" s="12" t="n"/>
+      <c r="A62" s="6" t="n"/>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="12" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="n"/>
-      <c r="B63" s="12" t="n"/>
-      <c r="C63" s="12" t="n"/>
-      <c r="D63" s="12" t="n"/>
-      <c r="E63" s="14" t="n"/>
-      <c r="F63" s="12" t="n"/>
-      <c r="G63" s="12" t="n"/>
+      <c r="A63" s="6" t="n"/>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="12" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="n"/>
-      <c r="B64" s="12" t="n"/>
-      <c r="C64" s="12" t="n"/>
-      <c r="D64" s="12" t="n"/>
-      <c r="E64" s="14" t="n"/>
-      <c r="F64" s="12" t="n"/>
-      <c r="G64" s="12" t="n"/>
+      <c r="A64" s="6" t="n"/>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="12" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="n"/>
-      <c r="B65" s="12" t="n"/>
-      <c r="C65" s="12" t="n"/>
-      <c r="D65" s="12" t="n"/>
-      <c r="E65" s="14" t="n"/>
-      <c r="F65" s="12" t="n"/>
-      <c r="G65" s="12" t="n"/>
+      <c r="A65" s="6" t="n"/>
+      <c r="B65" s="10" t="n"/>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="10" t="n"/>
+      <c r="E65" s="12" t="n"/>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="n"/>
-      <c r="B66" s="12" t="n"/>
-      <c r="C66" s="12" t="n"/>
-      <c r="D66" s="12" t="n"/>
-      <c r="E66" s="14" t="n"/>
-      <c r="F66" s="12" t="n"/>
-      <c r="G66" s="12" t="n"/>
+      <c r="A66" s="6" t="n"/>
+      <c r="B66" s="10" t="n"/>
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="12" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="n"/>
-      <c r="B67" s="12" t="n"/>
-      <c r="C67" s="12" t="n"/>
-      <c r="D67" s="12" t="n"/>
-      <c r="E67" s="14" t="n"/>
-      <c r="F67" s="12" t="n"/>
-      <c r="G67" s="12" t="n"/>
+      <c r="A67" s="6" t="n"/>
+      <c r="B67" s="10" t="n"/>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="12" t="n"/>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="n"/>
-      <c r="B68" s="12" t="n"/>
-      <c r="C68" s="12" t="n"/>
-      <c r="D68" s="12" t="n"/>
-      <c r="E68" s="14" t="n"/>
-      <c r="F68" s="12" t="n"/>
-      <c r="G68" s="12" t="n"/>
+      <c r="A68" s="6" t="n"/>
+      <c r="B68" s="10" t="n"/>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="12" t="n"/>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="n"/>
-      <c r="B69" s="12" t="n"/>
-      <c r="C69" s="12" t="n"/>
-      <c r="D69" s="12" t="n"/>
-      <c r="E69" s="14" t="n"/>
-      <c r="F69" s="12" t="n"/>
-      <c r="G69" s="12" t="n"/>
+      <c r="A69" s="6" t="n"/>
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="12" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="n"/>
-      <c r="B70" s="12" t="n"/>
-      <c r="C70" s="12" t="n"/>
-      <c r="D70" s="12" t="n"/>
-      <c r="E70" s="14" t="n"/>
-      <c r="F70" s="12" t="n"/>
-      <c r="G70" s="12" t="n"/>
+      <c r="A70" s="6" t="n"/>
+      <c r="B70" s="10" t="n"/>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="12" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="n"/>
-      <c r="B71" s="12" t="n"/>
-      <c r="C71" s="12" t="n"/>
-      <c r="D71" s="12" t="n"/>
-      <c r="E71" s="14" t="n"/>
-      <c r="F71" s="12" t="n"/>
-      <c r="G71" s="12" t="n"/>
+      <c r="A71" s="6" t="n"/>
+      <c r="B71" s="10" t="n"/>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="12" t="n"/>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="n"/>
-      <c r="B72" s="12" t="n"/>
-      <c r="C72" s="12" t="n"/>
-      <c r="D72" s="12" t="n"/>
-      <c r="E72" s="14" t="n"/>
-      <c r="F72" s="12" t="n"/>
-      <c r="G72" s="12" t="n"/>
+      <c r="A72" s="6" t="n"/>
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="12" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="n"/>
-      <c r="B73" s="12" t="n"/>
-      <c r="C73" s="12" t="n"/>
-      <c r="D73" s="12" t="n"/>
-      <c r="E73" s="14" t="n"/>
-      <c r="F73" s="12" t="n"/>
-      <c r="G73" s="12" t="n"/>
+      <c r="A73" s="6" t="n"/>
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="10" t="n"/>
+      <c r="E73" s="12" t="n"/>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="n"/>
-      <c r="B74" s="12" t="n"/>
-      <c r="C74" s="12" t="n"/>
-      <c r="D74" s="12" t="n"/>
-      <c r="E74" s="14" t="n"/>
-      <c r="F74" s="12" t="n"/>
-      <c r="G74" s="12" t="n"/>
+      <c r="A74" s="6" t="n"/>
+      <c r="B74" s="10" t="n"/>
+      <c r="C74" s="10" t="n"/>
+      <c r="D74" s="10" t="n"/>
+      <c r="E74" s="12" t="n"/>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="n"/>
-      <c r="B75" s="12" t="n"/>
-      <c r="C75" s="12" t="n"/>
-      <c r="D75" s="12" t="n"/>
-      <c r="E75" s="14" t="n"/>
-      <c r="F75" s="12" t="n"/>
-      <c r="G75" s="12" t="n"/>
+      <c r="A75" s="6" t="n"/>
+      <c r="B75" s="10" t="n"/>
+      <c r="C75" s="10" t="n"/>
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="12" t="n"/>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="n"/>
-      <c r="B76" s="12" t="n"/>
-      <c r="C76" s="12" t="n"/>
-      <c r="D76" s="12" t="n"/>
-      <c r="E76" s="14" t="n"/>
-      <c r="F76" s="12" t="n"/>
-      <c r="G76" s="12" t="n"/>
+      <c r="A76" s="6" t="n"/>
+      <c r="B76" s="10" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="12" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="n"/>
-      <c r="B77" s="12" t="n"/>
-      <c r="C77" s="12" t="n"/>
-      <c r="D77" s="12" t="n"/>
-      <c r="E77" s="14" t="n"/>
-      <c r="F77" s="12" t="n"/>
-      <c r="G77" s="12" t="n"/>
+      <c r="A77" s="6" t="n"/>
+      <c r="B77" s="10" t="n"/>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="10" t="n"/>
+      <c r="E77" s="12" t="n"/>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="n"/>
-      <c r="B78" s="12" t="n"/>
-      <c r="C78" s="12" t="n"/>
-      <c r="D78" s="12" t="n"/>
-      <c r="E78" s="14" t="n"/>
-      <c r="F78" s="12" t="n"/>
-      <c r="G78" s="12" t="n"/>
+      <c r="A78" s="6" t="n"/>
+      <c r="B78" s="10" t="n"/>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="12" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="n"/>
-      <c r="B79" s="12" t="n"/>
-      <c r="C79" s="12" t="n"/>
-      <c r="D79" s="12" t="n"/>
-      <c r="E79" s="14" t="n"/>
-      <c r="F79" s="12" t="n"/>
-      <c r="G79" s="12" t="n"/>
+      <c r="A79" s="6" t="n"/>
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="12" t="n"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="n"/>
-      <c r="B80" s="12" t="n"/>
-      <c r="C80" s="12" t="n"/>
-      <c r="D80" s="12" t="n"/>
-      <c r="E80" s="14" t="n"/>
-      <c r="F80" s="12" t="n"/>
-      <c r="G80" s="12" t="n"/>
+      <c r="A80" s="6" t="n"/>
+      <c r="B80" s="10" t="n"/>
+      <c r="C80" s="10" t="n"/>
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="12" t="n"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="n"/>
-      <c r="B81" s="12" t="n"/>
-      <c r="C81" s="12" t="n"/>
-      <c r="D81" s="12" t="n"/>
-      <c r="E81" s="14" t="n"/>
-      <c r="F81" s="12" t="n"/>
-      <c r="G81" s="12" t="n"/>
+      <c r="A81" s="6" t="n"/>
+      <c r="B81" s="10" t="n"/>
+      <c r="C81" s="10" t="n"/>
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="12" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="n"/>
-      <c r="B82" s="12" t="n"/>
-      <c r="C82" s="12" t="n"/>
-      <c r="D82" s="12" t="n"/>
-      <c r="E82" s="14" t="n"/>
-      <c r="F82" s="12" t="n"/>
-      <c r="G82" s="12" t="n"/>
+      <c r="A82" s="6" t="n"/>
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="10" t="n"/>
+      <c r="E82" s="12" t="n"/>
+      <c r="F82" s="10" t="n"/>
+      <c r="G82" s="10" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="n"/>
-      <c r="B83" s="12" t="n"/>
-      <c r="C83" s="12" t="n"/>
-      <c r="D83" s="12" t="n"/>
-      <c r="E83" s="14" t="n"/>
-      <c r="F83" s="12" t="n"/>
-      <c r="G83" s="12" t="n"/>
+      <c r="A83" s="6" t="n"/>
+      <c r="B83" s="10" t="n"/>
+      <c r="C83" s="10" t="n"/>
+      <c r="D83" s="10" t="n"/>
+      <c r="E83" s="12" t="n"/>
+      <c r="F83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="n"/>
-      <c r="B84" s="12" t="n"/>
-      <c r="C84" s="12" t="n"/>
-      <c r="D84" s="12" t="n"/>
-      <c r="E84" s="14" t="n"/>
-      <c r="F84" s="12" t="n"/>
-      <c r="G84" s="12" t="n"/>
+      <c r="A84" s="6" t="n"/>
+      <c r="B84" s="10" t="n"/>
+      <c r="C84" s="10" t="n"/>
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="12" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="n"/>
-      <c r="B85" s="12" t="n"/>
-      <c r="C85" s="12" t="n"/>
-      <c r="D85" s="12" t="n"/>
-      <c r="E85" s="14" t="n"/>
-      <c r="F85" s="12" t="n"/>
-      <c r="G85" s="12" t="n"/>
+      <c r="A85" s="6" t="n"/>
+      <c r="B85" s="10" t="n"/>
+      <c r="C85" s="10" t="n"/>
+      <c r="D85" s="10" t="n"/>
+      <c r="E85" s="12" t="n"/>
+      <c r="F85" s="10" t="n"/>
+      <c r="G85" s="10" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="n"/>
-      <c r="B86" s="12" t="n"/>
-      <c r="C86" s="12" t="n"/>
-      <c r="D86" s="12" t="n"/>
-      <c r="E86" s="14" t="n"/>
-      <c r="F86" s="12" t="n"/>
-      <c r="G86" s="12" t="n"/>
+      <c r="A86" s="6" t="n"/>
+      <c r="B86" s="10" t="n"/>
+      <c r="C86" s="10" t="n"/>
+      <c r="D86" s="10" t="n"/>
+      <c r="E86" s="12" t="n"/>
+      <c r="F86" s="10" t="n"/>
+      <c r="G86" s="10" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="n"/>
-      <c r="B87" s="12" t="n"/>
-      <c r="C87" s="12" t="n"/>
-      <c r="D87" s="12" t="n"/>
-      <c r="E87" s="14" t="n"/>
-      <c r="F87" s="12" t="n"/>
-      <c r="G87" s="12" t="n"/>
+      <c r="A87" s="6" t="n"/>
+      <c r="B87" s="10" t="n"/>
+      <c r="C87" s="10" t="n"/>
+      <c r="D87" s="10" t="n"/>
+      <c r="E87" s="12" t="n"/>
+      <c r="F87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="n"/>
-      <c r="B88" s="12" t="n"/>
-      <c r="C88" s="12" t="n"/>
-      <c r="D88" s="12" t="n"/>
-      <c r="E88" s="14" t="n"/>
-      <c r="F88" s="12" t="n"/>
-      <c r="G88" s="12" t="n"/>
+      <c r="A88" s="6" t="n"/>
+      <c r="B88" s="10" t="n"/>
+      <c r="C88" s="10" t="n"/>
+      <c r="D88" s="10" t="n"/>
+      <c r="E88" s="12" t="n"/>
+      <c r="F88" s="10" t="n"/>
+      <c r="G88" s="10" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="n"/>
-      <c r="B89" s="12" t="n"/>
-      <c r="C89" s="12" t="n"/>
-      <c r="D89" s="12" t="n"/>
-      <c r="E89" s="14" t="n"/>
-      <c r="F89" s="12" t="n"/>
-      <c r="G89" s="12" t="n"/>
+      <c r="A89" s="6" t="n"/>
+      <c r="B89" s="10" t="n"/>
+      <c r="C89" s="10" t="n"/>
+      <c r="D89" s="10" t="n"/>
+      <c r="E89" s="12" t="n"/>
+      <c r="F89" s="10" t="n"/>
+      <c r="G89" s="10" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="n"/>
-      <c r="B90" s="12" t="n"/>
-      <c r="C90" s="12" t="n"/>
-      <c r="D90" s="12" t="n"/>
-      <c r="E90" s="14" t="n"/>
-      <c r="F90" s="12" t="n"/>
-      <c r="G90" s="12" t="n"/>
+      <c r="A90" s="6" t="n"/>
+      <c r="B90" s="10" t="n"/>
+      <c r="C90" s="10" t="n"/>
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="12" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="n"/>
-      <c r="B91" s="12" t="n"/>
-      <c r="C91" s="12" t="n"/>
-      <c r="D91" s="12" t="n"/>
-      <c r="E91" s="14" t="n"/>
-      <c r="F91" s="12" t="n"/>
-      <c r="G91" s="12" t="n"/>
+      <c r="A91" s="6" t="n"/>
+      <c r="B91" s="10" t="n"/>
+      <c r="C91" s="10" t="n"/>
+      <c r="D91" s="10" t="n"/>
+      <c r="E91" s="12" t="n"/>
+      <c r="F91" s="10" t="n"/>
+      <c r="G91" s="10" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="n"/>
-      <c r="B92" s="12" t="n"/>
-      <c r="C92" s="12" t="n"/>
-      <c r="D92" s="12" t="n"/>
-      <c r="E92" s="14" t="n"/>
-      <c r="F92" s="12" t="n"/>
-      <c r="G92" s="12" t="n"/>
+      <c r="A92" s="6" t="n"/>
+      <c r="B92" s="10" t="n"/>
+      <c r="C92" s="10" t="n"/>
+      <c r="D92" s="10" t="n"/>
+      <c r="E92" s="12" t="n"/>
+      <c r="F92" s="10" t="n"/>
+      <c r="G92" s="10" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="n"/>
-      <c r="B93" s="12" t="n"/>
-      <c r="C93" s="12" t="n"/>
-      <c r="D93" s="12" t="n"/>
-      <c r="E93" s="14" t="n"/>
-      <c r="F93" s="12" t="n"/>
-      <c r="G93" s="12" t="n"/>
+      <c r="A93" s="6" t="n"/>
+      <c r="B93" s="10" t="n"/>
+      <c r="C93" s="10" t="n"/>
+      <c r="D93" s="10" t="n"/>
+      <c r="E93" s="12" t="n"/>
+      <c r="F93" s="10" t="n"/>
+      <c r="G93" s="10" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="n"/>
-      <c r="B94" s="12" t="n"/>
-      <c r="C94" s="12" t="n"/>
-      <c r="D94" s="12" t="n"/>
-      <c r="E94" s="14" t="n"/>
-      <c r="F94" s="12" t="n"/>
-      <c r="G94" s="12" t="n"/>
+      <c r="A94" s="6" t="n"/>
+      <c r="B94" s="10" t="n"/>
+      <c r="C94" s="10" t="n"/>
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="12" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="n"/>
-      <c r="B95" s="12" t="n"/>
-      <c r="C95" s="12" t="n"/>
-      <c r="D95" s="12" t="n"/>
-      <c r="E95" s="14" t="n"/>
-      <c r="F95" s="12" t="n"/>
-      <c r="G95" s="12" t="n"/>
+      <c r="A95" s="6" t="n"/>
+      <c r="B95" s="10" t="n"/>
+      <c r="C95" s="10" t="n"/>
+      <c r="D95" s="10" t="n"/>
+      <c r="E95" s="12" t="n"/>
+      <c r="F95" s="10" t="n"/>
+      <c r="G95" s="10" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="8" t="n"/>
-      <c r="B96" s="12" t="n"/>
-      <c r="C96" s="12" t="n"/>
-      <c r="D96" s="12" t="n"/>
-      <c r="E96" s="14" t="n"/>
-      <c r="F96" s="12" t="n"/>
-      <c r="G96" s="12" t="n"/>
+      <c r="A96" s="6" t="n"/>
+      <c r="B96" s="10" t="n"/>
+      <c r="C96" s="10" t="n"/>
+      <c r="D96" s="10" t="n"/>
+      <c r="E96" s="12" t="n"/>
+      <c r="F96" s="10" t="n"/>
+      <c r="G96" s="10" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="n"/>
-      <c r="B97" s="12" t="n"/>
-      <c r="C97" s="12" t="n"/>
-      <c r="D97" s="12" t="n"/>
-      <c r="E97" s="14" t="n"/>
-      <c r="F97" s="12" t="n"/>
-      <c r="G97" s="12" t="n"/>
+      <c r="A97" s="6" t="n"/>
+      <c r="B97" s="10" t="n"/>
+      <c r="C97" s="10" t="n"/>
+      <c r="D97" s="10" t="n"/>
+      <c r="E97" s="12" t="n"/>
+      <c r="F97" s="10" t="n"/>
+      <c r="G97" s="10" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="n"/>
-      <c r="B98" s="12" t="n"/>
-      <c r="C98" s="12" t="n"/>
-      <c r="D98" s="12" t="n"/>
-      <c r="E98" s="14" t="n"/>
-      <c r="F98" s="12" t="n"/>
-      <c r="G98" s="12" t="n"/>
+      <c r="A98" s="6" t="n"/>
+      <c r="B98" s="10" t="n"/>
+      <c r="C98" s="10" t="n"/>
+      <c r="D98" s="10" t="n"/>
+      <c r="E98" s="12" t="n"/>
+      <c r="F98" s="10" t="n"/>
+      <c r="G98" s="10" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="n"/>
-      <c r="B99" s="12" t="n"/>
-      <c r="C99" s="12" t="n"/>
-      <c r="D99" s="12" t="n"/>
-      <c r="E99" s="14" t="n"/>
-      <c r="F99" s="12" t="n"/>
-      <c r="G99" s="12" t="n"/>
+      <c r="A99" s="6" t="n"/>
+      <c r="B99" s="10" t="n"/>
+      <c r="C99" s="10" t="n"/>
+      <c r="D99" s="10" t="n"/>
+      <c r="E99" s="12" t="n"/>
+      <c r="F99" s="10" t="n"/>
+      <c r="G99" s="10" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="n"/>
-      <c r="B100" s="12" t="n"/>
-      <c r="C100" s="12" t="n"/>
-      <c r="D100" s="12" t="n"/>
-      <c r="E100" s="14" t="n"/>
-      <c r="F100" s="12" t="n"/>
-      <c r="G100" s="12" t="n"/>
+      <c r="A100" s="6" t="n"/>
+      <c r="B100" s="10" t="n"/>
+      <c r="C100" s="10" t="n"/>
+      <c r="D100" s="10" t="n"/>
+      <c r="E100" s="12" t="n"/>
+      <c r="F100" s="10" t="n"/>
+      <c r="G100" s="10" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="n"/>
-      <c r="B101" s="12" t="n"/>
-      <c r="C101" s="12" t="n"/>
-      <c r="D101" s="12" t="n"/>
-      <c r="E101" s="14" t="n"/>
-      <c r="F101" s="12" t="n"/>
-      <c r="G101" s="12" t="n"/>
+      <c r="A101" s="6" t="n"/>
+      <c r="B101" s="10" t="n"/>
+      <c r="C101" s="10" t="n"/>
+      <c r="D101" s="10" t="n"/>
+      <c r="E101" s="12" t="n"/>
+      <c r="F101" s="10" t="n"/>
+      <c r="G101" s="10" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="n"/>
-      <c r="B102" s="12" t="n"/>
-      <c r="C102" s="12" t="n"/>
-      <c r="D102" s="12" t="n"/>
-      <c r="E102" s="14" t="n"/>
-      <c r="F102" s="12" t="n"/>
-      <c r="G102" s="12" t="n"/>
+      <c r="A102" s="6" t="n"/>
+      <c r="B102" s="10" t="n"/>
+      <c r="C102" s="10" t="n"/>
+      <c r="D102" s="10" t="n"/>
+      <c r="E102" s="12" t="n"/>
+      <c r="F102" s="10" t="n"/>
+      <c r="G102" s="10" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="8" t="n"/>
-      <c r="B103" s="12" t="n"/>
-      <c r="C103" s="12" t="n"/>
-      <c r="D103" s="12" t="n"/>
-      <c r="E103" s="14" t="n"/>
-      <c r="F103" s="12" t="n"/>
-      <c r="G103" s="12" t="n"/>
+      <c r="A103" s="6" t="n"/>
+      <c r="B103" s="10" t="n"/>
+      <c r="C103" s="10" t="n"/>
+      <c r="D103" s="10" t="n"/>
+      <c r="E103" s="12" t="n"/>
+      <c r="F103" s="10" t="n"/>
+      <c r="G103" s="10" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="n"/>
-      <c r="B104" s="12" t="n"/>
-      <c r="C104" s="12" t="n"/>
-      <c r="D104" s="12" t="n"/>
-      <c r="E104" s="14" t="n"/>
-      <c r="F104" s="12" t="n"/>
-      <c r="G104" s="12" t="n"/>
+      <c r="A104" s="6" t="n"/>
+      <c r="B104" s="10" t="n"/>
+      <c r="C104" s="10" t="n"/>
+      <c r="D104" s="10" t="n"/>
+      <c r="E104" s="12" t="n"/>
+      <c r="F104" s="10" t="n"/>
+      <c r="G104" s="10" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="8" t="n"/>
-      <c r="B105" s="12" t="n"/>
-      <c r="C105" s="12" t="n"/>
-      <c r="D105" s="12" t="n"/>
-      <c r="E105" s="14" t="n"/>
-      <c r="F105" s="12" t="n"/>
-      <c r="G105" s="12" t="n"/>
+      <c r="A105" s="6" t="n"/>
+      <c r="B105" s="10" t="n"/>
+      <c r="C105" s="10" t="n"/>
+      <c r="D105" s="10" t="n"/>
+      <c r="E105" s="12" t="n"/>
+      <c r="F105" s="10" t="n"/>
+      <c r="G105" s="10" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="n"/>
-      <c r="B106" s="12" t="n"/>
-      <c r="C106" s="12" t="n"/>
-      <c r="D106" s="12" t="n"/>
-      <c r="E106" s="14" t="n"/>
-      <c r="F106" s="12" t="n"/>
-      <c r="G106" s="12" t="n"/>
+      <c r="A106" s="6" t="n"/>
+      <c r="B106" s="10" t="n"/>
+      <c r="C106" s="10" t="n"/>
+      <c r="D106" s="10" t="n"/>
+      <c r="E106" s="12" t="n"/>
+      <c r="F106" s="10" t="n"/>
+      <c r="G106" s="10" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="8" t="n"/>
-      <c r="B107" s="12" t="n"/>
-      <c r="C107" s="12" t="n"/>
-      <c r="D107" s="12" t="n"/>
-      <c r="E107" s="14" t="n"/>
-      <c r="F107" s="12" t="n"/>
-      <c r="G107" s="12" t="n"/>
+      <c r="A107" s="6" t="n"/>
+      <c r="B107" s="10" t="n"/>
+      <c r="C107" s="10" t="n"/>
+      <c r="D107" s="10" t="n"/>
+      <c r="E107" s="12" t="n"/>
+      <c r="F107" s="10" t="n"/>
+      <c r="G107" s="10" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="n"/>
-      <c r="B108" s="12" t="n"/>
-      <c r="C108" s="12" t="n"/>
-      <c r="D108" s="12" t="n"/>
-      <c r="E108" s="14" t="n"/>
-      <c r="F108" s="12" t="n"/>
-      <c r="G108" s="12" t="n"/>
+      <c r="A108" s="6" t="n"/>
+      <c r="B108" s="10" t="n"/>
+      <c r="C108" s="10" t="n"/>
+      <c r="D108" s="10" t="n"/>
+      <c r="E108" s="12" t="n"/>
+      <c r="F108" s="10" t="n"/>
+      <c r="G108" s="10" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="n"/>
-      <c r="B109" s="12" t="n"/>
-      <c r="C109" s="12" t="n"/>
-      <c r="D109" s="12" t="n"/>
-      <c r="E109" s="14" t="n"/>
-      <c r="F109" s="12" t="n"/>
-      <c r="G109" s="12" t="n"/>
+      <c r="A109" s="6" t="n"/>
+      <c r="B109" s="10" t="n"/>
+      <c r="C109" s="10" t="n"/>
+      <c r="D109" s="10" t="n"/>
+      <c r="E109" s="12" t="n"/>
+      <c r="F109" s="10" t="n"/>
+      <c r="G109" s="10" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="n"/>
-      <c r="B110" s="12" t="n"/>
-      <c r="C110" s="12" t="n"/>
-      <c r="D110" s="12" t="n"/>
-      <c r="E110" s="14" t="n"/>
-      <c r="F110" s="12" t="n"/>
-      <c r="G110" s="12" t="n"/>
+      <c r="A110" s="6" t="n"/>
+      <c r="B110" s="10" t="n"/>
+      <c r="C110" s="10" t="n"/>
+      <c r="D110" s="10" t="n"/>
+      <c r="E110" s="12" t="n"/>
+      <c r="F110" s="10" t="n"/>
+      <c r="G110" s="10" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="8" t="n"/>
-      <c r="B111" s="12" t="n"/>
-      <c r="C111" s="12" t="n"/>
-      <c r="D111" s="12" t="n"/>
-      <c r="E111" s="14" t="n"/>
-      <c r="F111" s="12" t="n"/>
-      <c r="G111" s="12" t="n"/>
+      <c r="A111" s="6" t="n"/>
+      <c r="B111" s="10" t="n"/>
+      <c r="C111" s="10" t="n"/>
+      <c r="D111" s="10" t="n"/>
+      <c r="E111" s="12" t="n"/>
+      <c r="F111" s="10" t="n"/>
+      <c r="G111" s="10" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="n"/>
-      <c r="B112" s="12" t="n"/>
-      <c r="C112" s="12" t="n"/>
-      <c r="D112" s="12" t="n"/>
-      <c r="E112" s="14" t="n"/>
-      <c r="F112" s="12" t="n"/>
-      <c r="G112" s="12" t="n"/>
+      <c r="A112" s="6" t="n"/>
+      <c r="B112" s="10" t="n"/>
+      <c r="C112" s="10" t="n"/>
+      <c r="D112" s="10" t="n"/>
+      <c r="E112" s="12" t="n"/>
+      <c r="F112" s="10" t="n"/>
+      <c r="G112" s="10" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="8" t="n"/>
-      <c r="B113" s="12" t="n"/>
-      <c r="C113" s="12" t="n"/>
-      <c r="D113" s="12" t="n"/>
-      <c r="E113" s="14" t="n"/>
-      <c r="F113" s="12" t="n"/>
-      <c r="G113" s="12" t="n"/>
+      <c r="A113" s="6" t="n"/>
+      <c r="B113" s="10" t="n"/>
+      <c r="C113" s="10" t="n"/>
+      <c r="D113" s="10" t="n"/>
+      <c r="E113" s="12" t="n"/>
+      <c r="F113" s="10" t="n"/>
+      <c r="G113" s="10" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="8" t="n"/>
-      <c r="B114" s="12" t="n"/>
-      <c r="C114" s="12" t="n"/>
-      <c r="D114" s="12" t="n"/>
-      <c r="E114" s="14" t="n"/>
-      <c r="F114" s="12" t="n"/>
-      <c r="G114" s="12" t="n"/>
+      <c r="A114" s="6" t="n"/>
+      <c r="B114" s="10" t="n"/>
+      <c r="C114" s="10" t="n"/>
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="12" t="n"/>
+      <c r="F114" s="10" t="n"/>
+      <c r="G114" s="10" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="n"/>
-      <c r="B115" s="12" t="n"/>
-      <c r="C115" s="12" t="n"/>
-      <c r="D115" s="12" t="n"/>
-      <c r="E115" s="14" t="n"/>
-      <c r="F115" s="12" t="n"/>
-      <c r="G115" s="12" t="n"/>
+      <c r="A115" s="6" t="n"/>
+      <c r="B115" s="10" t="n"/>
+      <c r="C115" s="10" t="n"/>
+      <c r="D115" s="10" t="n"/>
+      <c r="E115" s="12" t="n"/>
+      <c r="F115" s="10" t="n"/>
+      <c r="G115" s="10" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="n"/>
-      <c r="B116" s="12" t="n"/>
-      <c r="C116" s="12" t="n"/>
-      <c r="D116" s="12" t="n"/>
-      <c r="E116" s="14" t="n"/>
-      <c r="F116" s="12" t="n"/>
-      <c r="G116" s="12" t="n"/>
+      <c r="A116" s="6" t="n"/>
+      <c r="B116" s="10" t="n"/>
+      <c r="C116" s="10" t="n"/>
+      <c r="D116" s="10" t="n"/>
+      <c r="E116" s="12" t="n"/>
+      <c r="F116" s="10" t="n"/>
+      <c r="G116" s="10" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="8" t="n"/>
-      <c r="B117" s="12" t="n"/>
-      <c r="C117" s="12" t="n"/>
-      <c r="D117" s="12" t="n"/>
-      <c r="E117" s="14" t="n"/>
-      <c r="F117" s="12" t="n"/>
-      <c r="G117" s="12" t="n"/>
+      <c r="A117" s="6" t="n"/>
+      <c r="B117" s="10" t="n"/>
+      <c r="C117" s="10" t="n"/>
+      <c r="D117" s="10" t="n"/>
+      <c r="E117" s="12" t="n"/>
+      <c r="F117" s="10" t="n"/>
+      <c r="G117" s="10" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="8" t="n"/>
-      <c r="B118" s="12" t="n"/>
-      <c r="C118" s="12" t="n"/>
-      <c r="D118" s="12" t="n"/>
-      <c r="E118" s="14" t="n"/>
-      <c r="F118" s="12" t="n"/>
-      <c r="G118" s="12" t="n"/>
+      <c r="A118" s="6" t="n"/>
+      <c r="B118" s="10" t="n"/>
+      <c r="C118" s="10" t="n"/>
+      <c r="D118" s="10" t="n"/>
+      <c r="E118" s="12" t="n"/>
+      <c r="F118" s="10" t="n"/>
+      <c r="G118" s="10" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="8" t="n"/>
-      <c r="B119" s="12" t="n"/>
-      <c r="C119" s="12" t="n"/>
-      <c r="D119" s="12" t="n"/>
-      <c r="E119" s="14" t="n"/>
-      <c r="F119" s="12" t="n"/>
-      <c r="G119" s="12" t="n"/>
+      <c r="A119" s="6" t="n"/>
+      <c r="B119" s="10" t="n"/>
+      <c r="C119" s="10" t="n"/>
+      <c r="D119" s="10" t="n"/>
+      <c r="E119" s="12" t="n"/>
+      <c r="F119" s="10" t="n"/>
+      <c r="G119" s="10" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="8" t="n"/>
-      <c r="B120" s="12" t="n"/>
-      <c r="C120" s="12" t="n"/>
-      <c r="D120" s="12" t="n"/>
-      <c r="E120" s="14" t="n"/>
-      <c r="F120" s="12" t="n"/>
-      <c r="G120" s="12" t="n"/>
+      <c r="A120" s="6" t="n"/>
+      <c r="B120" s="10" t="n"/>
+      <c r="C120" s="10" t="n"/>
+      <c r="D120" s="10" t="n"/>
+      <c r="E120" s="12" t="n"/>
+      <c r="F120" s="10" t="n"/>
+      <c r="G120" s="10" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="8" t="n"/>
-      <c r="B121" s="12" t="n"/>
-      <c r="C121" s="12" t="n"/>
-      <c r="D121" s="12" t="n"/>
-      <c r="E121" s="14" t="n"/>
-      <c r="F121" s="12" t="n"/>
-      <c r="G121" s="12" t="n"/>
+      <c r="A121" s="6" t="n"/>
+      <c r="B121" s="10" t="n"/>
+      <c r="C121" s="10" t="n"/>
+      <c r="D121" s="10" t="n"/>
+      <c r="E121" s="12" t="n"/>
+      <c r="F121" s="10" t="n"/>
+      <c r="G121" s="10" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="8" t="n"/>
-      <c r="B122" s="12" t="n"/>
-      <c r="C122" s="12" t="n"/>
-      <c r="D122" s="12" t="n"/>
-      <c r="E122" s="14" t="n"/>
-      <c r="F122" s="12" t="n"/>
-      <c r="G122" s="12" t="n"/>
+      <c r="A122" s="6" t="n"/>
+      <c r="B122" s="10" t="n"/>
+      <c r="C122" s="10" t="n"/>
+      <c r="D122" s="10" t="n"/>
+      <c r="E122" s="12" t="n"/>
+      <c r="F122" s="10" t="n"/>
+      <c r="G122" s="10" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="8" t="n"/>
-      <c r="B123" s="12" t="n"/>
-      <c r="C123" s="12" t="n"/>
-      <c r="D123" s="12" t="n"/>
-      <c r="E123" s="14" t="n"/>
-      <c r="F123" s="12" t="n"/>
-      <c r="G123" s="12" t="n"/>
+      <c r="A123" s="6" t="n"/>
+      <c r="B123" s="10" t="n"/>
+      <c r="C123" s="10" t="n"/>
+      <c r="D123" s="10" t="n"/>
+      <c r="E123" s="12" t="n"/>
+      <c r="F123" s="10" t="n"/>
+      <c r="G123" s="10" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="8" t="n"/>
-      <c r="B124" s="12" t="n"/>
-      <c r="C124" s="12" t="n"/>
-      <c r="D124" s="12" t="n"/>
-      <c r="E124" s="14" t="n"/>
-      <c r="F124" s="12" t="n"/>
-      <c r="G124" s="12" t="n"/>
+      <c r="A124" s="6" t="n"/>
+      <c r="B124" s="10" t="n"/>
+      <c r="C124" s="10" t="n"/>
+      <c r="D124" s="10" t="n"/>
+      <c r="E124" s="12" t="n"/>
+      <c r="F124" s="10" t="n"/>
+      <c r="G124" s="10" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="8" t="n"/>
-      <c r="B125" s="12" t="n"/>
-      <c r="C125" s="12" t="n"/>
-      <c r="D125" s="12" t="n"/>
-      <c r="E125" s="14" t="n"/>
-      <c r="F125" s="12" t="n"/>
-      <c r="G125" s="12" t="n"/>
+      <c r="A125" s="6" t="n"/>
+      <c r="B125" s="10" t="n"/>
+      <c r="C125" s="10" t="n"/>
+      <c r="D125" s="10" t="n"/>
+      <c r="E125" s="12" t="n"/>
+      <c r="F125" s="10" t="n"/>
+      <c r="G125" s="10" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="8" t="n"/>
-      <c r="B126" s="12" t="n"/>
-      <c r="C126" s="12" t="n"/>
-      <c r="D126" s="12" t="n"/>
-      <c r="E126" s="14" t="n"/>
-      <c r="F126" s="12" t="n"/>
-      <c r="G126" s="12" t="n"/>
+      <c r="A126" s="6" t="n"/>
+      <c r="B126" s="10" t="n"/>
+      <c r="C126" s="10" t="n"/>
+      <c r="D126" s="10" t="n"/>
+      <c r="E126" s="12" t="n"/>
+      <c r="F126" s="10" t="n"/>
+      <c r="G126" s="10" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="8" t="n"/>
-      <c r="B127" s="12" t="n"/>
-      <c r="C127" s="12" t="n"/>
-      <c r="D127" s="12" t="n"/>
-      <c r="E127" s="14" t="n"/>
-      <c r="F127" s="12" t="n"/>
-      <c r="G127" s="12" t="n"/>
+      <c r="A127" s="6" t="n"/>
+      <c r="B127" s="10" t="n"/>
+      <c r="C127" s="10" t="n"/>
+      <c r="D127" s="10" t="n"/>
+      <c r="E127" s="12" t="n"/>
+      <c r="F127" s="10" t="n"/>
+      <c r="G127" s="10" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="8" t="n"/>
-      <c r="B128" s="12" t="n"/>
-      <c r="C128" s="12" t="n"/>
-      <c r="D128" s="12" t="n"/>
-      <c r="E128" s="14" t="n"/>
-      <c r="F128" s="12" t="n"/>
-      <c r="G128" s="12" t="n"/>
+      <c r="A128" s="6" t="n"/>
+      <c r="B128" s="10" t="n"/>
+      <c r="C128" s="10" t="n"/>
+      <c r="D128" s="10" t="n"/>
+      <c r="E128" s="12" t="n"/>
+      <c r="F128" s="10" t="n"/>
+      <c r="G128" s="10" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="8" t="n"/>
-      <c r="B129" s="12" t="n"/>
-      <c r="C129" s="12" t="n"/>
-      <c r="D129" s="12" t="n"/>
-      <c r="E129" s="14" t="n"/>
-      <c r="F129" s="12" t="n"/>
-      <c r="G129" s="12" t="n"/>
+      <c r="A129" s="6" t="n"/>
+      <c r="B129" s="10" t="n"/>
+      <c r="C129" s="10" t="n"/>
+      <c r="D129" s="10" t="n"/>
+      <c r="E129" s="12" t="n"/>
+      <c r="F129" s="10" t="n"/>
+      <c r="G129" s="10" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="8" t="n"/>
-      <c r="B130" s="12" t="n"/>
-      <c r="C130" s="12" t="n"/>
-      <c r="D130" s="12" t="n"/>
-      <c r="E130" s="14" t="n"/>
-      <c r="F130" s="12" t="n"/>
-      <c r="G130" s="12" t="n"/>
+      <c r="A130" s="6" t="n"/>
+      <c r="B130" s="10" t="n"/>
+      <c r="C130" s="10" t="n"/>
+      <c r="D130" s="10" t="n"/>
+      <c r="E130" s="12" t="n"/>
+      <c r="F130" s="10" t="n"/>
+      <c r="G130" s="10" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="8" t="n"/>
-      <c r="B131" s="12" t="n"/>
-      <c r="C131" s="12" t="n"/>
-      <c r="D131" s="12" t="n"/>
-      <c r="E131" s="14" t="n"/>
-      <c r="F131" s="12" t="n"/>
-      <c r="G131" s="12" t="n"/>
+      <c r="A131" s="6" t="n"/>
+      <c r="B131" s="10" t="n"/>
+      <c r="C131" s="10" t="n"/>
+      <c r="D131" s="10" t="n"/>
+      <c r="E131" s="12" t="n"/>
+      <c r="F131" s="10" t="n"/>
+      <c r="G131" s="10" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="8" t="n"/>
-      <c r="B132" s="12" t="n"/>
-      <c r="C132" s="12" t="n"/>
-      <c r="D132" s="12" t="n"/>
-      <c r="E132" s="14" t="n"/>
-      <c r="F132" s="12" t="n"/>
-      <c r="G132" s="12" t="n"/>
+      <c r="A132" s="6" t="n"/>
+      <c r="B132" s="10" t="n"/>
+      <c r="C132" s="10" t="n"/>
+      <c r="D132" s="10" t="n"/>
+      <c r="E132" s="12" t="n"/>
+      <c r="F132" s="10" t="n"/>
+      <c r="G132" s="10" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="8" t="n"/>
-      <c r="B133" s="12" t="n"/>
-      <c r="C133" s="12" t="n"/>
-      <c r="D133" s="12" t="n"/>
-      <c r="E133" s="14" t="n"/>
-      <c r="F133" s="12" t="n"/>
-      <c r="G133" s="12" t="n"/>
+      <c r="A133" s="6" t="n"/>
+      <c r="B133" s="10" t="n"/>
+      <c r="C133" s="10" t="n"/>
+      <c r="D133" s="10" t="n"/>
+      <c r="E133" s="12" t="n"/>
+      <c r="F133" s="10" t="n"/>
+      <c r="G133" s="10" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="8" t="n"/>
-      <c r="B134" s="12" t="n"/>
-      <c r="C134" s="12" t="n"/>
-      <c r="D134" s="12" t="n"/>
-      <c r="E134" s="14" t="n"/>
-      <c r="F134" s="12" t="n"/>
-      <c r="G134" s="12" t="n"/>
+      <c r="A134" s="6" t="n"/>
+      <c r="B134" s="10" t="n"/>
+      <c r="C134" s="10" t="n"/>
+      <c r="D134" s="10" t="n"/>
+      <c r="E134" s="12" t="n"/>
+      <c r="F134" s="10" t="n"/>
+      <c r="G134" s="10" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="8" t="n"/>
-      <c r="B135" s="12" t="n"/>
-      <c r="C135" s="12" t="n"/>
-      <c r="D135" s="12" t="n"/>
-      <c r="E135" s="14" t="n"/>
-      <c r="F135" s="12" t="n"/>
-      <c r="G135" s="12" t="n"/>
+      <c r="A135" s="6" t="n"/>
+      <c r="B135" s="10" t="n"/>
+      <c r="C135" s="10" t="n"/>
+      <c r="D135" s="10" t="n"/>
+      <c r="E135" s="12" t="n"/>
+      <c r="F135" s="10" t="n"/>
+      <c r="G135" s="10" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="8" t="n"/>
-      <c r="B136" s="12" t="n"/>
-      <c r="C136" s="12" t="n"/>
-      <c r="D136" s="12" t="n"/>
-      <c r="E136" s="14" t="n"/>
-      <c r="F136" s="12" t="n"/>
-      <c r="G136" s="12" t="n"/>
+      <c r="A136" s="6" t="n"/>
+      <c r="B136" s="10" t="n"/>
+      <c r="C136" s="10" t="n"/>
+      <c r="D136" s="10" t="n"/>
+      <c r="E136" s="12" t="n"/>
+      <c r="F136" s="10" t="n"/>
+      <c r="G136" s="10" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="8" t="n"/>
-      <c r="B137" s="12" t="n"/>
-      <c r="C137" s="12" t="n"/>
-      <c r="D137" s="12" t="n"/>
-      <c r="E137" s="14" t="n"/>
-      <c r="F137" s="12" t="n"/>
-      <c r="G137" s="12" t="n"/>
+      <c r="A137" s="6" t="n"/>
+      <c r="B137" s="10" t="n"/>
+      <c r="C137" s="10" t="n"/>
+      <c r="D137" s="10" t="n"/>
+      <c r="E137" s="12" t="n"/>
+      <c r="F137" s="10" t="n"/>
+      <c r="G137" s="10" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="8" t="n"/>
-      <c r="B138" s="12" t="n"/>
-      <c r="C138" s="12" t="n"/>
-      <c r="D138" s="12" t="n"/>
-      <c r="E138" s="14" t="n"/>
-      <c r="F138" s="12" t="n"/>
-      <c r="G138" s="12" t="n"/>
+      <c r="A138" s="6" t="n"/>
+      <c r="B138" s="10" t="n"/>
+      <c r="C138" s="10" t="n"/>
+      <c r="D138" s="10" t="n"/>
+      <c r="E138" s="12" t="n"/>
+      <c r="F138" s="10" t="n"/>
+      <c r="G138" s="10" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="8" t="n"/>
-      <c r="B139" s="12" t="n"/>
-      <c r="C139" s="12" t="n"/>
-      <c r="D139" s="12" t="n"/>
-      <c r="E139" s="14" t="n"/>
-      <c r="F139" s="12" t="n"/>
-      <c r="G139" s="12" t="n"/>
+      <c r="A139" s="6" t="n"/>
+      <c r="B139" s="10" t="n"/>
+      <c r="C139" s="10" t="n"/>
+      <c r="D139" s="10" t="n"/>
+      <c r="E139" s="12" t="n"/>
+      <c r="F139" s="10" t="n"/>
+      <c r="G139" s="10" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="8" t="n"/>
-      <c r="B140" s="12" t="n"/>
-      <c r="C140" s="12" t="n"/>
-      <c r="D140" s="12" t="n"/>
-      <c r="E140" s="14" t="n"/>
-      <c r="F140" s="12" t="n"/>
-      <c r="G140" s="12" t="n"/>
+      <c r="A140" s="6" t="n"/>
+      <c r="B140" s="10" t="n"/>
+      <c r="C140" s="10" t="n"/>
+      <c r="D140" s="10" t="n"/>
+      <c r="E140" s="12" t="n"/>
+      <c r="F140" s="10" t="n"/>
+      <c r="G140" s="10" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="8" t="n"/>
-      <c r="B141" s="12" t="n"/>
-      <c r="C141" s="12" t="n"/>
-      <c r="D141" s="12" t="n"/>
-      <c r="E141" s="14" t="n"/>
-      <c r="F141" s="12" t="n"/>
-      <c r="G141" s="12" t="n"/>
+      <c r="A141" s="6" t="n"/>
+      <c r="B141" s="10" t="n"/>
+      <c r="C141" s="10" t="n"/>
+      <c r="D141" s="10" t="n"/>
+      <c r="E141" s="12" t="n"/>
+      <c r="F141" s="10" t="n"/>
+      <c r="G141" s="10" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="8" t="n"/>
-      <c r="B142" s="12" t="n"/>
-      <c r="C142" s="12" t="n"/>
-      <c r="D142" s="12" t="n"/>
-      <c r="E142" s="14" t="n"/>
-      <c r="F142" s="12" t="n"/>
-      <c r="G142" s="12" t="n"/>
+      <c r="A142" s="6" t="n"/>
+      <c r="B142" s="10" t="n"/>
+      <c r="C142" s="10" t="n"/>
+      <c r="D142" s="10" t="n"/>
+      <c r="E142" s="12" t="n"/>
+      <c r="F142" s="10" t="n"/>
+      <c r="G142" s="10" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="8" t="n"/>
-      <c r="B143" s="12" t="n"/>
-      <c r="C143" s="12" t="n"/>
-      <c r="D143" s="12" t="n"/>
-      <c r="E143" s="14" t="n"/>
-      <c r="F143" s="12" t="n"/>
-      <c r="G143" s="12" t="n"/>
+      <c r="A143" s="6" t="n"/>
+      <c r="B143" s="10" t="n"/>
+      <c r="C143" s="10" t="n"/>
+      <c r="D143" s="10" t="n"/>
+      <c r="E143" s="12" t="n"/>
+      <c r="F143" s="10" t="n"/>
+      <c r="G143" s="10" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="8" t="n"/>
-      <c r="B144" s="12" t="n"/>
-      <c r="C144" s="12" t="n"/>
-      <c r="D144" s="12" t="n"/>
-      <c r="E144" s="14" t="n"/>
-      <c r="F144" s="12" t="n"/>
-      <c r="G144" s="12" t="n"/>
+      <c r="A144" s="6" t="n"/>
+      <c r="B144" s="10" t="n"/>
+      <c r="C144" s="10" t="n"/>
+      <c r="D144" s="10" t="n"/>
+      <c r="E144" s="12" t="n"/>
+      <c r="F144" s="10" t="n"/>
+      <c r="G144" s="10" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="8" t="n"/>
-      <c r="B145" s="12" t="n"/>
-      <c r="C145" s="12" t="n"/>
-      <c r="D145" s="12" t="n"/>
-      <c r="E145" s="14" t="n"/>
-      <c r="F145" s="12" t="n"/>
-      <c r="G145" s="12" t="n"/>
+      <c r="A145" s="6" t="n"/>
+      <c r="B145" s="10" t="n"/>
+      <c r="C145" s="10" t="n"/>
+      <c r="D145" s="10" t="n"/>
+      <c r="E145" s="12" t="n"/>
+      <c r="F145" s="10" t="n"/>
+      <c r="G145" s="10" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="8" t="n"/>
-      <c r="B146" s="12" t="n"/>
-      <c r="C146" s="12" t="n"/>
-      <c r="D146" s="12" t="n"/>
-      <c r="E146" s="14" t="n"/>
-      <c r="F146" s="12" t="n"/>
-      <c r="G146" s="12" t="n"/>
+      <c r="A146" s="6" t="n"/>
+      <c r="B146" s="10" t="n"/>
+      <c r="C146" s="10" t="n"/>
+      <c r="D146" s="10" t="n"/>
+      <c r="E146" s="12" t="n"/>
+      <c r="F146" s="10" t="n"/>
+      <c r="G146" s="10" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="8" t="n"/>
-      <c r="B147" s="12" t="n"/>
-      <c r="C147" s="12" t="n"/>
-      <c r="D147" s="12" t="n"/>
-      <c r="E147" s="14" t="n"/>
-      <c r="F147" s="12" t="n"/>
-      <c r="G147" s="12" t="n"/>
+      <c r="A147" s="6" t="n"/>
+      <c r="B147" s="10" t="n"/>
+      <c r="C147" s="10" t="n"/>
+      <c r="D147" s="10" t="n"/>
+      <c r="E147" s="12" t="n"/>
+      <c r="F147" s="10" t="n"/>
+      <c r="G147" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -2847,6 +2739,586 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E5395"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PROJECT ESTIMATES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>4 Indian Brook Road, Ashland, MA 01721</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Total estimated — all</t>
+        </is>
+      </c>
+      <c r="B4" s="12">
+        <f>SUM(E9:E58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Total estimated — marked Now</t>
+        </is>
+      </c>
+      <c r="B5" s="12">
+        <f>SUMIF(F9:F58,"Now",E9:E58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>QUOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Contractor / vendor</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Quote date</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Est. cost</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>HVAC system</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Carpentry work</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Carpentry</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="10" t="n"/>
+      <c r="G37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="n"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="12" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="n"/>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="10" t="n"/>
+      <c r="G45" s="10" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="n"/>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="n"/>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="n"/>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="n"/>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="n"/>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="n"/>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="n"/>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="12" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="n"/>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="12" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="n"/>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="12" t="n"/>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="n"/>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="12" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="n"/>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="12" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="n"/>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A7:G7"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Now,Later,Undecided,Passed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2877,1509 +3349,1509 @@
       <c r="A2" s="2" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>PROJECT INFO</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Contractor / quote</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr"/>
+      <c r="B6" s="17" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Materials source</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr"/>
+      <c r="B7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Selected option</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n"/>
+      <c r="B8" s="18" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Contingency %</t>
         </is>
       </c>
-      <c r="B9" s="21" t="n">
+      <c r="B9" s="19" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr"/>
+      <c r="B10" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>OPTION COMPARISON</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Cost component</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>Option A</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>Option B</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>Option C</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Item # / SKU</t>
         </is>
       </c>
-      <c r="B14" s="25" t="n"/>
-      <c r="C14" s="25" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="12" t="n"/>
+      <c r="B14" s="23" t="n"/>
+      <c r="C14" s="23" t="n"/>
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Unit price</t>
         </is>
       </c>
-      <c r="B15" s="27" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="12" t="n"/>
+      <c r="B15" s="25" t="n"/>
+      <c r="C15" s="25" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="B16" s="28" t="n"/>
-      <c r="C16" s="28" t="n"/>
-      <c r="D16" s="28" t="n"/>
-      <c r="E16" s="12" t="n"/>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="26" t="n"/>
+      <c r="E16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>Flooring material</t>
         </is>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="25">
         <f>B15*B16</f>
         <v/>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="25">
         <f>C15*C16</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="25">
         <f>D15*D16</f>
         <v/>
       </c>
-      <c r="E17" s="12" t="n"/>
+      <c r="E17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Underlayment &amp; supplies</t>
         </is>
       </c>
-      <c r="B18" s="27" t="inlineStr"/>
-      <c r="C18" s="27" t="inlineStr"/>
-      <c r="D18" s="27" t="inlineStr"/>
-      <c r="E18" s="12" t="n"/>
+      <c r="B18" s="25" t="inlineStr"/>
+      <c r="C18" s="25" t="inlineStr"/>
+      <c r="D18" s="25" t="inlineStr"/>
+      <c r="E18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>Stair nose trim</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr"/>
-      <c r="C19" s="27" t="inlineStr"/>
-      <c r="D19" s="27" t="inlineStr"/>
-      <c r="E19" s="12" t="n"/>
+      <c r="B19" s="25" t="inlineStr"/>
+      <c r="C19" s="25" t="inlineStr"/>
+      <c r="D19" s="25" t="inlineStr"/>
+      <c r="E19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>Stair risers</t>
         </is>
       </c>
-      <c r="B20" s="27" t="inlineStr"/>
-      <c r="C20" s="27" t="inlineStr"/>
-      <c r="D20" s="27" t="inlineStr"/>
-      <c r="E20" s="12" t="n"/>
+      <c r="B20" s="25" t="inlineStr"/>
+      <c r="C20" s="25" t="inlineStr"/>
+      <c r="D20" s="25" t="inlineStr"/>
+      <c r="E20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>Contractor discount on materials (0%)</t>
         </is>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="25">
         <f>-0.0*SUM(B17:B20)</f>
         <v/>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="25">
         <f>-0.0*SUM(C17:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="25">
         <f>-0.0*SUM(D17:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="12" t="n"/>
+      <c r="E21" s="10" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>Est. sales tax (6.25% MA, materials)</t>
         </is>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="25">
         <f>SUM(B17:B21)*0.0625</f>
         <v/>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="25">
         <f>SUM(C17:C21)*0.0625</f>
         <v/>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="25">
         <f>SUM(D17:D21)*0.0625</f>
         <v/>
       </c>
-      <c r="E22" s="12" t="n"/>
+      <c r="E22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>Labor — demo &amp; disposal</t>
         </is>
       </c>
-      <c r="B23" s="27" t="inlineStr"/>
-      <c r="C23" s="27" t="inlineStr"/>
-      <c r="D23" s="27" t="inlineStr"/>
-      <c r="E23" s="12" t="n"/>
+      <c r="B23" s="25" t="inlineStr"/>
+      <c r="C23" s="25" t="inlineStr"/>
+      <c r="D23" s="25" t="inlineStr"/>
+      <c r="E23" s="10" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>Labor — install</t>
         </is>
       </c>
-      <c r="B24" s="27" t="inlineStr"/>
-      <c r="C24" s="27" t="inlineStr"/>
-      <c r="D24" s="27" t="inlineStr"/>
-      <c r="E24" s="12" t="n"/>
+      <c r="B24" s="25" t="inlineStr"/>
+      <c r="C24" s="25" t="inlineStr"/>
+      <c r="D24" s="25" t="inlineStr"/>
+      <c r="E24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>Labor — stairs (treads &amp; risers)</t>
         </is>
       </c>
-      <c r="B25" s="27" t="inlineStr"/>
-      <c r="C25" s="27" t="inlineStr"/>
-      <c r="D25" s="27" t="inlineStr"/>
-      <c r="E25" s="12" t="n"/>
+      <c r="B25" s="25" t="inlineStr"/>
+      <c r="C25" s="25" t="inlineStr"/>
+      <c r="D25" s="25" t="inlineStr"/>
+      <c r="E25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>TOTAL ESTIMATED</t>
         </is>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="28">
         <f>SUM(B17:B25)</f>
         <v/>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="28">
         <f>SUM(C17:C25)</f>
         <v/>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="28">
         <f>SUM(D17:D25)</f>
         <v/>
       </c>
-      <c r="E26" s="12" t="n"/>
+      <c r="E26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>Premium vs. cheapest option</t>
         </is>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="30">
         <f>B26-MIN($B$26:$D$26)</f>
         <v/>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="30">
         <f>C26-MIN($B$26:$D$26)</f>
         <v/>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="30">
         <f>D26-MIN($B$26:$D$26)</f>
         <v/>
       </c>
-      <c r="E27" s="12" t="n"/>
+      <c r="E27" s="10" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>BUDGET vs. ACTUAL</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Flooring materials</t>
         </is>
       </c>
-      <c r="B31" s="14">
+      <c r="B31" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,5,FALSE))</f>
         <v/>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="12">
         <f>SUMIF($D$48:$D$147,$A31,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="12">
         <f>IF(B31="","",B31-C31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Underlayment &amp; supplies</t>
         </is>
       </c>
-      <c r="B32" s="14">
+      <c r="B32" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,6,FALSE))</f>
         <v/>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="12">
         <f>SUMIF($D$48:$D$147,$A32,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="12">
         <f>IF(B32="","",B32-C32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Stair nose trim</t>
         </is>
       </c>
-      <c r="B33" s="14">
+      <c r="B33" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,7,FALSE))</f>
         <v/>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="12">
         <f>SUMIF($D$48:$D$147,$A33,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="12">
         <f>IF(B33="","",B33-C33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>Stair risers</t>
         </is>
       </c>
-      <c r="B34" s="14">
+      <c r="B34" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,8,FALSE))</f>
         <v/>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="12">
         <f>SUMIF($D$48:$D$147,$A34,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="12">
         <f>IF(B34="","",B34-C34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>Contractor discount</t>
         </is>
       </c>
-      <c r="B35" s="14">
+      <c r="B35" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,9,FALSE))</f>
         <v/>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="12">
         <f>SUMIF($D$48:$D$147,$A35,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="12">
         <f>IF(B35="","",B35-C35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>Sales tax</t>
         </is>
       </c>
-      <c r="B36" s="14">
+      <c r="B36" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,10,FALSE))</f>
         <v/>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="12">
         <f>SUMIF($D$48:$D$147,$A36,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="12">
         <f>IF(B36="","",B36-C36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>Labor — demo &amp; disposal</t>
         </is>
       </c>
-      <c r="B37" s="14">
+      <c r="B37" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,11,FALSE))</f>
         <v/>
       </c>
-      <c r="C37" s="14">
+      <c r="C37" s="12">
         <f>SUMIF($D$48:$D$147,$A37,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="12">
         <f>IF(B37="","",B37-C37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Labor — install</t>
         </is>
       </c>
-      <c r="B38" s="14">
+      <c r="B38" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,12,FALSE))</f>
         <v/>
       </c>
-      <c r="C38" s="14">
+      <c r="C38" s="12">
         <f>SUMIF($D$48:$D$147,$A38,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="12">
         <f>IF(B38="","",B38-C38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Labor — stairs</t>
         </is>
       </c>
-      <c r="B39" s="14">
+      <c r="B39" s="12">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,13,FALSE))</f>
         <v/>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="12">
         <f>SUMIF($D$48:$D$147,$A39,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D39" s="14">
+      <c r="D39" s="12">
         <f>IF(B39="","",B39-C39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Permits &amp; fees</t>
         </is>
       </c>
-      <c r="B40" s="14" t="n"/>
-      <c r="C40" s="14">
+      <c r="B40" s="12" t="n"/>
+      <c r="C40" s="12">
         <f>SUMIF($D$48:$D$147,$A40,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="12">
         <f>IF(B40="","",B40-C40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B41" s="14" t="n"/>
-      <c r="C41" s="14">
+      <c r="B41" s="12" t="n"/>
+      <c r="C41" s="12">
         <f>SUMIF($D$48:$D$147,$A41,$E$48:$E$147)</f>
         <v/>
       </c>
-      <c r="D41" s="14">
+      <c r="D41" s="12">
         <f>IF(B41="","",B41-C41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Contingency</t>
         </is>
       </c>
-      <c r="B42" s="14">
+      <c r="B42" s="12">
         <f>SUM(B31:B41)*$B$9</f>
         <v/>
       </c>
-      <c r="C42" s="14" t="n"/>
-      <c r="D42" s="14">
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12">
         <f>B42-C42</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="27" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B43" s="33">
+      <c r="B43" s="31">
         <f>SUM(B31:B42)</f>
         <v/>
       </c>
-      <c r="C43" s="33">
+      <c r="C43" s="31">
         <f>SUM(C31:C42)</f>
         <v/>
       </c>
-      <c r="D43" s="33">
+      <c r="D43" s="31">
         <f>B43-C43</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>COST LOG</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>Payment method</t>
         </is>
       </c>
-      <c r="G47" s="9" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="n"/>
-      <c r="B48" s="12" t="n"/>
-      <c r="C48" s="12" t="n"/>
-      <c r="D48" s="12" t="n"/>
-      <c r="E48" s="14" t="n"/>
-      <c r="F48" s="12" t="n"/>
-      <c r="G48" s="12" t="n"/>
+      <c r="A48" s="6" t="n"/>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="n"/>
-      <c r="B49" s="12" t="n"/>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="12" t="n"/>
-      <c r="E49" s="14" t="n"/>
-      <c r="F49" s="12" t="n"/>
-      <c r="G49" s="12" t="n"/>
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="n"/>
-      <c r="B50" s="12" t="n"/>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="12" t="n"/>
-      <c r="E50" s="14" t="n"/>
-      <c r="F50" s="12" t="n"/>
-      <c r="G50" s="12" t="n"/>
+      <c r="A50" s="6" t="n"/>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="n"/>
-      <c r="B51" s="12" t="n"/>
-      <c r="C51" s="12" t="n"/>
-      <c r="D51" s="12" t="n"/>
-      <c r="E51" s="14" t="n"/>
-      <c r="F51" s="12" t="n"/>
-      <c r="G51" s="12" t="n"/>
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="n"/>
-      <c r="B52" s="12" t="n"/>
-      <c r="C52" s="12" t="n"/>
-      <c r="D52" s="12" t="n"/>
-      <c r="E52" s="14" t="n"/>
-      <c r="F52" s="12" t="n"/>
-      <c r="G52" s="12" t="n"/>
+      <c r="A52" s="6" t="n"/>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="n"/>
-      <c r="B53" s="12" t="n"/>
-      <c r="C53" s="12" t="n"/>
-      <c r="D53" s="12" t="n"/>
-      <c r="E53" s="14" t="n"/>
-      <c r="F53" s="12" t="n"/>
-      <c r="G53" s="12" t="n"/>
+      <c r="A53" s="6" t="n"/>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="12" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="n"/>
-      <c r="B54" s="12" t="n"/>
-      <c r="C54" s="12" t="n"/>
-      <c r="D54" s="12" t="n"/>
-      <c r="E54" s="14" t="n"/>
-      <c r="F54" s="12" t="n"/>
-      <c r="G54" s="12" t="n"/>
+      <c r="A54" s="6" t="n"/>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="12" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="n"/>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="12" t="n"/>
-      <c r="D55" s="12" t="n"/>
-      <c r="E55" s="14" t="n"/>
-      <c r="F55" s="12" t="n"/>
-      <c r="G55" s="12" t="n"/>
+      <c r="A55" s="6" t="n"/>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="12" t="n"/>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="n"/>
-      <c r="B56" s="12" t="n"/>
-      <c r="C56" s="12" t="n"/>
-      <c r="D56" s="12" t="n"/>
-      <c r="E56" s="14" t="n"/>
-      <c r="F56" s="12" t="n"/>
-      <c r="G56" s="12" t="n"/>
+      <c r="A56" s="6" t="n"/>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="12" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="n"/>
-      <c r="B57" s="12" t="n"/>
-      <c r="C57" s="12" t="n"/>
-      <c r="D57" s="12" t="n"/>
-      <c r="E57" s="14" t="n"/>
-      <c r="F57" s="12" t="n"/>
-      <c r="G57" s="12" t="n"/>
+      <c r="A57" s="6" t="n"/>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="12" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="n"/>
-      <c r="B58" s="12" t="n"/>
-      <c r="C58" s="12" t="n"/>
-      <c r="D58" s="12" t="n"/>
-      <c r="E58" s="14" t="n"/>
-      <c r="F58" s="12" t="n"/>
-      <c r="G58" s="12" t="n"/>
+      <c r="A58" s="6" t="n"/>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="n"/>
-      <c r="B59" s="12" t="n"/>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="12" t="n"/>
-      <c r="E59" s="14" t="n"/>
-      <c r="F59" s="12" t="n"/>
-      <c r="G59" s="12" t="n"/>
+      <c r="A59" s="6" t="n"/>
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="12" t="n"/>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="n"/>
-      <c r="B60" s="12" t="n"/>
-      <c r="C60" s="12" t="n"/>
-      <c r="D60" s="12" t="n"/>
-      <c r="E60" s="14" t="n"/>
-      <c r="F60" s="12" t="n"/>
-      <c r="G60" s="12" t="n"/>
+      <c r="A60" s="6" t="n"/>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="12" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="n"/>
-      <c r="B61" s="12" t="n"/>
-      <c r="C61" s="12" t="n"/>
-      <c r="D61" s="12" t="n"/>
-      <c r="E61" s="14" t="n"/>
-      <c r="F61" s="12" t="n"/>
-      <c r="G61" s="12" t="n"/>
+      <c r="A61" s="6" t="n"/>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="12" t="n"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="n"/>
-      <c r="B62" s="12" t="n"/>
-      <c r="C62" s="12" t="n"/>
-      <c r="D62" s="12" t="n"/>
-      <c r="E62" s="14" t="n"/>
-      <c r="F62" s="12" t="n"/>
-      <c r="G62" s="12" t="n"/>
+      <c r="A62" s="6" t="n"/>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="12" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="n"/>
-      <c r="B63" s="12" t="n"/>
-      <c r="C63" s="12" t="n"/>
-      <c r="D63" s="12" t="n"/>
-      <c r="E63" s="14" t="n"/>
-      <c r="F63" s="12" t="n"/>
-      <c r="G63" s="12" t="n"/>
+      <c r="A63" s="6" t="n"/>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="12" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="n"/>
-      <c r="B64" s="12" t="n"/>
-      <c r="C64" s="12" t="n"/>
-      <c r="D64" s="12" t="n"/>
-      <c r="E64" s="14" t="n"/>
-      <c r="F64" s="12" t="n"/>
-      <c r="G64" s="12" t="n"/>
+      <c r="A64" s="6" t="n"/>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="12" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="n"/>
-      <c r="B65" s="12" t="n"/>
-      <c r="C65" s="12" t="n"/>
-      <c r="D65" s="12" t="n"/>
-      <c r="E65" s="14" t="n"/>
-      <c r="F65" s="12" t="n"/>
-      <c r="G65" s="12" t="n"/>
+      <c r="A65" s="6" t="n"/>
+      <c r="B65" s="10" t="n"/>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="10" t="n"/>
+      <c r="E65" s="12" t="n"/>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="n"/>
-      <c r="B66" s="12" t="n"/>
-      <c r="C66" s="12" t="n"/>
-      <c r="D66" s="12" t="n"/>
-      <c r="E66" s="14" t="n"/>
-      <c r="F66" s="12" t="n"/>
-      <c r="G66" s="12" t="n"/>
+      <c r="A66" s="6" t="n"/>
+      <c r="B66" s="10" t="n"/>
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="12" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="n"/>
-      <c r="B67" s="12" t="n"/>
-      <c r="C67" s="12" t="n"/>
-      <c r="D67" s="12" t="n"/>
-      <c r="E67" s="14" t="n"/>
-      <c r="F67" s="12" t="n"/>
-      <c r="G67" s="12" t="n"/>
+      <c r="A67" s="6" t="n"/>
+      <c r="B67" s="10" t="n"/>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="12" t="n"/>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="n"/>
-      <c r="B68" s="12" t="n"/>
-      <c r="C68" s="12" t="n"/>
-      <c r="D68" s="12" t="n"/>
-      <c r="E68" s="14" t="n"/>
-      <c r="F68" s="12" t="n"/>
-      <c r="G68" s="12" t="n"/>
+      <c r="A68" s="6" t="n"/>
+      <c r="B68" s="10" t="n"/>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="12" t="n"/>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="n"/>
-      <c r="B69" s="12" t="n"/>
-      <c r="C69" s="12" t="n"/>
-      <c r="D69" s="12" t="n"/>
-      <c r="E69" s="14" t="n"/>
-      <c r="F69" s="12" t="n"/>
-      <c r="G69" s="12" t="n"/>
+      <c r="A69" s="6" t="n"/>
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="12" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="n"/>
-      <c r="B70" s="12" t="n"/>
-      <c r="C70" s="12" t="n"/>
-      <c r="D70" s="12" t="n"/>
-      <c r="E70" s="14" t="n"/>
-      <c r="F70" s="12" t="n"/>
-      <c r="G70" s="12" t="n"/>
+      <c r="A70" s="6" t="n"/>
+      <c r="B70" s="10" t="n"/>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="12" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="n"/>
-      <c r="B71" s="12" t="n"/>
-      <c r="C71" s="12" t="n"/>
-      <c r="D71" s="12" t="n"/>
-      <c r="E71" s="14" t="n"/>
-      <c r="F71" s="12" t="n"/>
-      <c r="G71" s="12" t="n"/>
+      <c r="A71" s="6" t="n"/>
+      <c r="B71" s="10" t="n"/>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="12" t="n"/>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="n"/>
-      <c r="B72" s="12" t="n"/>
-      <c r="C72" s="12" t="n"/>
-      <c r="D72" s="12" t="n"/>
-      <c r="E72" s="14" t="n"/>
-      <c r="F72" s="12" t="n"/>
-      <c r="G72" s="12" t="n"/>
+      <c r="A72" s="6" t="n"/>
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="12" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="n"/>
-      <c r="B73" s="12" t="n"/>
-      <c r="C73" s="12" t="n"/>
-      <c r="D73" s="12" t="n"/>
-      <c r="E73" s="14" t="n"/>
-      <c r="F73" s="12" t="n"/>
-      <c r="G73" s="12" t="n"/>
+      <c r="A73" s="6" t="n"/>
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="10" t="n"/>
+      <c r="E73" s="12" t="n"/>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="n"/>
-      <c r="B74" s="12" t="n"/>
-      <c r="C74" s="12" t="n"/>
-      <c r="D74" s="12" t="n"/>
-      <c r="E74" s="14" t="n"/>
-      <c r="F74" s="12" t="n"/>
-      <c r="G74" s="12" t="n"/>
+      <c r="A74" s="6" t="n"/>
+      <c r="B74" s="10" t="n"/>
+      <c r="C74" s="10" t="n"/>
+      <c r="D74" s="10" t="n"/>
+      <c r="E74" s="12" t="n"/>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="n"/>
-      <c r="B75" s="12" t="n"/>
-      <c r="C75" s="12" t="n"/>
-      <c r="D75" s="12" t="n"/>
-      <c r="E75" s="14" t="n"/>
-      <c r="F75" s="12" t="n"/>
-      <c r="G75" s="12" t="n"/>
+      <c r="A75" s="6" t="n"/>
+      <c r="B75" s="10" t="n"/>
+      <c r="C75" s="10" t="n"/>
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="12" t="n"/>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="n"/>
-      <c r="B76" s="12" t="n"/>
-      <c r="C76" s="12" t="n"/>
-      <c r="D76" s="12" t="n"/>
-      <c r="E76" s="14" t="n"/>
-      <c r="F76" s="12" t="n"/>
-      <c r="G76" s="12" t="n"/>
+      <c r="A76" s="6" t="n"/>
+      <c r="B76" s="10" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="12" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="n"/>
-      <c r="B77" s="12" t="n"/>
-      <c r="C77" s="12" t="n"/>
-      <c r="D77" s="12" t="n"/>
-      <c r="E77" s="14" t="n"/>
-      <c r="F77" s="12" t="n"/>
-      <c r="G77" s="12" t="n"/>
+      <c r="A77" s="6" t="n"/>
+      <c r="B77" s="10" t="n"/>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="10" t="n"/>
+      <c r="E77" s="12" t="n"/>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="n"/>
-      <c r="B78" s="12" t="n"/>
-      <c r="C78" s="12" t="n"/>
-      <c r="D78" s="12" t="n"/>
-      <c r="E78" s="14" t="n"/>
-      <c r="F78" s="12" t="n"/>
-      <c r="G78" s="12" t="n"/>
+      <c r="A78" s="6" t="n"/>
+      <c r="B78" s="10" t="n"/>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="12" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="n"/>
-      <c r="B79" s="12" t="n"/>
-      <c r="C79" s="12" t="n"/>
-      <c r="D79" s="12" t="n"/>
-      <c r="E79" s="14" t="n"/>
-      <c r="F79" s="12" t="n"/>
-      <c r="G79" s="12" t="n"/>
+      <c r="A79" s="6" t="n"/>
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="12" t="n"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="n"/>
-      <c r="B80" s="12" t="n"/>
-      <c r="C80" s="12" t="n"/>
-      <c r="D80" s="12" t="n"/>
-      <c r="E80" s="14" t="n"/>
-      <c r="F80" s="12" t="n"/>
-      <c r="G80" s="12" t="n"/>
+      <c r="A80" s="6" t="n"/>
+      <c r="B80" s="10" t="n"/>
+      <c r="C80" s="10" t="n"/>
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="12" t="n"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="n"/>
-      <c r="B81" s="12" t="n"/>
-      <c r="C81" s="12" t="n"/>
-      <c r="D81" s="12" t="n"/>
-      <c r="E81" s="14" t="n"/>
-      <c r="F81" s="12" t="n"/>
-      <c r="G81" s="12" t="n"/>
+      <c r="A81" s="6" t="n"/>
+      <c r="B81" s="10" t="n"/>
+      <c r="C81" s="10" t="n"/>
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="12" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="n"/>
-      <c r="B82" s="12" t="n"/>
-      <c r="C82" s="12" t="n"/>
-      <c r="D82" s="12" t="n"/>
-      <c r="E82" s="14" t="n"/>
-      <c r="F82" s="12" t="n"/>
-      <c r="G82" s="12" t="n"/>
+      <c r="A82" s="6" t="n"/>
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="10" t="n"/>
+      <c r="E82" s="12" t="n"/>
+      <c r="F82" s="10" t="n"/>
+      <c r="G82" s="10" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="n"/>
-      <c r="B83" s="12" t="n"/>
-      <c r="C83" s="12" t="n"/>
-      <c r="D83" s="12" t="n"/>
-      <c r="E83" s="14" t="n"/>
-      <c r="F83" s="12" t="n"/>
-      <c r="G83" s="12" t="n"/>
+      <c r="A83" s="6" t="n"/>
+      <c r="B83" s="10" t="n"/>
+      <c r="C83" s="10" t="n"/>
+      <c r="D83" s="10" t="n"/>
+      <c r="E83" s="12" t="n"/>
+      <c r="F83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="n"/>
-      <c r="B84" s="12" t="n"/>
-      <c r="C84" s="12" t="n"/>
-      <c r="D84" s="12" t="n"/>
-      <c r="E84" s="14" t="n"/>
-      <c r="F84" s="12" t="n"/>
-      <c r="G84" s="12" t="n"/>
+      <c r="A84" s="6" t="n"/>
+      <c r="B84" s="10" t="n"/>
+      <c r="C84" s="10" t="n"/>
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="12" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="n"/>
-      <c r="B85" s="12" t="n"/>
-      <c r="C85" s="12" t="n"/>
-      <c r="D85" s="12" t="n"/>
-      <c r="E85" s="14" t="n"/>
-      <c r="F85" s="12" t="n"/>
-      <c r="G85" s="12" t="n"/>
+      <c r="A85" s="6" t="n"/>
+      <c r="B85" s="10" t="n"/>
+      <c r="C85" s="10" t="n"/>
+      <c r="D85" s="10" t="n"/>
+      <c r="E85" s="12" t="n"/>
+      <c r="F85" s="10" t="n"/>
+      <c r="G85" s="10" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="n"/>
-      <c r="B86" s="12" t="n"/>
-      <c r="C86" s="12" t="n"/>
-      <c r="D86" s="12" t="n"/>
-      <c r="E86" s="14" t="n"/>
-      <c r="F86" s="12" t="n"/>
-      <c r="G86" s="12" t="n"/>
+      <c r="A86" s="6" t="n"/>
+      <c r="B86" s="10" t="n"/>
+      <c r="C86" s="10" t="n"/>
+      <c r="D86" s="10" t="n"/>
+      <c r="E86" s="12" t="n"/>
+      <c r="F86" s="10" t="n"/>
+      <c r="G86" s="10" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="n"/>
-      <c r="B87" s="12" t="n"/>
-      <c r="C87" s="12" t="n"/>
-      <c r="D87" s="12" t="n"/>
-      <c r="E87" s="14" t="n"/>
-      <c r="F87" s="12" t="n"/>
-      <c r="G87" s="12" t="n"/>
+      <c r="A87" s="6" t="n"/>
+      <c r="B87" s="10" t="n"/>
+      <c r="C87" s="10" t="n"/>
+      <c r="D87" s="10" t="n"/>
+      <c r="E87" s="12" t="n"/>
+      <c r="F87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="n"/>
-      <c r="B88" s="12" t="n"/>
-      <c r="C88" s="12" t="n"/>
-      <c r="D88" s="12" t="n"/>
-      <c r="E88" s="14" t="n"/>
-      <c r="F88" s="12" t="n"/>
-      <c r="G88" s="12" t="n"/>
+      <c r="A88" s="6" t="n"/>
+      <c r="B88" s="10" t="n"/>
+      <c r="C88" s="10" t="n"/>
+      <c r="D88" s="10" t="n"/>
+      <c r="E88" s="12" t="n"/>
+      <c r="F88" s="10" t="n"/>
+      <c r="G88" s="10" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="n"/>
-      <c r="B89" s="12" t="n"/>
-      <c r="C89" s="12" t="n"/>
-      <c r="D89" s="12" t="n"/>
-      <c r="E89" s="14" t="n"/>
-      <c r="F89" s="12" t="n"/>
-      <c r="G89" s="12" t="n"/>
+      <c r="A89" s="6" t="n"/>
+      <c r="B89" s="10" t="n"/>
+      <c r="C89" s="10" t="n"/>
+      <c r="D89" s="10" t="n"/>
+      <c r="E89" s="12" t="n"/>
+      <c r="F89" s="10" t="n"/>
+      <c r="G89" s="10" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="n"/>
-      <c r="B90" s="12" t="n"/>
-      <c r="C90" s="12" t="n"/>
-      <c r="D90" s="12" t="n"/>
-      <c r="E90" s="14" t="n"/>
-      <c r="F90" s="12" t="n"/>
-      <c r="G90" s="12" t="n"/>
+      <c r="A90" s="6" t="n"/>
+      <c r="B90" s="10" t="n"/>
+      <c r="C90" s="10" t="n"/>
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="12" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="n"/>
-      <c r="B91" s="12" t="n"/>
-      <c r="C91" s="12" t="n"/>
-      <c r="D91" s="12" t="n"/>
-      <c r="E91" s="14" t="n"/>
-      <c r="F91" s="12" t="n"/>
-      <c r="G91" s="12" t="n"/>
+      <c r="A91" s="6" t="n"/>
+      <c r="B91" s="10" t="n"/>
+      <c r="C91" s="10" t="n"/>
+      <c r="D91" s="10" t="n"/>
+      <c r="E91" s="12" t="n"/>
+      <c r="F91" s="10" t="n"/>
+      <c r="G91" s="10" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="n"/>
-      <c r="B92" s="12" t="n"/>
-      <c r="C92" s="12" t="n"/>
-      <c r="D92" s="12" t="n"/>
-      <c r="E92" s="14" t="n"/>
-      <c r="F92" s="12" t="n"/>
-      <c r="G92" s="12" t="n"/>
+      <c r="A92" s="6" t="n"/>
+      <c r="B92" s="10" t="n"/>
+      <c r="C92" s="10" t="n"/>
+      <c r="D92" s="10" t="n"/>
+      <c r="E92" s="12" t="n"/>
+      <c r="F92" s="10" t="n"/>
+      <c r="G92" s="10" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="n"/>
-      <c r="B93" s="12" t="n"/>
-      <c r="C93" s="12" t="n"/>
-      <c r="D93" s="12" t="n"/>
-      <c r="E93" s="14" t="n"/>
-      <c r="F93" s="12" t="n"/>
-      <c r="G93" s="12" t="n"/>
+      <c r="A93" s="6" t="n"/>
+      <c r="B93" s="10" t="n"/>
+      <c r="C93" s="10" t="n"/>
+      <c r="D93" s="10" t="n"/>
+      <c r="E93" s="12" t="n"/>
+      <c r="F93" s="10" t="n"/>
+      <c r="G93" s="10" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="n"/>
-      <c r="B94" s="12" t="n"/>
-      <c r="C94" s="12" t="n"/>
-      <c r="D94" s="12" t="n"/>
-      <c r="E94" s="14" t="n"/>
-      <c r="F94" s="12" t="n"/>
-      <c r="G94" s="12" t="n"/>
+      <c r="A94" s="6" t="n"/>
+      <c r="B94" s="10" t="n"/>
+      <c r="C94" s="10" t="n"/>
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="12" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="n"/>
-      <c r="B95" s="12" t="n"/>
-      <c r="C95" s="12" t="n"/>
-      <c r="D95" s="12" t="n"/>
-      <c r="E95" s="14" t="n"/>
-      <c r="F95" s="12" t="n"/>
-      <c r="G95" s="12" t="n"/>
+      <c r="A95" s="6" t="n"/>
+      <c r="B95" s="10" t="n"/>
+      <c r="C95" s="10" t="n"/>
+      <c r="D95" s="10" t="n"/>
+      <c r="E95" s="12" t="n"/>
+      <c r="F95" s="10" t="n"/>
+      <c r="G95" s="10" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="8" t="n"/>
-      <c r="B96" s="12" t="n"/>
-      <c r="C96" s="12" t="n"/>
-      <c r="D96" s="12" t="n"/>
-      <c r="E96" s="14" t="n"/>
-      <c r="F96" s="12" t="n"/>
-      <c r="G96" s="12" t="n"/>
+      <c r="A96" s="6" t="n"/>
+      <c r="B96" s="10" t="n"/>
+      <c r="C96" s="10" t="n"/>
+      <c r="D96" s="10" t="n"/>
+      <c r="E96" s="12" t="n"/>
+      <c r="F96" s="10" t="n"/>
+      <c r="G96" s="10" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="n"/>
-      <c r="B97" s="12" t="n"/>
-      <c r="C97" s="12" t="n"/>
-      <c r="D97" s="12" t="n"/>
-      <c r="E97" s="14" t="n"/>
-      <c r="F97" s="12" t="n"/>
-      <c r="G97" s="12" t="n"/>
+      <c r="A97" s="6" t="n"/>
+      <c r="B97" s="10" t="n"/>
+      <c r="C97" s="10" t="n"/>
+      <c r="D97" s="10" t="n"/>
+      <c r="E97" s="12" t="n"/>
+      <c r="F97" s="10" t="n"/>
+      <c r="G97" s="10" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="n"/>
-      <c r="B98" s="12" t="n"/>
-      <c r="C98" s="12" t="n"/>
-      <c r="D98" s="12" t="n"/>
-      <c r="E98" s="14" t="n"/>
-      <c r="F98" s="12" t="n"/>
-      <c r="G98" s="12" t="n"/>
+      <c r="A98" s="6" t="n"/>
+      <c r="B98" s="10" t="n"/>
+      <c r="C98" s="10" t="n"/>
+      <c r="D98" s="10" t="n"/>
+      <c r="E98" s="12" t="n"/>
+      <c r="F98" s="10" t="n"/>
+      <c r="G98" s="10" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="n"/>
-      <c r="B99" s="12" t="n"/>
-      <c r="C99" s="12" t="n"/>
-      <c r="D99" s="12" t="n"/>
-      <c r="E99" s="14" t="n"/>
-      <c r="F99" s="12" t="n"/>
-      <c r="G99" s="12" t="n"/>
+      <c r="A99" s="6" t="n"/>
+      <c r="B99" s="10" t="n"/>
+      <c r="C99" s="10" t="n"/>
+      <c r="D99" s="10" t="n"/>
+      <c r="E99" s="12" t="n"/>
+      <c r="F99" s="10" t="n"/>
+      <c r="G99" s="10" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="n"/>
-      <c r="B100" s="12" t="n"/>
-      <c r="C100" s="12" t="n"/>
-      <c r="D100" s="12" t="n"/>
-      <c r="E100" s="14" t="n"/>
-      <c r="F100" s="12" t="n"/>
-      <c r="G100" s="12" t="n"/>
+      <c r="A100" s="6" t="n"/>
+      <c r="B100" s="10" t="n"/>
+      <c r="C100" s="10" t="n"/>
+      <c r="D100" s="10" t="n"/>
+      <c r="E100" s="12" t="n"/>
+      <c r="F100" s="10" t="n"/>
+      <c r="G100" s="10" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="n"/>
-      <c r="B101" s="12" t="n"/>
-      <c r="C101" s="12" t="n"/>
-      <c r="D101" s="12" t="n"/>
-      <c r="E101" s="14" t="n"/>
-      <c r="F101" s="12" t="n"/>
-      <c r="G101" s="12" t="n"/>
+      <c r="A101" s="6" t="n"/>
+      <c r="B101" s="10" t="n"/>
+      <c r="C101" s="10" t="n"/>
+      <c r="D101" s="10" t="n"/>
+      <c r="E101" s="12" t="n"/>
+      <c r="F101" s="10" t="n"/>
+      <c r="G101" s="10" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="n"/>
-      <c r="B102" s="12" t="n"/>
-      <c r="C102" s="12" t="n"/>
-      <c r="D102" s="12" t="n"/>
-      <c r="E102" s="14" t="n"/>
-      <c r="F102" s="12" t="n"/>
-      <c r="G102" s="12" t="n"/>
+      <c r="A102" s="6" t="n"/>
+      <c r="B102" s="10" t="n"/>
+      <c r="C102" s="10" t="n"/>
+      <c r="D102" s="10" t="n"/>
+      <c r="E102" s="12" t="n"/>
+      <c r="F102" s="10" t="n"/>
+      <c r="G102" s="10" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="8" t="n"/>
-      <c r="B103" s="12" t="n"/>
-      <c r="C103" s="12" t="n"/>
-      <c r="D103" s="12" t="n"/>
-      <c r="E103" s="14" t="n"/>
-      <c r="F103" s="12" t="n"/>
-      <c r="G103" s="12" t="n"/>
+      <c r="A103" s="6" t="n"/>
+      <c r="B103" s="10" t="n"/>
+      <c r="C103" s="10" t="n"/>
+      <c r="D103" s="10" t="n"/>
+      <c r="E103" s="12" t="n"/>
+      <c r="F103" s="10" t="n"/>
+      <c r="G103" s="10" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="n"/>
-      <c r="B104" s="12" t="n"/>
-      <c r="C104" s="12" t="n"/>
-      <c r="D104" s="12" t="n"/>
-      <c r="E104" s="14" t="n"/>
-      <c r="F104" s="12" t="n"/>
-      <c r="G104" s="12" t="n"/>
+      <c r="A104" s="6" t="n"/>
+      <c r="B104" s="10" t="n"/>
+      <c r="C104" s="10" t="n"/>
+      <c r="D104" s="10" t="n"/>
+      <c r="E104" s="12" t="n"/>
+      <c r="F104" s="10" t="n"/>
+      <c r="G104" s="10" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="8" t="n"/>
-      <c r="B105" s="12" t="n"/>
-      <c r="C105" s="12" t="n"/>
-      <c r="D105" s="12" t="n"/>
-      <c r="E105" s="14" t="n"/>
-      <c r="F105" s="12" t="n"/>
-      <c r="G105" s="12" t="n"/>
+      <c r="A105" s="6" t="n"/>
+      <c r="B105" s="10" t="n"/>
+      <c r="C105" s="10" t="n"/>
+      <c r="D105" s="10" t="n"/>
+      <c r="E105" s="12" t="n"/>
+      <c r="F105" s="10" t="n"/>
+      <c r="G105" s="10" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="n"/>
-      <c r="B106" s="12" t="n"/>
-      <c r="C106" s="12" t="n"/>
-      <c r="D106" s="12" t="n"/>
-      <c r="E106" s="14" t="n"/>
-      <c r="F106" s="12" t="n"/>
-      <c r="G106" s="12" t="n"/>
+      <c r="A106" s="6" t="n"/>
+      <c r="B106" s="10" t="n"/>
+      <c r="C106" s="10" t="n"/>
+      <c r="D106" s="10" t="n"/>
+      <c r="E106" s="12" t="n"/>
+      <c r="F106" s="10" t="n"/>
+      <c r="G106" s="10" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="8" t="n"/>
-      <c r="B107" s="12" t="n"/>
-      <c r="C107" s="12" t="n"/>
-      <c r="D107" s="12" t="n"/>
-      <c r="E107" s="14" t="n"/>
-      <c r="F107" s="12" t="n"/>
-      <c r="G107" s="12" t="n"/>
+      <c r="A107" s="6" t="n"/>
+      <c r="B107" s="10" t="n"/>
+      <c r="C107" s="10" t="n"/>
+      <c r="D107" s="10" t="n"/>
+      <c r="E107" s="12" t="n"/>
+      <c r="F107" s="10" t="n"/>
+      <c r="G107" s="10" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="n"/>
-      <c r="B108" s="12" t="n"/>
-      <c r="C108" s="12" t="n"/>
-      <c r="D108" s="12" t="n"/>
-      <c r="E108" s="14" t="n"/>
-      <c r="F108" s="12" t="n"/>
-      <c r="G108" s="12" t="n"/>
+      <c r="A108" s="6" t="n"/>
+      <c r="B108" s="10" t="n"/>
+      <c r="C108" s="10" t="n"/>
+      <c r="D108" s="10" t="n"/>
+      <c r="E108" s="12" t="n"/>
+      <c r="F108" s="10" t="n"/>
+      <c r="G108" s="10" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="n"/>
-      <c r="B109" s="12" t="n"/>
-      <c r="C109" s="12" t="n"/>
-      <c r="D109" s="12" t="n"/>
-      <c r="E109" s="14" t="n"/>
-      <c r="F109" s="12" t="n"/>
-      <c r="G109" s="12" t="n"/>
+      <c r="A109" s="6" t="n"/>
+      <c r="B109" s="10" t="n"/>
+      <c r="C109" s="10" t="n"/>
+      <c r="D109" s="10" t="n"/>
+      <c r="E109" s="12" t="n"/>
+      <c r="F109" s="10" t="n"/>
+      <c r="G109" s="10" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="n"/>
-      <c r="B110" s="12" t="n"/>
-      <c r="C110" s="12" t="n"/>
-      <c r="D110" s="12" t="n"/>
-      <c r="E110" s="14" t="n"/>
-      <c r="F110" s="12" t="n"/>
-      <c r="G110" s="12" t="n"/>
+      <c r="A110" s="6" t="n"/>
+      <c r="B110" s="10" t="n"/>
+      <c r="C110" s="10" t="n"/>
+      <c r="D110" s="10" t="n"/>
+      <c r="E110" s="12" t="n"/>
+      <c r="F110" s="10" t="n"/>
+      <c r="G110" s="10" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="8" t="n"/>
-      <c r="B111" s="12" t="n"/>
-      <c r="C111" s="12" t="n"/>
-      <c r="D111" s="12" t="n"/>
-      <c r="E111" s="14" t="n"/>
-      <c r="F111" s="12" t="n"/>
-      <c r="G111" s="12" t="n"/>
+      <c r="A111" s="6" t="n"/>
+      <c r="B111" s="10" t="n"/>
+      <c r="C111" s="10" t="n"/>
+      <c r="D111" s="10" t="n"/>
+      <c r="E111" s="12" t="n"/>
+      <c r="F111" s="10" t="n"/>
+      <c r="G111" s="10" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="n"/>
-      <c r="B112" s="12" t="n"/>
-      <c r="C112" s="12" t="n"/>
-      <c r="D112" s="12" t="n"/>
-      <c r="E112" s="14" t="n"/>
-      <c r="F112" s="12" t="n"/>
-      <c r="G112" s="12" t="n"/>
+      <c r="A112" s="6" t="n"/>
+      <c r="B112" s="10" t="n"/>
+      <c r="C112" s="10" t="n"/>
+      <c r="D112" s="10" t="n"/>
+      <c r="E112" s="12" t="n"/>
+      <c r="F112" s="10" t="n"/>
+      <c r="G112" s="10" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="8" t="n"/>
-      <c r="B113" s="12" t="n"/>
-      <c r="C113" s="12" t="n"/>
-      <c r="D113" s="12" t="n"/>
-      <c r="E113" s="14" t="n"/>
-      <c r="F113" s="12" t="n"/>
-      <c r="G113" s="12" t="n"/>
+      <c r="A113" s="6" t="n"/>
+      <c r="B113" s="10" t="n"/>
+      <c r="C113" s="10" t="n"/>
+      <c r="D113" s="10" t="n"/>
+      <c r="E113" s="12" t="n"/>
+      <c r="F113" s="10" t="n"/>
+      <c r="G113" s="10" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="8" t="n"/>
-      <c r="B114" s="12" t="n"/>
-      <c r="C114" s="12" t="n"/>
-      <c r="D114" s="12" t="n"/>
-      <c r="E114" s="14" t="n"/>
-      <c r="F114" s="12" t="n"/>
-      <c r="G114" s="12" t="n"/>
+      <c r="A114" s="6" t="n"/>
+      <c r="B114" s="10" t="n"/>
+      <c r="C114" s="10" t="n"/>
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="12" t="n"/>
+      <c r="F114" s="10" t="n"/>
+      <c r="G114" s="10" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="n"/>
-      <c r="B115" s="12" t="n"/>
-      <c r="C115" s="12" t="n"/>
-      <c r="D115" s="12" t="n"/>
-      <c r="E115" s="14" t="n"/>
-      <c r="F115" s="12" t="n"/>
-      <c r="G115" s="12" t="n"/>
+      <c r="A115" s="6" t="n"/>
+      <c r="B115" s="10" t="n"/>
+      <c r="C115" s="10" t="n"/>
+      <c r="D115" s="10" t="n"/>
+      <c r="E115" s="12" t="n"/>
+      <c r="F115" s="10" t="n"/>
+      <c r="G115" s="10" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="n"/>
-      <c r="B116" s="12" t="n"/>
-      <c r="C116" s="12" t="n"/>
-      <c r="D116" s="12" t="n"/>
-      <c r="E116" s="14" t="n"/>
-      <c r="F116" s="12" t="n"/>
-      <c r="G116" s="12" t="n"/>
+      <c r="A116" s="6" t="n"/>
+      <c r="B116" s="10" t="n"/>
+      <c r="C116" s="10" t="n"/>
+      <c r="D116" s="10" t="n"/>
+      <c r="E116" s="12" t="n"/>
+      <c r="F116" s="10" t="n"/>
+      <c r="G116" s="10" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="8" t="n"/>
-      <c r="B117" s="12" t="n"/>
-      <c r="C117" s="12" t="n"/>
-      <c r="D117" s="12" t="n"/>
-      <c r="E117" s="14" t="n"/>
-      <c r="F117" s="12" t="n"/>
-      <c r="G117" s="12" t="n"/>
+      <c r="A117" s="6" t="n"/>
+      <c r="B117" s="10" t="n"/>
+      <c r="C117" s="10" t="n"/>
+      <c r="D117" s="10" t="n"/>
+      <c r="E117" s="12" t="n"/>
+      <c r="F117" s="10" t="n"/>
+      <c r="G117" s="10" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="8" t="n"/>
-      <c r="B118" s="12" t="n"/>
-      <c r="C118" s="12" t="n"/>
-      <c r="D118" s="12" t="n"/>
-      <c r="E118" s="14" t="n"/>
-      <c r="F118" s="12" t="n"/>
-      <c r="G118" s="12" t="n"/>
+      <c r="A118" s="6" t="n"/>
+      <c r="B118" s="10" t="n"/>
+      <c r="C118" s="10" t="n"/>
+      <c r="D118" s="10" t="n"/>
+      <c r="E118" s="12" t="n"/>
+      <c r="F118" s="10" t="n"/>
+      <c r="G118" s="10" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="8" t="n"/>
-      <c r="B119" s="12" t="n"/>
-      <c r="C119" s="12" t="n"/>
-      <c r="D119" s="12" t="n"/>
-      <c r="E119" s="14" t="n"/>
-      <c r="F119" s="12" t="n"/>
-      <c r="G119" s="12" t="n"/>
+      <c r="A119" s="6" t="n"/>
+      <c r="B119" s="10" t="n"/>
+      <c r="C119" s="10" t="n"/>
+      <c r="D119" s="10" t="n"/>
+      <c r="E119" s="12" t="n"/>
+      <c r="F119" s="10" t="n"/>
+      <c r="G119" s="10" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="8" t="n"/>
-      <c r="B120" s="12" t="n"/>
-      <c r="C120" s="12" t="n"/>
-      <c r="D120" s="12" t="n"/>
-      <c r="E120" s="14" t="n"/>
-      <c r="F120" s="12" t="n"/>
-      <c r="G120" s="12" t="n"/>
+      <c r="A120" s="6" t="n"/>
+      <c r="B120" s="10" t="n"/>
+      <c r="C120" s="10" t="n"/>
+      <c r="D120" s="10" t="n"/>
+      <c r="E120" s="12" t="n"/>
+      <c r="F120" s="10" t="n"/>
+      <c r="G120" s="10" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="8" t="n"/>
-      <c r="B121" s="12" t="n"/>
-      <c r="C121" s="12" t="n"/>
-      <c r="D121" s="12" t="n"/>
-      <c r="E121" s="14" t="n"/>
-      <c r="F121" s="12" t="n"/>
-      <c r="G121" s="12" t="n"/>
+      <c r="A121" s="6" t="n"/>
+      <c r="B121" s="10" t="n"/>
+      <c r="C121" s="10" t="n"/>
+      <c r="D121" s="10" t="n"/>
+      <c r="E121" s="12" t="n"/>
+      <c r="F121" s="10" t="n"/>
+      <c r="G121" s="10" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="8" t="n"/>
-      <c r="B122" s="12" t="n"/>
-      <c r="C122" s="12" t="n"/>
-      <c r="D122" s="12" t="n"/>
-      <c r="E122" s="14" t="n"/>
-      <c r="F122" s="12" t="n"/>
-      <c r="G122" s="12" t="n"/>
+      <c r="A122" s="6" t="n"/>
+      <c r="B122" s="10" t="n"/>
+      <c r="C122" s="10" t="n"/>
+      <c r="D122" s="10" t="n"/>
+      <c r="E122" s="12" t="n"/>
+      <c r="F122" s="10" t="n"/>
+      <c r="G122" s="10" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="8" t="n"/>
-      <c r="B123" s="12" t="n"/>
-      <c r="C123" s="12" t="n"/>
-      <c r="D123" s="12" t="n"/>
-      <c r="E123" s="14" t="n"/>
-      <c r="F123" s="12" t="n"/>
-      <c r="G123" s="12" t="n"/>
+      <c r="A123" s="6" t="n"/>
+      <c r="B123" s="10" t="n"/>
+      <c r="C123" s="10" t="n"/>
+      <c r="D123" s="10" t="n"/>
+      <c r="E123" s="12" t="n"/>
+      <c r="F123" s="10" t="n"/>
+      <c r="G123" s="10" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="8" t="n"/>
-      <c r="B124" s="12" t="n"/>
-      <c r="C124" s="12" t="n"/>
-      <c r="D124" s="12" t="n"/>
-      <c r="E124" s="14" t="n"/>
-      <c r="F124" s="12" t="n"/>
-      <c r="G124" s="12" t="n"/>
+      <c r="A124" s="6" t="n"/>
+      <c r="B124" s="10" t="n"/>
+      <c r="C124" s="10" t="n"/>
+      <c r="D124" s="10" t="n"/>
+      <c r="E124" s="12" t="n"/>
+      <c r="F124" s="10" t="n"/>
+      <c r="G124" s="10" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="8" t="n"/>
-      <c r="B125" s="12" t="n"/>
-      <c r="C125" s="12" t="n"/>
-      <c r="D125" s="12" t="n"/>
-      <c r="E125" s="14" t="n"/>
-      <c r="F125" s="12" t="n"/>
-      <c r="G125" s="12" t="n"/>
+      <c r="A125" s="6" t="n"/>
+      <c r="B125" s="10" t="n"/>
+      <c r="C125" s="10" t="n"/>
+      <c r="D125" s="10" t="n"/>
+      <c r="E125" s="12" t="n"/>
+      <c r="F125" s="10" t="n"/>
+      <c r="G125" s="10" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="8" t="n"/>
-      <c r="B126" s="12" t="n"/>
-      <c r="C126" s="12" t="n"/>
-      <c r="D126" s="12" t="n"/>
-      <c r="E126" s="14" t="n"/>
-      <c r="F126" s="12" t="n"/>
-      <c r="G126" s="12" t="n"/>
+      <c r="A126" s="6" t="n"/>
+      <c r="B126" s="10" t="n"/>
+      <c r="C126" s="10" t="n"/>
+      <c r="D126" s="10" t="n"/>
+      <c r="E126" s="12" t="n"/>
+      <c r="F126" s="10" t="n"/>
+      <c r="G126" s="10" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="8" t="n"/>
-      <c r="B127" s="12" t="n"/>
-      <c r="C127" s="12" t="n"/>
-      <c r="D127" s="12" t="n"/>
-      <c r="E127" s="14" t="n"/>
-      <c r="F127" s="12" t="n"/>
-      <c r="G127" s="12" t="n"/>
+      <c r="A127" s="6" t="n"/>
+      <c r="B127" s="10" t="n"/>
+      <c r="C127" s="10" t="n"/>
+      <c r="D127" s="10" t="n"/>
+      <c r="E127" s="12" t="n"/>
+      <c r="F127" s="10" t="n"/>
+      <c r="G127" s="10" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="8" t="n"/>
-      <c r="B128" s="12" t="n"/>
-      <c r="C128" s="12" t="n"/>
-      <c r="D128" s="12" t="n"/>
-      <c r="E128" s="14" t="n"/>
-      <c r="F128" s="12" t="n"/>
-      <c r="G128" s="12" t="n"/>
+      <c r="A128" s="6" t="n"/>
+      <c r="B128" s="10" t="n"/>
+      <c r="C128" s="10" t="n"/>
+      <c r="D128" s="10" t="n"/>
+      <c r="E128" s="12" t="n"/>
+      <c r="F128" s="10" t="n"/>
+      <c r="G128" s="10" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="8" t="n"/>
-      <c r="B129" s="12" t="n"/>
-      <c r="C129" s="12" t="n"/>
-      <c r="D129" s="12" t="n"/>
-      <c r="E129" s="14" t="n"/>
-      <c r="F129" s="12" t="n"/>
-      <c r="G129" s="12" t="n"/>
+      <c r="A129" s="6" t="n"/>
+      <c r="B129" s="10" t="n"/>
+      <c r="C129" s="10" t="n"/>
+      <c r="D129" s="10" t="n"/>
+      <c r="E129" s="12" t="n"/>
+      <c r="F129" s="10" t="n"/>
+      <c r="G129" s="10" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="8" t="n"/>
-      <c r="B130" s="12" t="n"/>
-      <c r="C130" s="12" t="n"/>
-      <c r="D130" s="12" t="n"/>
-      <c r="E130" s="14" t="n"/>
-      <c r="F130" s="12" t="n"/>
-      <c r="G130" s="12" t="n"/>
+      <c r="A130" s="6" t="n"/>
+      <c r="B130" s="10" t="n"/>
+      <c r="C130" s="10" t="n"/>
+      <c r="D130" s="10" t="n"/>
+      <c r="E130" s="12" t="n"/>
+      <c r="F130" s="10" t="n"/>
+      <c r="G130" s="10" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="8" t="n"/>
-      <c r="B131" s="12" t="n"/>
-      <c r="C131" s="12" t="n"/>
-      <c r="D131" s="12" t="n"/>
-      <c r="E131" s="14" t="n"/>
-      <c r="F131" s="12" t="n"/>
-      <c r="G131" s="12" t="n"/>
+      <c r="A131" s="6" t="n"/>
+      <c r="B131" s="10" t="n"/>
+      <c r="C131" s="10" t="n"/>
+      <c r="D131" s="10" t="n"/>
+      <c r="E131" s="12" t="n"/>
+      <c r="F131" s="10" t="n"/>
+      <c r="G131" s="10" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="8" t="n"/>
-      <c r="B132" s="12" t="n"/>
-      <c r="C132" s="12" t="n"/>
-      <c r="D132" s="12" t="n"/>
-      <c r="E132" s="14" t="n"/>
-      <c r="F132" s="12" t="n"/>
-      <c r="G132" s="12" t="n"/>
+      <c r="A132" s="6" t="n"/>
+      <c r="B132" s="10" t="n"/>
+      <c r="C132" s="10" t="n"/>
+      <c r="D132" s="10" t="n"/>
+      <c r="E132" s="12" t="n"/>
+      <c r="F132" s="10" t="n"/>
+      <c r="G132" s="10" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="8" t="n"/>
-      <c r="B133" s="12" t="n"/>
-      <c r="C133" s="12" t="n"/>
-      <c r="D133" s="12" t="n"/>
-      <c r="E133" s="14" t="n"/>
-      <c r="F133" s="12" t="n"/>
-      <c r="G133" s="12" t="n"/>
+      <c r="A133" s="6" t="n"/>
+      <c r="B133" s="10" t="n"/>
+      <c r="C133" s="10" t="n"/>
+      <c r="D133" s="10" t="n"/>
+      <c r="E133" s="12" t="n"/>
+      <c r="F133" s="10" t="n"/>
+      <c r="G133" s="10" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="8" t="n"/>
-      <c r="B134" s="12" t="n"/>
-      <c r="C134" s="12" t="n"/>
-      <c r="D134" s="12" t="n"/>
-      <c r="E134" s="14" t="n"/>
-      <c r="F134" s="12" t="n"/>
-      <c r="G134" s="12" t="n"/>
+      <c r="A134" s="6" t="n"/>
+      <c r="B134" s="10" t="n"/>
+      <c r="C134" s="10" t="n"/>
+      <c r="D134" s="10" t="n"/>
+      <c r="E134" s="12" t="n"/>
+      <c r="F134" s="10" t="n"/>
+      <c r="G134" s="10" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="8" t="n"/>
-      <c r="B135" s="12" t="n"/>
-      <c r="C135" s="12" t="n"/>
-      <c r="D135" s="12" t="n"/>
-      <c r="E135" s="14" t="n"/>
-      <c r="F135" s="12" t="n"/>
-      <c r="G135" s="12" t="n"/>
+      <c r="A135" s="6" t="n"/>
+      <c r="B135" s="10" t="n"/>
+      <c r="C135" s="10" t="n"/>
+      <c r="D135" s="10" t="n"/>
+      <c r="E135" s="12" t="n"/>
+      <c r="F135" s="10" t="n"/>
+      <c r="G135" s="10" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="8" t="n"/>
-      <c r="B136" s="12" t="n"/>
-      <c r="C136" s="12" t="n"/>
-      <c r="D136" s="12" t="n"/>
-      <c r="E136" s="14" t="n"/>
-      <c r="F136" s="12" t="n"/>
-      <c r="G136" s="12" t="n"/>
+      <c r="A136" s="6" t="n"/>
+      <c r="B136" s="10" t="n"/>
+      <c r="C136" s="10" t="n"/>
+      <c r="D136" s="10" t="n"/>
+      <c r="E136" s="12" t="n"/>
+      <c r="F136" s="10" t="n"/>
+      <c r="G136" s="10" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="8" t="n"/>
-      <c r="B137" s="12" t="n"/>
-      <c r="C137" s="12" t="n"/>
-      <c r="D137" s="12" t="n"/>
-      <c r="E137" s="14" t="n"/>
-      <c r="F137" s="12" t="n"/>
-      <c r="G137" s="12" t="n"/>
+      <c r="A137" s="6" t="n"/>
+      <c r="B137" s="10" t="n"/>
+      <c r="C137" s="10" t="n"/>
+      <c r="D137" s="10" t="n"/>
+      <c r="E137" s="12" t="n"/>
+      <c r="F137" s="10" t="n"/>
+      <c r="G137" s="10" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="8" t="n"/>
-      <c r="B138" s="12" t="n"/>
-      <c r="C138" s="12" t="n"/>
-      <c r="D138" s="12" t="n"/>
-      <c r="E138" s="14" t="n"/>
-      <c r="F138" s="12" t="n"/>
-      <c r="G138" s="12" t="n"/>
+      <c r="A138" s="6" t="n"/>
+      <c r="B138" s="10" t="n"/>
+      <c r="C138" s="10" t="n"/>
+      <c r="D138" s="10" t="n"/>
+      <c r="E138" s="12" t="n"/>
+      <c r="F138" s="10" t="n"/>
+      <c r="G138" s="10" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="8" t="n"/>
-      <c r="B139" s="12" t="n"/>
-      <c r="C139" s="12" t="n"/>
-      <c r="D139" s="12" t="n"/>
-      <c r="E139" s="14" t="n"/>
-      <c r="F139" s="12" t="n"/>
-      <c r="G139" s="12" t="n"/>
+      <c r="A139" s="6" t="n"/>
+      <c r="B139" s="10" t="n"/>
+      <c r="C139" s="10" t="n"/>
+      <c r="D139" s="10" t="n"/>
+      <c r="E139" s="12" t="n"/>
+      <c r="F139" s="10" t="n"/>
+      <c r="G139" s="10" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="8" t="n"/>
-      <c r="B140" s="12" t="n"/>
-      <c r="C140" s="12" t="n"/>
-      <c r="D140" s="12" t="n"/>
-      <c r="E140" s="14" t="n"/>
-      <c r="F140" s="12" t="n"/>
-      <c r="G140" s="12" t="n"/>
+      <c r="A140" s="6" t="n"/>
+      <c r="B140" s="10" t="n"/>
+      <c r="C140" s="10" t="n"/>
+      <c r="D140" s="10" t="n"/>
+      <c r="E140" s="12" t="n"/>
+      <c r="F140" s="10" t="n"/>
+      <c r="G140" s="10" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="8" t="n"/>
-      <c r="B141" s="12" t="n"/>
-      <c r="C141" s="12" t="n"/>
-      <c r="D141" s="12" t="n"/>
-      <c r="E141" s="14" t="n"/>
-      <c r="F141" s="12" t="n"/>
-      <c r="G141" s="12" t="n"/>
+      <c r="A141" s="6" t="n"/>
+      <c r="B141" s="10" t="n"/>
+      <c r="C141" s="10" t="n"/>
+      <c r="D141" s="10" t="n"/>
+      <c r="E141" s="12" t="n"/>
+      <c r="F141" s="10" t="n"/>
+      <c r="G141" s="10" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="8" t="n"/>
-      <c r="B142" s="12" t="n"/>
-      <c r="C142" s="12" t="n"/>
-      <c r="D142" s="12" t="n"/>
-      <c r="E142" s="14" t="n"/>
-      <c r="F142" s="12" t="n"/>
-      <c r="G142" s="12" t="n"/>
+      <c r="A142" s="6" t="n"/>
+      <c r="B142" s="10" t="n"/>
+      <c r="C142" s="10" t="n"/>
+      <c r="D142" s="10" t="n"/>
+      <c r="E142" s="12" t="n"/>
+      <c r="F142" s="10" t="n"/>
+      <c r="G142" s="10" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="8" t="n"/>
-      <c r="B143" s="12" t="n"/>
-      <c r="C143" s="12" t="n"/>
-      <c r="D143" s="12" t="n"/>
-      <c r="E143" s="14" t="n"/>
-      <c r="F143" s="12" t="n"/>
-      <c r="G143" s="12" t="n"/>
+      <c r="A143" s="6" t="n"/>
+      <c r="B143" s="10" t="n"/>
+      <c r="C143" s="10" t="n"/>
+      <c r="D143" s="10" t="n"/>
+      <c r="E143" s="12" t="n"/>
+      <c r="F143" s="10" t="n"/>
+      <c r="G143" s="10" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="8" t="n"/>
-      <c r="B144" s="12" t="n"/>
-      <c r="C144" s="12" t="n"/>
-      <c r="D144" s="12" t="n"/>
-      <c r="E144" s="14" t="n"/>
-      <c r="F144" s="12" t="n"/>
-      <c r="G144" s="12" t="n"/>
+      <c r="A144" s="6" t="n"/>
+      <c r="B144" s="10" t="n"/>
+      <c r="C144" s="10" t="n"/>
+      <c r="D144" s="10" t="n"/>
+      <c r="E144" s="12" t="n"/>
+      <c r="F144" s="10" t="n"/>
+      <c r="G144" s="10" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="8" t="n"/>
-      <c r="B145" s="12" t="n"/>
-      <c r="C145" s="12" t="n"/>
-      <c r="D145" s="12" t="n"/>
-      <c r="E145" s="14" t="n"/>
-      <c r="F145" s="12" t="n"/>
-      <c r="G145" s="12" t="n"/>
+      <c r="A145" s="6" t="n"/>
+      <c r="B145" s="10" t="n"/>
+      <c r="C145" s="10" t="n"/>
+      <c r="D145" s="10" t="n"/>
+      <c r="E145" s="12" t="n"/>
+      <c r="F145" s="10" t="n"/>
+      <c r="G145" s="10" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="8" t="n"/>
-      <c r="B146" s="12" t="n"/>
-      <c r="C146" s="12" t="n"/>
-      <c r="D146" s="12" t="n"/>
-      <c r="E146" s="14" t="n"/>
-      <c r="F146" s="12" t="n"/>
-      <c r="G146" s="12" t="n"/>
+      <c r="A146" s="6" t="n"/>
+      <c r="B146" s="10" t="n"/>
+      <c r="C146" s="10" t="n"/>
+      <c r="D146" s="10" t="n"/>
+      <c r="E146" s="12" t="n"/>
+      <c r="F146" s="10" t="n"/>
+      <c r="G146" s="10" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="8" t="n"/>
-      <c r="B147" s="12" t="n"/>
-      <c r="C147" s="12" t="n"/>
-      <c r="D147" s="12" t="n"/>
-      <c r="E147" s="14" t="n"/>
-      <c r="F147" s="12" t="n"/>
-      <c r="G147" s="12" t="n"/>
+      <c r="A147" s="6" t="n"/>
+      <c r="B147" s="10" t="n"/>
+      <c r="C147" s="10" t="n"/>
+      <c r="D147" s="10" t="n"/>
+      <c r="E147" s="12" t="n"/>
+      <c r="F147" s="10" t="n"/>
+      <c r="G147" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -4409,4 +4881,125 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>4 INDIAN BROOK ROAD — HOUSE TRACKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Purchase &amp; improvement history</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>What this is</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>One workbook that tracks what the house cost and every project that adds to it. Share it in Google Drive so both of you can edit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>Basis Tracker</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>Purchase price ($1,060,000, closing 7/17/2026) + closing costs + capital improvements = adjusted cost basis. Each project tab feeds one row of the improvements table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>2nd Floor Flooring</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>First project. Compare the 3 Floor &amp; Decor plank options (incl. underlayment, stair nose &amp; risers, 5% contractor discount, est. tax, and Footprints labor), pick one in 'Selected option' (yellow cell), and the budget fills in automatically. Log payments in the cost log at the bottom — actuals and the Basis Tracker update themselves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>Project Estimates</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>Preliminary phase: log each quote you collect (HVAC, carpentry, etc.) with its estimated cost, and mark Timing (Now / Later / Undecided / Passed) to decide what to take on. When a project is a go, give it its own tab from the template.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>Project Template</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>For the next project: right-click the tab &gt; Duplicate, rename it, fill in your options/quotes, then add a row in the Basis Tracker improvements table pointing at the new tab's cell C43 (its Actual total).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>Labor: Footprints Floors of Central MA proposal #25584 (6/30/2026) — $9,057.60, materials excluded. Materials: Floor &amp; Decor Waltham cart (7/2026) — Sapelo Shore / Big Sur / Gunstock Oak + Sentinel underlayment (15 rolls), plus 7 stair noses @ $29.99 and 13 risers @ $20; 5% contractor discount on materials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>In Google Sheets everything here — dropdowns, cross-tab formulas, formatting — survives File &gt; Import. Use 'Replace spreadsheet' when importing so tab references stay intact.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/4-Indian-Brook-House-Tracker.xlsx
+++ b/4-Indian-Brook-House-Tracker.xlsx
@@ -11,7 +11,10 @@
     <sheet name="2nd Floor Flooring" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Project Estimates" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Project Template" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Read Me" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Vendors &amp; Contacts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Finishes &amp; Materials" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Appliances &amp; Systems" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Read Me" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -193,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -256,6 +259,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -2746,7 +2752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2755,7 +2761,8 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2775,22 +2782,22 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Total estimated — all</t>
+          <t>Total estimated — counted quotes</t>
         </is>
       </c>
       <c r="B4" s="12">
-        <f>SUM(E9:E58)</f>
+        <f>SUMIFS(E9:E58,G9:G58,"Y")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Total estimated — marked Now</t>
+          <t>Total estimated — counted &amp; marked Now</t>
         </is>
       </c>
       <c r="B5" s="12">
-        <f>SUMIF(F9:F58,"Now",E9:E58)</f>
+        <f>SUMIFS(E9:E58,G9:G58,"Y",F9:F58,"Now")</f>
         <v/>
       </c>
     </row>
@@ -2833,6 +2840,11 @@
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Count?</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2853,7 +2865,12 @@
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="12" t="n"/>
       <c r="F9" s="10" t="n"/>
-      <c r="G9" s="10" t="n"/>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -2870,7 +2887,12 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="12" t="n"/>
       <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="n"/>
@@ -2879,7 +2901,8 @@
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="12" t="n"/>
       <c r="F11" s="10" t="n"/>
-      <c r="G11" s="10" t="n"/>
+      <c r="G11" s="23" t="n"/>
+      <c r="H11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n"/>
@@ -2888,7 +2911,8 @@
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="G12" s="23" t="n"/>
+      <c r="H12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n"/>
@@ -2897,7 +2921,8 @@
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="12" t="n"/>
       <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
+      <c r="G13" s="23" t="n"/>
+      <c r="H13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n"/>
@@ -2906,7 +2931,8 @@
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="12" t="n"/>
       <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="G14" s="23" t="n"/>
+      <c r="H14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n"/>
@@ -2915,7 +2941,8 @@
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="12" t="n"/>
       <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n"/>
@@ -2924,7 +2951,8 @@
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="12" t="n"/>
       <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
+      <c r="G16" s="23" t="n"/>
+      <c r="H16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n"/>
@@ -2933,7 +2961,8 @@
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="12" t="n"/>
       <c r="F17" s="10" t="n"/>
-      <c r="G17" s="10" t="n"/>
+      <c r="G17" s="23" t="n"/>
+      <c r="H17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n"/>
@@ -2942,7 +2971,8 @@
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="12" t="n"/>
       <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
+      <c r="G18" s="23" t="n"/>
+      <c r="H18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n"/>
@@ -2951,7 +2981,8 @@
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="12" t="n"/>
       <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
+      <c r="G19" s="23" t="n"/>
+      <c r="H19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n"/>
@@ -2960,7 +2991,8 @@
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="12" t="n"/>
       <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
+      <c r="G20" s="23" t="n"/>
+      <c r="H20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="n"/>
@@ -2969,7 +3001,8 @@
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="12" t="n"/>
       <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
+      <c r="G21" s="23" t="n"/>
+      <c r="H21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n"/>
@@ -2978,7 +3011,8 @@
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="12" t="n"/>
       <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
+      <c r="G22" s="23" t="n"/>
+      <c r="H22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n"/>
@@ -2987,7 +3021,8 @@
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="12" t="n"/>
       <c r="F23" s="10" t="n"/>
-      <c r="G23" s="10" t="n"/>
+      <c r="G23" s="23" t="n"/>
+      <c r="H23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n"/>
@@ -2996,7 +3031,8 @@
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="12" t="n"/>
       <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
+      <c r="G24" s="23" t="n"/>
+      <c r="H24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n"/>
@@ -3005,7 +3041,8 @@
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="12" t="n"/>
       <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
+      <c r="G25" s="23" t="n"/>
+      <c r="H25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n"/>
@@ -3014,7 +3051,8 @@
       <c r="D26" s="6" t="n"/>
       <c r="E26" s="12" t="n"/>
       <c r="F26" s="10" t="n"/>
-      <c r="G26" s="10" t="n"/>
+      <c r="G26" s="23" t="n"/>
+      <c r="H26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n"/>
@@ -3023,7 +3061,8 @@
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="12" t="n"/>
       <c r="F27" s="10" t="n"/>
-      <c r="G27" s="10" t="n"/>
+      <c r="G27" s="23" t="n"/>
+      <c r="H27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n"/>
@@ -3032,7 +3071,8 @@
       <c r="D28" s="6" t="n"/>
       <c r="E28" s="12" t="n"/>
       <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
+      <c r="G28" s="23" t="n"/>
+      <c r="H28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n"/>
@@ -3041,7 +3081,8 @@
       <c r="D29" s="6" t="n"/>
       <c r="E29" s="12" t="n"/>
       <c r="F29" s="10" t="n"/>
-      <c r="G29" s="10" t="n"/>
+      <c r="G29" s="23" t="n"/>
+      <c r="H29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n"/>
@@ -3050,7 +3091,8 @@
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="12" t="n"/>
       <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
+      <c r="G30" s="23" t="n"/>
+      <c r="H30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="n"/>
@@ -3059,7 +3101,8 @@
       <c r="D31" s="6" t="n"/>
       <c r="E31" s="12" t="n"/>
       <c r="F31" s="10" t="n"/>
-      <c r="G31" s="10" t="n"/>
+      <c r="G31" s="23" t="n"/>
+      <c r="H31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n"/>
@@ -3068,7 +3111,8 @@
       <c r="D32" s="6" t="n"/>
       <c r="E32" s="12" t="n"/>
       <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
+      <c r="G32" s="23" t="n"/>
+      <c r="H32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n"/>
@@ -3077,7 +3121,8 @@
       <c r="D33" s="6" t="n"/>
       <c r="E33" s="12" t="n"/>
       <c r="F33" s="10" t="n"/>
-      <c r="G33" s="10" t="n"/>
+      <c r="G33" s="23" t="n"/>
+      <c r="H33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n"/>
@@ -3086,7 +3131,8 @@
       <c r="D34" s="6" t="n"/>
       <c r="E34" s="12" t="n"/>
       <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
+      <c r="G34" s="23" t="n"/>
+      <c r="H34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n"/>
@@ -3095,7 +3141,8 @@
       <c r="D35" s="6" t="n"/>
       <c r="E35" s="12" t="n"/>
       <c r="F35" s="10" t="n"/>
-      <c r="G35" s="10" t="n"/>
+      <c r="G35" s="23" t="n"/>
+      <c r="H35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n"/>
@@ -3104,7 +3151,8 @@
       <c r="D36" s="6" t="n"/>
       <c r="E36" s="12" t="n"/>
       <c r="F36" s="10" t="n"/>
-      <c r="G36" s="10" t="n"/>
+      <c r="G36" s="23" t="n"/>
+      <c r="H36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n"/>
@@ -3113,7 +3161,8 @@
       <c r="D37" s="6" t="n"/>
       <c r="E37" s="12" t="n"/>
       <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
+      <c r="G37" s="23" t="n"/>
+      <c r="H37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n"/>
@@ -3122,7 +3171,8 @@
       <c r="D38" s="6" t="n"/>
       <c r="E38" s="12" t="n"/>
       <c r="F38" s="10" t="n"/>
-      <c r="G38" s="10" t="n"/>
+      <c r="G38" s="23" t="n"/>
+      <c r="H38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n"/>
@@ -3131,7 +3181,8 @@
       <c r="D39" s="6" t="n"/>
       <c r="E39" s="12" t="n"/>
       <c r="F39" s="10" t="n"/>
-      <c r="G39" s="10" t="n"/>
+      <c r="G39" s="23" t="n"/>
+      <c r="H39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="n"/>
@@ -3140,7 +3191,8 @@
       <c r="D40" s="6" t="n"/>
       <c r="E40" s="12" t="n"/>
       <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
+      <c r="G40" s="23" t="n"/>
+      <c r="H40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="n"/>
@@ -3149,7 +3201,8 @@
       <c r="D41" s="6" t="n"/>
       <c r="E41" s="12" t="n"/>
       <c r="F41" s="10" t="n"/>
-      <c r="G41" s="10" t="n"/>
+      <c r="G41" s="23" t="n"/>
+      <c r="H41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="n"/>
@@ -3158,7 +3211,8 @@
       <c r="D42" s="6" t="n"/>
       <c r="E42" s="12" t="n"/>
       <c r="F42" s="10" t="n"/>
-      <c r="G42" s="10" t="n"/>
+      <c r="G42" s="23" t="n"/>
+      <c r="H42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="n"/>
@@ -3167,7 +3221,8 @@
       <c r="D43" s="6" t="n"/>
       <c r="E43" s="12" t="n"/>
       <c r="F43" s="10" t="n"/>
-      <c r="G43" s="10" t="n"/>
+      <c r="G43" s="23" t="n"/>
+      <c r="H43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n"/>
@@ -3176,7 +3231,8 @@
       <c r="D44" s="6" t="n"/>
       <c r="E44" s="12" t="n"/>
       <c r="F44" s="10" t="n"/>
-      <c r="G44" s="10" t="n"/>
+      <c r="G44" s="23" t="n"/>
+      <c r="H44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="n"/>
@@ -3185,7 +3241,8 @@
       <c r="D45" s="6" t="n"/>
       <c r="E45" s="12" t="n"/>
       <c r="F45" s="10" t="n"/>
-      <c r="G45" s="10" t="n"/>
+      <c r="G45" s="23" t="n"/>
+      <c r="H45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="n"/>
@@ -3194,7 +3251,8 @@
       <c r="D46" s="6" t="n"/>
       <c r="E46" s="12" t="n"/>
       <c r="F46" s="10" t="n"/>
-      <c r="G46" s="10" t="n"/>
+      <c r="G46" s="23" t="n"/>
+      <c r="H46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="n"/>
@@ -3203,7 +3261,8 @@
       <c r="D47" s="6" t="n"/>
       <c r="E47" s="12" t="n"/>
       <c r="F47" s="10" t="n"/>
-      <c r="G47" s="10" t="n"/>
+      <c r="G47" s="23" t="n"/>
+      <c r="H47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="n"/>
@@ -3212,7 +3271,8 @@
       <c r="D48" s="6" t="n"/>
       <c r="E48" s="12" t="n"/>
       <c r="F48" s="10" t="n"/>
-      <c r="G48" s="10" t="n"/>
+      <c r="G48" s="23" t="n"/>
+      <c r="H48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="n"/>
@@ -3221,7 +3281,8 @@
       <c r="D49" s="6" t="n"/>
       <c r="E49" s="12" t="n"/>
       <c r="F49" s="10" t="n"/>
-      <c r="G49" s="10" t="n"/>
+      <c r="G49" s="23" t="n"/>
+      <c r="H49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="n"/>
@@ -3230,7 +3291,8 @@
       <c r="D50" s="6" t="n"/>
       <c r="E50" s="12" t="n"/>
       <c r="F50" s="10" t="n"/>
-      <c r="G50" s="10" t="n"/>
+      <c r="G50" s="23" t="n"/>
+      <c r="H50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="n"/>
@@ -3239,7 +3301,8 @@
       <c r="D51" s="6" t="n"/>
       <c r="E51" s="12" t="n"/>
       <c r="F51" s="10" t="n"/>
-      <c r="G51" s="10" t="n"/>
+      <c r="G51" s="23" t="n"/>
+      <c r="H51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n"/>
@@ -3248,7 +3311,8 @@
       <c r="D52" s="6" t="n"/>
       <c r="E52" s="12" t="n"/>
       <c r="F52" s="10" t="n"/>
-      <c r="G52" s="10" t="n"/>
+      <c r="G52" s="23" t="n"/>
+      <c r="H52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="n"/>
@@ -3257,7 +3321,8 @@
       <c r="D53" s="6" t="n"/>
       <c r="E53" s="12" t="n"/>
       <c r="F53" s="10" t="n"/>
-      <c r="G53" s="10" t="n"/>
+      <c r="G53" s="23" t="n"/>
+      <c r="H53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="n"/>
@@ -3266,7 +3331,8 @@
       <c r="D54" s="6" t="n"/>
       <c r="E54" s="12" t="n"/>
       <c r="F54" s="10" t="n"/>
-      <c r="G54" s="10" t="n"/>
+      <c r="G54" s="23" t="n"/>
+      <c r="H54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="n"/>
@@ -3275,7 +3341,8 @@
       <c r="D55" s="6" t="n"/>
       <c r="E55" s="12" t="n"/>
       <c r="F55" s="10" t="n"/>
-      <c r="G55" s="10" t="n"/>
+      <c r="G55" s="23" t="n"/>
+      <c r="H55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="n"/>
@@ -3284,7 +3351,8 @@
       <c r="D56" s="6" t="n"/>
       <c r="E56" s="12" t="n"/>
       <c r="F56" s="10" t="n"/>
-      <c r="G56" s="10" t="n"/>
+      <c r="G56" s="23" t="n"/>
+      <c r="H56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n"/>
@@ -3293,7 +3361,8 @@
       <c r="D57" s="6" t="n"/>
       <c r="E57" s="12" t="n"/>
       <c r="F57" s="10" t="n"/>
-      <c r="G57" s="10" t="n"/>
+      <c r="G57" s="23" t="n"/>
+      <c r="H57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="n"/>
@@ -3302,17 +3371,21 @@
       <c r="D58" s="6" t="n"/>
       <c r="E58" s="12" t="n"/>
       <c r="F58" s="10" t="n"/>
-      <c r="G58" s="10" t="n"/>
+      <c r="G58" s="23" t="n"/>
+      <c r="H58" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Now,Later,Undecided,Passed"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4886,11 +4959,1999 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00548235"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VENDORS &amp; CONTACTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>4 Indian Brook Road, Ashland, MA 01721</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>DIRECTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Trade / service</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Used for</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Use again?</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Footprints Floors of Central MA</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Flooring install</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>S. Donohoe</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>(508) 422-4545</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>sdonohoe@footprintsfloors.com</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>2nd floor flooring</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="n"/>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>ACS Custom Solutions Inc.; proposal #25584</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Floor &amp; Decor — Waltham</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Flooring materials</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>2nd floor flooring materials</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="n"/>
+      <c r="H7" s="10" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="10" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="23" t="n"/>
+      <c r="H9" s="10" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="23" t="n"/>
+      <c r="H10" s="10" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="23" t="n"/>
+      <c r="H11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="23" t="n"/>
+      <c r="H12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="23" t="n"/>
+      <c r="H13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="23" t="n"/>
+      <c r="H14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="23" t="n"/>
+      <c r="H16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="23" t="n"/>
+      <c r="H17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="23" t="n"/>
+      <c r="H18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="23" t="n"/>
+      <c r="H19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="23" t="n"/>
+      <c r="H20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="23" t="n"/>
+      <c r="H21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="23" t="n"/>
+      <c r="H22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="23" t="n"/>
+      <c r="H23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="23" t="n"/>
+      <c r="H24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="23" t="n"/>
+      <c r="H25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="23" t="n"/>
+      <c r="H26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="23" t="n"/>
+      <c r="H27" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="23" t="n"/>
+      <c r="H28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="23" t="n"/>
+      <c r="H29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="23" t="n"/>
+      <c r="H30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="23" t="n"/>
+      <c r="H31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="23" t="n"/>
+      <c r="H32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="23" t="n"/>
+      <c r="H33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="23" t="n"/>
+      <c r="H34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="23" t="n"/>
+      <c r="H35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="23" t="n"/>
+      <c r="H36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+      <c r="G37" s="23" t="n"/>
+      <c r="H37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="23" t="n"/>
+      <c r="H38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="23" t="n"/>
+      <c r="H39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="23" t="n"/>
+      <c r="H40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="23" t="n"/>
+      <c r="H41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="n"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="23" t="n"/>
+      <c r="H42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="23" t="n"/>
+      <c r="H43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="23" t="n"/>
+      <c r="H44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="n"/>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
+      <c r="G45" s="23" t="n"/>
+      <c r="H45" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00548235"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FINISHES &amp; MATERIALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>4 Indian Brook Road, Ashland, MA 01721</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>RECORD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Room / area</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Brand / product</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Color / finish</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>SKU / code</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Where purchased</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Second floor</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Flooring — LVP</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Floor &amp; Decor — Waltham</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="10" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="10" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="10" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="10" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="10" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="n"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="n"/>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="10" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="n"/>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="n"/>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="10" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="n"/>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="6" t="n"/>
+      <c r="H48" s="10" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="n"/>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="n"/>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="10" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="n"/>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="n"/>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="10" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="n"/>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="6" t="n"/>
+      <c r="H54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="n"/>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00548235"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>APPLIANCES &amp; SYSTEMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>4 Indian Brook Road, Ashland, MA 01721</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>INVENTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Make &amp; model</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Serial #</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Install date</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Warranty expires</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Typical lifespan (yrs)</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Suggested replacement</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Service cadence</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Last serviced</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Heating system (furnace / boiler)</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Basement</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" s="6">
+        <f>IF(OR(E6="",G6=""),"",EDATE(E6,12*G6))</f>
+        <v/>
+      </c>
+      <c r="I6" s="32" t="inlineStr">
+        <is>
+          <t>Annual tune-up; replace filters every 1-3 months (forced air)</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="10" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Central A/C / heat pump</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Exterior + attic</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" s="6">
+        <f>IF(OR(E7="",G7=""),"",EDATE(E7,12*G7))</f>
+        <v/>
+      </c>
+      <c r="I7" s="32" t="inlineStr">
+        <is>
+          <t>Annual tune-up; keep outdoor unit clear</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="10" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Water heater</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Basement</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" s="6">
+        <f>IF(OR(E8="",G8=""),"",EDATE(E8,12*G8))</f>
+        <v/>
+      </c>
+      <c r="I8" s="32" t="inlineStr">
+        <is>
+          <t>Flush tank annually; test T&amp;P valve</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="10" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Refrigerator</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="H9" s="6">
+        <f>IF(OR(E9="",G9=""),"",EDATE(E9,12*G9))</f>
+        <v/>
+      </c>
+      <c r="I9" s="32" t="inlineStr">
+        <is>
+          <t>Vacuum coils annually</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="10" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Range / oven</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="H10" s="6">
+        <f>IF(OR(E10="",G10=""),"",EDATE(E10,12*G10))</f>
+        <v/>
+      </c>
+      <c r="I10" s="32" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="10" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Dishwasher</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" s="6">
+        <f>IF(OR(E11="",G11=""),"",EDATE(E11,12*G11))</f>
+        <v/>
+      </c>
+      <c r="I11" s="32" t="inlineStr">
+        <is>
+          <t>Clean filter quarterly</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Microwave</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" s="6">
+        <f>IF(OR(E12="",G12=""),"",EDATE(E12,12*G12))</f>
+        <v/>
+      </c>
+      <c r="I12" s="32" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Washer</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Laundry</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="H13" s="6">
+        <f>IF(OR(E13="",G13=""),"",EDATE(E13,12*G13))</f>
+        <v/>
+      </c>
+      <c r="I13" s="32" t="inlineStr">
+        <is>
+          <t>Inspect supply hoses annually</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Dryer</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Laundry</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="H14" s="6">
+        <f>IF(OR(E14="",G14=""),"",EDATE(E14,12*G14))</f>
+        <v/>
+      </c>
+      <c r="I14" s="32" t="inlineStr">
+        <is>
+          <t>Clean vent duct annually; lint trap every load</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Garbage disposal</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" s="6">
+        <f>IF(OR(E15="",G15=""),"",EDATE(E15,12*G15))</f>
+        <v/>
+      </c>
+      <c r="I15" s="32" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Sump pump</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Basement</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" s="6">
+        <f>IF(OR(E16="",G16=""),"",EDATE(E16,12*G16))</f>
+        <v/>
+      </c>
+      <c r="I16" s="32" t="inlineStr">
+        <is>
+          <t>Test quarterly; check before spring thaw</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Roof (asphalt shingle)</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Exterior</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="H17" s="6">
+        <f>IF(OR(E17="",G17=""),"",EDATE(E17,12*G17))</f>
+        <v/>
+      </c>
+      <c r="I17" s="32" t="inlineStr">
+        <is>
+          <t>Inspect annually and after major storms</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Gutters &amp; downspouts</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Exterior</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" s="6">
+        <f>IF(OR(E18="",G18=""),"",EDATE(E18,12*G18))</f>
+        <v/>
+      </c>
+      <c r="I18" s="32" t="inlineStr">
+        <is>
+          <t>Clean spring and fall</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Whole house</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" s="6">
+        <f>IF(OR(E19="",G19=""),"",EDATE(E19,12*G19))</f>
+        <v/>
+      </c>
+      <c r="I19" s="32" t="inlineStr">
+        <is>
+          <t>Check seals/caulk annually</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Deck / porch</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Exterior</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" s="6">
+        <f>IF(OR(E20="",G20=""),"",EDATE(E20,12*G20))</f>
+        <v/>
+      </c>
+      <c r="I20" s="32" t="inlineStr">
+        <is>
+          <t>Reseal or restain every 2-3 years</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Garage door &amp; opener</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="H21" s="6">
+        <f>IF(OR(E21="",G21=""),"",EDATE(E21,12*G21))</f>
+        <v/>
+      </c>
+      <c r="I21" s="32" t="inlineStr">
+        <is>
+          <t>Lubricate tracks/rollers annually</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Smoke / CO detectors</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Whole house</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" s="6">
+        <f>IF(OR(E22="",G22=""),"",EDATE(E22,12*G22))</f>
+        <v/>
+      </c>
+      <c r="I22" s="32" t="inlineStr">
+        <is>
+          <t>Test monthly; replace batteries annually</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Septic system (if applicable)</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Exterior</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" s="6">
+        <f>IF(OR(E23="",G23=""),"",EDATE(E23,12*G23))</f>
+        <v/>
+      </c>
+      <c r="I23" s="32" t="inlineStr">
+        <is>
+          <t>Pump every 2-3 years; Title 5 inspection at sale</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Irrigation system (if applicable)</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Exterior</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" s="6">
+        <f>IF(OR(E24="",G24=""),"",EDATE(E24,12*G24))</f>
+        <v/>
+      </c>
+      <c r="I24" s="32" t="inlineStr">
+        <is>
+          <t>Winterize every fall; startup check in spring</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="23" t="n"/>
+      <c r="H25" s="6">
+        <f>IF(OR(E25="",G25=""),"",EDATE(E25,12*G25))</f>
+        <v/>
+      </c>
+      <c r="I25" s="32" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="23" t="n"/>
+      <c r="H26" s="6">
+        <f>IF(OR(E26="",G26=""),"",EDATE(E26,12*G26))</f>
+        <v/>
+      </c>
+      <c r="I26" s="32" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="23" t="n"/>
+      <c r="H27" s="6">
+        <f>IF(OR(E27="",G27=""),"",EDATE(E27,12*G27))</f>
+        <v/>
+      </c>
+      <c r="I27" s="32" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="23" t="n"/>
+      <c r="H28" s="6">
+        <f>IF(OR(E28="",G28=""),"",EDATE(E28,12*G28))</f>
+        <v/>
+      </c>
+      <c r="I28" s="32" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="23" t="n"/>
+      <c r="H29" s="6">
+        <f>IF(OR(E29="",G29=""),"",EDATE(E29,12*G29))</f>
+        <v/>
+      </c>
+      <c r="I29" s="32" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="23" t="n"/>
+      <c r="H30" s="6">
+        <f>IF(OR(E30="",G30=""),"",EDATE(E30,12*G30))</f>
+        <v/>
+      </c>
+      <c r="I30" s="32" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="23" t="n"/>
+      <c r="H31" s="6">
+        <f>IF(OR(E31="",G31=""),"",EDATE(E31,12*G31))</f>
+        <v/>
+      </c>
+      <c r="I31" s="32" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="23" t="n"/>
+      <c r="H32" s="6">
+        <f>IF(OR(E32="",G32=""),"",EDATE(E32,12*G32))</f>
+        <v/>
+      </c>
+      <c r="I32" s="32" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="23" t="n"/>
+      <c r="H33" s="6">
+        <f>IF(OR(E33="",G33=""),"",EDATE(E33,12*G33))</f>
+        <v/>
+      </c>
+      <c r="I33" s="32" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="23" t="n"/>
+      <c r="H34" s="6">
+        <f>IF(OR(E34="",G34=""),"",EDATE(E34,12*G34))</f>
+        <v/>
+      </c>
+      <c r="I34" s="32" t="n"/>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="23" t="n"/>
+      <c r="H35" s="6">
+        <f>IF(OR(E35="",G35=""),"",EDATE(E35,12*G35))</f>
+        <v/>
+      </c>
+      <c r="I35" s="32" t="n"/>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A4:K4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4912,84 +6973,120 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>What this is</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>One workbook that tracks what the house cost and every project that adds to it. Share it in Google Drive so both of you can edit.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>Basis Tracker</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Purchase price ($1,060,000, closing 7/17/2026) + closing costs + capital improvements = adjusted cost basis. Each project tab feeds one row of the improvements table.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>2nd Floor Flooring</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>First project. Compare the 3 Floor &amp; Decor plank options (incl. underlayment, stair nose &amp; risers, 5% contractor discount, est. tax, and Footprints labor), pick one in 'Selected option' (yellow cell), and the budget fills in automatically. Log payments in the cost log at the bottom — actuals and the Basis Tracker update themselves.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="32" t="inlineStr">
+    <row r="8" ht="75" customHeight="1">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>Project Estimates</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>Preliminary phase: log each quote you collect (HVAC, carpentry, etc.) with its estimated cost, and mark Timing (Now / Later / Undecided / Passed) to decide what to take on. When a project is a go, give it its own tab from the template.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>Preliminary phase: log each quote you collect (HVAC, carpentry, etc.) with its estimated cost, and mark Timing (Now / Later / Undecided / Passed) to decide what to take on. Set Count? to Y on the one quote per project you'd actually use — competing quotes marked N stay listed but don't double-count in the totals. When a project is a go, give it its own tab from the template.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>Vendors &amp; Contacts</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>Directory of contractors, suppliers, and service companies used on the house.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>Finishes &amp; Materials</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>Room-by-room record of paint colors, flooring, fixtures, and their SKUs — for touch-ups and matching repairs later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>Appliances &amp; Systems</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>Inventory of the house's equipment with make/model/serial, warranty dates, and service cadence. Enter an install date and the suggested replacement date computes from the typical lifespan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>Project Template</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>For the next project: right-click the tab &gt; Duplicate, rename it, fill in your options/quotes, then add a row in the Basis Tracker improvements table pointing at the new tab's cell C43 (its Actual total).</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="32" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Labor: Footprints Floors of Central MA proposal #25584 (6/30/2026) — $9,057.60, materials excluded. Materials: Floor &amp; Decor Waltham cart (7/2026) — Sapelo Shore / Big Sur / Gunstock Oak + Sentinel underlayment (15 rolls), plus 7 stair noses @ $29.99 and 13 risers @ $20; 5% contractor discount on materials.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="32" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>In Google Sheets everything here — dropdowns, cross-tab formulas, formatting — survives File &gt; Import. Use 'Replace spreadsheet' when importing so tab references stay intact.</t>
         </is>

--- a/4-Indian-Brook-House-Tracker.xlsx
+++ b/4-Indian-Brook-House-Tracker.xlsx
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="E21" s="12">
-        <f>'2nd Floor Flooring'!C43</f>
+        <f>'2nd Floor Flooring'!C41</f>
         <v/>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>All Floor &amp; Decor. Sapelo Shore &amp; Big Sur: waterproof hybrid resilient plank w/ cork pad, 8mm 7"x51". Gunstock Oak: waterproof rigid core LVP.</t>
+          <t>All Floor &amp; Decor. Sapelo Shore &amp; Big Sur: waterproof hybrid resilient plank w/ cork pad, 8mm 7"x51". Gunstock Oak: waterproof rigid core LVP. Underlayment attached — no separate order.</t>
         </is>
       </c>
       <c r="F14" s="8" t="n"/>
@@ -1273,24 +1273,24 @@
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>Underlayment &amp; supplies</t>
+          <t>Stair nose trim</t>
         </is>
       </c>
       <c r="B18" s="25">
-        <f>15*59.99</f>
+        <f>7*29.99</f>
         <v/>
       </c>
       <c r="C18" s="25">
-        <f>15*59.99</f>
+        <f>7*29.99</f>
         <v/>
       </c>
       <c r="D18" s="25">
-        <f>15*59.99</f>
+        <f>7*29.99</f>
         <v/>
       </c>
       <c r="E18" s="24" t="inlineStr">
         <is>
-          <t>Sentinel Protect Plus underlayment — 15 rolls x $59.99 (100 sqft each).</t>
+          <t>7 stair noses x $29.99.</t>
         </is>
       </c>
       <c r="F18" s="8" t="n"/>
@@ -1299,24 +1299,24 @@
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>Stair nose trim</t>
+          <t>Stair risers</t>
         </is>
       </c>
       <c r="B19" s="25">
-        <f>7*29.99</f>
+        <f>13*20</f>
         <v/>
       </c>
       <c r="C19" s="25">
-        <f>7*29.99</f>
+        <f>13*20</f>
         <v/>
       </c>
       <c r="D19" s="25">
-        <f>7*29.99</f>
+        <f>13*20</f>
         <v/>
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>7 stair noses x $29.99.</t>
+          <t>13 risers x $20.00.</t>
         </is>
       </c>
       <c r="F19" s="8" t="n"/>
@@ -1325,24 +1325,24 @@
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>Stair risers</t>
+          <t>Contractor discount on materials (5%)</t>
         </is>
       </c>
       <c r="B20" s="25">
-        <f>13*20</f>
+        <f>-0.05*SUM(B17:B19)</f>
         <v/>
       </c>
       <c r="C20" s="25">
-        <f>13*20</f>
+        <f>-0.05*SUM(C17:C19)</f>
         <v/>
       </c>
       <c r="D20" s="25">
-        <f>13*20</f>
+        <f>-0.05*SUM(D17:D19)</f>
         <v/>
       </c>
       <c r="E20" s="24" t="inlineStr">
         <is>
-          <t>13 risers x $20.00.</t>
+          <t>5% off all materials through the flooring contractor.</t>
         </is>
       </c>
       <c r="F20" s="8" t="n"/>
@@ -1351,67 +1351,64 @@
     <row r="21">
       <c r="A21" s="22" t="inlineStr">
         <is>
-          <t>Contractor discount on materials (5%)</t>
+          <t>Est. sales tax (6.25% MA, materials)</t>
         </is>
       </c>
       <c r="B21" s="25">
-        <f>-0.05*SUM(B17:B20)</f>
+        <f>SUM(B17:B20)*0.0625</f>
         <v/>
       </c>
       <c r="C21" s="25">
-        <f>-0.05*SUM(C17:C20)</f>
+        <f>SUM(C17:C20)*0.0625</f>
         <v/>
       </c>
       <c r="D21" s="25">
-        <f>-0.05*SUM(D17:D20)</f>
-        <v/>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>5% off all materials through the flooring contractor.</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="9" t="n"/>
+        <f>SUM(D17:D20)*0.0625</f>
+        <v/>
+      </c>
+      <c r="E21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>Est. sales tax (6.25% MA, materials)</t>
-        </is>
-      </c>
-      <c r="B22" s="25">
-        <f>SUM(B17:B21)*0.0625</f>
-        <v/>
-      </c>
-      <c r="C22" s="25">
-        <f>SUM(C17:C21)*0.0625</f>
-        <v/>
-      </c>
-      <c r="D22" s="25">
-        <f>SUM(D17:D21)*0.0625</f>
-        <v/>
-      </c>
-      <c r="E22" s="10" t="n"/>
+          <t>Labor — demo &amp; disposal</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="n">
+        <v>2642.3</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>2642.3</v>
+      </c>
+      <c r="D22" s="25" t="n">
+        <v>2642.3</v>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>Footprints: demo carpet, remove &amp; return baseboards, trash removal.</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="22" t="inlineStr">
         <is>
-          <t>Labor — demo &amp; disposal</t>
+          <t>Labor — install</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
-        <v>2642.3</v>
+        <v>4535.3</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>2642.3</v>
+        <v>4535.3</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>2642.3</v>
+        <v>4535.3</v>
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>Footprints: demo carpet, remove &amp; return baseboards, trash removal.</t>
+          <t>Footprints: install click-lock floating floor.</t>
         </is>
       </c>
       <c r="F23" s="8" t="n"/>
@@ -1420,124 +1417,120 @@
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>Labor — install</t>
+          <t>Labor — stairs (treads &amp; risers)</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
-        <v>4535.3</v>
+        <v>1880</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>4535.3</v>
+        <v>1880</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>4535.3</v>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
-        <is>
-          <t>Footprints: install click-lock floating floor.</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="9" t="n"/>
+        <v>1880</v>
+      </c>
+      <c r="E24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
-        <is>
-          <t>Labor — stairs (treads &amp; risers)</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="n">
-        <v>1880</v>
-      </c>
-      <c r="C25" s="25" t="n">
-        <v>1880</v>
-      </c>
-      <c r="D25" s="25" t="n">
-        <v>1880</v>
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>TOTAL ESTIMATED</t>
+        </is>
+      </c>
+      <c r="B25" s="28">
+        <f>SUM(B17:B24)</f>
+        <v/>
+      </c>
+      <c r="C25" s="28">
+        <f>SUM(C17:C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="28">
+        <f>SUM(D17:D24)</f>
+        <v/>
       </c>
       <c r="E25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
-        <is>
-          <t>TOTAL ESTIMATED</t>
-        </is>
-      </c>
-      <c r="B26" s="28">
-        <f>SUM(B17:B25)</f>
-        <v/>
-      </c>
-      <c r="C26" s="28">
-        <f>SUM(C17:C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="28">
-        <f>SUM(D17:D25)</f>
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>Premium vs. cheapest option</t>
+        </is>
+      </c>
+      <c r="B26" s="30">
+        <f>B25-MIN($B$25:$D$25)</f>
+        <v/>
+      </c>
+      <c r="C26" s="30">
+        <f>C25-MIN($B$25:$D$25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="30">
+        <f>D25-MIN($B$25:$D$25)</f>
         <v/>
       </c>
       <c r="E26" s="10" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="29" t="inlineStr">
-        <is>
-          <t>Premium vs. cheapest option</t>
-        </is>
-      </c>
-      <c r="B27" s="30">
-        <f>B26-MIN($B$26:$D$26)</f>
-        <v/>
-      </c>
-      <c r="C27" s="30">
-        <f>C26-MIN($B$26:$D$26)</f>
-        <v/>
-      </c>
-      <c r="D27" s="30">
-        <f>D26-MIN($B$26:$D$26)</f>
-        <v/>
-      </c>
-      <c r="E27" s="10" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>BUDGET vs. ACTUAL</t>
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Flooring materials</t>
+        </is>
+      </c>
+      <c r="B30" s="12">
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,5,FALSE))</f>
+        <v/>
+      </c>
+      <c r="C30" s="12">
+        <f>SUMIF($D$46:$D$145,$A30,$E$46:$E$145)</f>
+        <v/>
+      </c>
+      <c r="D30" s="12">
+        <f>IF(B30="","",B30-C30)</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Flooring materials</t>
+          <t>Stair nose trim</t>
         </is>
       </c>
       <c r="B31" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,5,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,6,FALSE))</f>
         <v/>
       </c>
       <c r="C31" s="12">
-        <f>SUMIF($D$48:$D$147,$A31,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A31,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D31" s="12">
@@ -1548,15 +1541,15 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Underlayment &amp; supplies</t>
+          <t>Stair risers</t>
         </is>
       </c>
       <c r="B32" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,6,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,7,FALSE))</f>
         <v/>
       </c>
       <c r="C32" s="12">
-        <f>SUMIF($D$48:$D$147,$A32,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A32,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D32" s="12">
@@ -1567,15 +1560,15 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>Stair nose trim</t>
+          <t>Contractor discount</t>
         </is>
       </c>
       <c r="B33" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,7,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,8,FALSE))</f>
         <v/>
       </c>
       <c r="C33" s="12">
-        <f>SUMIF($D$48:$D$147,$A33,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A33,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D33" s="12">
@@ -1586,15 +1579,15 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Stair risers</t>
+          <t>Sales tax</t>
         </is>
       </c>
       <c r="B34" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,8,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,9,FALSE))</f>
         <v/>
       </c>
       <c r="C34" s="12">
-        <f>SUMIF($D$48:$D$147,$A34,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A34,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D34" s="12">
@@ -1605,15 +1598,15 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Contractor discount</t>
+          <t>Labor — demo &amp; disposal</t>
         </is>
       </c>
       <c r="B35" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,9,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,10,FALSE))</f>
         <v/>
       </c>
       <c r="C35" s="12">
-        <f>SUMIF($D$48:$D$147,$A35,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A35,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D35" s="12">
@@ -1624,15 +1617,15 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Sales tax</t>
+          <t>Labor — install</t>
         </is>
       </c>
       <c r="B36" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,10,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,11,FALSE))</f>
         <v/>
       </c>
       <c r="C36" s="12">
-        <f>SUMIF($D$48:$D$147,$A36,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A36,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D36" s="12">
@@ -1643,15 +1636,15 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>Labor — demo &amp; disposal</t>
+          <t>Labor — stairs</t>
         </is>
       </c>
       <c r="B37" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,11,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,12,FALSE))</f>
         <v/>
       </c>
       <c r="C37" s="12">
-        <f>SUMIF($D$48:$D$147,$A37,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A37,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D37" s="12">
@@ -1662,15 +1655,12 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Labor — install</t>
-        </is>
-      </c>
-      <c r="B38" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,12,FALSE))</f>
-        <v/>
-      </c>
+          <t>Permits &amp; fees</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n"/>
       <c r="C38" s="12">
-        <f>SUMIF($D$48:$D$147,$A38,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A38,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D38" s="12">
@@ -1681,15 +1671,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Labor — stairs</t>
-        </is>
-      </c>
-      <c r="B39" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,13,FALSE))</f>
-        <v/>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="n"/>
       <c r="C39" s="12">
-        <f>SUMIF($D$48:$D$147,$A39,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A39,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D39" s="12">
@@ -1700,113 +1687,99 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Permits &amp; fees</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="n"/>
-      <c r="C40" s="12">
-        <f>SUMIF($D$48:$D$147,$A40,$E$48:$E$147)</f>
-        <v/>
-      </c>
+          <t>Contingency</t>
+        </is>
+      </c>
+      <c r="B40" s="12">
+        <f>SUM(B30:B39)*$B$9</f>
+        <v/>
+      </c>
+      <c r="C40" s="12" t="n"/>
       <c r="D40" s="12">
-        <f>IF(B40="","",B40-C40)</f>
+        <f>B40-C40</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="12">
-        <f>SUMIF($D$48:$D$147,$A41,$E$48:$E$147)</f>
-        <v/>
-      </c>
-      <c r="D41" s="12">
-        <f>IF(B41="","",B41-C41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>Contingency</t>
-        </is>
-      </c>
-      <c r="B42" s="12">
-        <f>SUM(B31:B41)*$B$9</f>
-        <v/>
-      </c>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="12">
-        <f>B42-C42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="27" t="inlineStr">
+      <c r="A41" s="27" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B43" s="31">
-        <f>SUM(B31:B42)</f>
-        <v/>
-      </c>
-      <c r="C43" s="31">
-        <f>SUM(C31:C42)</f>
-        <v/>
-      </c>
-      <c r="D43" s="31">
-        <f>B43-C43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="B41" s="31">
+        <f>SUM(B30:B40)</f>
+        <v/>
+      </c>
+      <c r="C41" s="31">
+        <f>SUM(C30:C40)</f>
+        <v/>
+      </c>
+      <c r="D41" s="31">
+        <f>B41-C41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>COST LOG</t>
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Payment method</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+    </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>Payment method</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
+      <c r="A47" s="6" t="n"/>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -2690,45 +2663,26 @@
       <c r="F145" s="10" t="n"/>
       <c r="G145" s="10" t="n"/>
     </row>
-    <row r="146">
-      <c r="A146" s="6" t="n"/>
-      <c r="B146" s="10" t="n"/>
-      <c r="C146" s="10" t="n"/>
-      <c r="D146" s="10" t="n"/>
-      <c r="E146" s="12" t="n"/>
-      <c r="F146" s="10" t="n"/>
-      <c r="G146" s="10" t="n"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="6" t="n"/>
-      <c r="B147" s="10" t="n"/>
-      <c r="C147" s="10" t="n"/>
-      <c r="D147" s="10" t="n"/>
-      <c r="E147" s="12" t="n"/>
-      <c r="F147" s="10" t="n"/>
-      <c r="G147" s="10" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="18">
+    <mergeCell ref="A44:G44"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="B8:F8"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A46:G46"/>
-    <mergeCell ref="E24:G24"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="E14:G14"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B10:F10"/>
     <mergeCell ref="E23:G23"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
     <mergeCell ref="E20:G20"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2737,8 +2691,8 @@
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=$B$13:$D$13</formula1>
     </dataValidation>
-    <dataValidation sqref="D48 D49 D50 D51 D52 D53 D54 D55 D56 D57 D58 D59 D60 D61 D62 D63 D64 D65 D66 D67 D68 D69 D70 D71 D72 D73 D74 D75 D76 D77 D78 D79 D80 D81 D82 D83 D84 D85 D86 D87 D88 D89 D90 D91 D92 D93 D94 D95 D96 D97 D98 D99 D100 D101 D102 D103 D104 D105 D106 D107 D108 D109 D110 D111 D112 D113 D114 D115 D116 D117 D118 D119 D120 D121 D122 D123 D124 D125 D126 D127 D128 D129 D130 D131 D132 D133 D134 D135 D136 D137 D138 D139 D140 D141 D142 D143 D144 D145 D146 D147" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=$A$31:$A$41</formula1>
+    <dataValidation sqref="D46 D47 D48 D49 D50 D51 D52 D53 D54 D55 D56 D57 D58 D59 D60 D61 D62 D63 D64 D65 D66 D67 D68 D69 D70 D71 D72 D73 D74 D75 D76 D77 D78 D79 D80 D81 D82 D83 D84 D85 D86 D87 D88 D89 D90 D91 D92 D93 D94 D95 D96 D97 D98 D99 D100 D101 D102 D103 D104 D105 D106 D107 D108 D109 D110 D111 D112 D113 D114 D115 D116 D117 D118 D119 D120 D121 D122 D123 D124 D125 D126 D127 D128 D129 D130 D131 D132 D133 D134 D135 D136 D137 D138 D139 D140 D141 D142 D143 D144 D145" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=$A$30:$A$39</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3399,7 +3353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3572,7 +3526,7 @@
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>Underlayment &amp; supplies</t>
+          <t>Stair nose trim</t>
         </is>
       </c>
       <c r="B18" s="25" t="inlineStr"/>
@@ -3583,7 +3537,7 @@
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>Stair nose trim</t>
+          <t>Stair risers</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr"/>
@@ -3594,30 +3548,39 @@
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>Stair risers</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="inlineStr"/>
-      <c r="C20" s="25" t="inlineStr"/>
-      <c r="D20" s="25" t="inlineStr"/>
+          <t>Contractor discount on materials (0%)</t>
+        </is>
+      </c>
+      <c r="B20" s="25">
+        <f>-0.0*SUM(B17:B19)</f>
+        <v/>
+      </c>
+      <c r="C20" s="25">
+        <f>-0.0*SUM(C17:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="25">
+        <f>-0.0*SUM(D17:D19)</f>
+        <v/>
+      </c>
       <c r="E20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="22" t="inlineStr">
         <is>
-          <t>Contractor discount on materials (0%)</t>
+          <t>Est. sales tax (6.25% MA, materials)</t>
         </is>
       </c>
       <c r="B21" s="25">
-        <f>-0.0*SUM(B17:B20)</f>
+        <f>SUM(B17:B20)*0.0625</f>
         <v/>
       </c>
       <c r="C21" s="25">
-        <f>-0.0*SUM(C17:C20)</f>
+        <f>SUM(C17:C20)*0.0625</f>
         <v/>
       </c>
       <c r="D21" s="25">
-        <f>-0.0*SUM(D17:D20)</f>
+        <f>SUM(D17:D20)*0.0625</f>
         <v/>
       </c>
       <c r="E21" s="10" t="n"/>
@@ -3625,27 +3588,18 @@
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>Est. sales tax (6.25% MA, materials)</t>
-        </is>
-      </c>
-      <c r="B22" s="25">
-        <f>SUM(B17:B21)*0.0625</f>
-        <v/>
-      </c>
-      <c r="C22" s="25">
-        <f>SUM(C17:C21)*0.0625</f>
-        <v/>
-      </c>
-      <c r="D22" s="25">
-        <f>SUM(D17:D21)*0.0625</f>
-        <v/>
-      </c>
+          <t>Labor — demo &amp; disposal</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr"/>
+      <c r="C22" s="25" t="inlineStr"/>
+      <c r="D22" s="25" t="inlineStr"/>
       <c r="E22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="22" t="inlineStr">
         <is>
-          <t>Labor — demo &amp; disposal</t>
+          <t>Labor — install</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr"/>
@@ -3656,7 +3610,7 @@
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>Labor — install</t>
+          <t>Labor — stairs (treads &amp; risers)</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr"/>
@@ -3665,97 +3619,105 @@
       <c r="E24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
-        <is>
-          <t>Labor — stairs (treads &amp; risers)</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr"/>
-      <c r="C25" s="25" t="inlineStr"/>
-      <c r="D25" s="25" t="inlineStr"/>
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>TOTAL ESTIMATED</t>
+        </is>
+      </c>
+      <c r="B25" s="28">
+        <f>SUM(B17:B24)</f>
+        <v/>
+      </c>
+      <c r="C25" s="28">
+        <f>SUM(C17:C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="28">
+        <f>SUM(D17:D24)</f>
+        <v/>
+      </c>
       <c r="E25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
-        <is>
-          <t>TOTAL ESTIMATED</t>
-        </is>
-      </c>
-      <c r="B26" s="28">
-        <f>SUM(B17:B25)</f>
-        <v/>
-      </c>
-      <c r="C26" s="28">
-        <f>SUM(C17:C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="28">
-        <f>SUM(D17:D25)</f>
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>Premium vs. cheapest option</t>
+        </is>
+      </c>
+      <c r="B26" s="30">
+        <f>B25-MIN($B$25:$D$25)</f>
+        <v/>
+      </c>
+      <c r="C26" s="30">
+        <f>C25-MIN($B$25:$D$25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="30">
+        <f>D25-MIN($B$25:$D$25)</f>
         <v/>
       </c>
       <c r="E26" s="10" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="29" t="inlineStr">
-        <is>
-          <t>Premium vs. cheapest option</t>
-        </is>
-      </c>
-      <c r="B27" s="30">
-        <f>B26-MIN($B$26:$D$26)</f>
-        <v/>
-      </c>
-      <c r="C27" s="30">
-        <f>C26-MIN($B$26:$D$26)</f>
-        <v/>
-      </c>
-      <c r="D27" s="30">
-        <f>D26-MIN($B$26:$D$26)</f>
-        <v/>
-      </c>
-      <c r="E27" s="10" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>BUDGET vs. ACTUAL</t>
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Flooring materials</t>
+        </is>
+      </c>
+      <c r="B30" s="12">
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,5,FALSE))</f>
+        <v/>
+      </c>
+      <c r="C30" s="12">
+        <f>SUMIF($D$46:$D$145,$A30,$E$46:$E$145)</f>
+        <v/>
+      </c>
+      <c r="D30" s="12">
+        <f>IF(B30="","",B30-C30)</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Flooring materials</t>
+          <t>Stair nose trim</t>
         </is>
       </c>
       <c r="B31" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,5,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,6,FALSE))</f>
         <v/>
       </c>
       <c r="C31" s="12">
-        <f>SUMIF($D$48:$D$147,$A31,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A31,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D31" s="12">
@@ -3766,15 +3728,15 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Underlayment &amp; supplies</t>
+          <t>Stair risers</t>
         </is>
       </c>
       <c r="B32" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,6,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,7,FALSE))</f>
         <v/>
       </c>
       <c r="C32" s="12">
-        <f>SUMIF($D$48:$D$147,$A32,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A32,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D32" s="12">
@@ -3785,15 +3747,15 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>Stair nose trim</t>
+          <t>Contractor discount</t>
         </is>
       </c>
       <c r="B33" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,7,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,8,FALSE))</f>
         <v/>
       </c>
       <c r="C33" s="12">
-        <f>SUMIF($D$48:$D$147,$A33,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A33,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D33" s="12">
@@ -3804,15 +3766,15 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Stair risers</t>
+          <t>Sales tax</t>
         </is>
       </c>
       <c r="B34" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,8,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,9,FALSE))</f>
         <v/>
       </c>
       <c r="C34" s="12">
-        <f>SUMIF($D$48:$D$147,$A34,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A34,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D34" s="12">
@@ -3823,15 +3785,15 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Contractor discount</t>
+          <t>Labor — demo &amp; disposal</t>
         </is>
       </c>
       <c r="B35" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,9,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,10,FALSE))</f>
         <v/>
       </c>
       <c r="C35" s="12">
-        <f>SUMIF($D$48:$D$147,$A35,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A35,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D35" s="12">
@@ -3842,15 +3804,15 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Sales tax</t>
+          <t>Labor — install</t>
         </is>
       </c>
       <c r="B36" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,10,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,11,FALSE))</f>
         <v/>
       </c>
       <c r="C36" s="12">
-        <f>SUMIF($D$48:$D$147,$A36,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A36,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D36" s="12">
@@ -3861,15 +3823,15 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>Labor — demo &amp; disposal</t>
+          <t>Labor — stairs</t>
         </is>
       </c>
       <c r="B37" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,11,FALSE))</f>
+        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,12,FALSE))</f>
         <v/>
       </c>
       <c r="C37" s="12">
-        <f>SUMIF($D$48:$D$147,$A37,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A37,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D37" s="12">
@@ -3880,15 +3842,12 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Labor — install</t>
-        </is>
-      </c>
-      <c r="B38" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,12,FALSE))</f>
-        <v/>
-      </c>
+          <t>Permits &amp; fees</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n"/>
       <c r="C38" s="12">
-        <f>SUMIF($D$48:$D$147,$A38,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A38,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D38" s="12">
@@ -3899,15 +3858,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Labor — stairs</t>
-        </is>
-      </c>
-      <c r="B39" s="12">
-        <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$26,13,FALSE))</f>
-        <v/>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="n"/>
       <c r="C39" s="12">
-        <f>SUMIF($D$48:$D$147,$A39,$E$48:$E$147)</f>
+        <f>SUMIF($D$46:$D$145,$A39,$E$46:$E$145)</f>
         <v/>
       </c>
       <c r="D39" s="12">
@@ -3918,113 +3874,99 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Permits &amp; fees</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="n"/>
-      <c r="C40" s="12">
-        <f>SUMIF($D$48:$D$147,$A40,$E$48:$E$147)</f>
-        <v/>
-      </c>
+          <t>Contingency</t>
+        </is>
+      </c>
+      <c r="B40" s="12">
+        <f>SUM(B30:B39)*$B$9</f>
+        <v/>
+      </c>
+      <c r="C40" s="12" t="n"/>
       <c r="D40" s="12">
-        <f>IF(B40="","",B40-C40)</f>
+        <f>B40-C40</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="12">
-        <f>SUMIF($D$48:$D$147,$A41,$E$48:$E$147)</f>
-        <v/>
-      </c>
-      <c r="D41" s="12">
-        <f>IF(B41="","",B41-C41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>Contingency</t>
-        </is>
-      </c>
-      <c r="B42" s="12">
-        <f>SUM(B31:B41)*$B$9</f>
-        <v/>
-      </c>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="12">
-        <f>B42-C42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="27" t="inlineStr">
+      <c r="A41" s="27" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B43" s="31">
-        <f>SUM(B31:B42)</f>
-        <v/>
-      </c>
-      <c r="C43" s="31">
-        <f>SUM(C31:C42)</f>
-        <v/>
-      </c>
-      <c r="D43" s="31">
-        <f>B43-C43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="B41" s="31">
+        <f>SUM(B30:B40)</f>
+        <v/>
+      </c>
+      <c r="C41" s="31">
+        <f>SUM(C30:C40)</f>
+        <v/>
+      </c>
+      <c r="D41" s="31">
+        <f>B41-C41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>COST LOG</t>
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Payment method</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+    </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>Payment method</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
+      <c r="A47" s="6" t="n"/>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -4908,26 +4850,9 @@
       <c r="F145" s="10" t="n"/>
       <c r="G145" s="10" t="n"/>
     </row>
-    <row r="146">
-      <c r="A146" s="6" t="n"/>
-      <c r="B146" s="10" t="n"/>
-      <c r="C146" s="10" t="n"/>
-      <c r="D146" s="10" t="n"/>
-      <c r="E146" s="12" t="n"/>
-      <c r="F146" s="10" t="n"/>
-      <c r="G146" s="10" t="n"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="6" t="n"/>
-      <c r="B147" s="10" t="n"/>
-      <c r="C147" s="10" t="n"/>
-      <c r="D147" s="10" t="n"/>
-      <c r="E147" s="12" t="n"/>
-      <c r="F147" s="10" t="n"/>
-      <c r="G147" s="10" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A44:G44"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B6:F6"/>
@@ -4936,10 +4861,9 @@
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A29:G29"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -4948,8 +4872,8 @@
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=$B$13:$D$13</formula1>
     </dataValidation>
-    <dataValidation sqref="D48 D49 D50 D51 D52 D53 D54 D55 D56 D57 D58 D59 D60 D61 D62 D63 D64 D65 D66 D67 D68 D69 D70 D71 D72 D73 D74 D75 D76 D77 D78 D79 D80 D81 D82 D83 D84 D85 D86 D87 D88 D89 D90 D91 D92 D93 D94 D95 D96 D97 D98 D99 D100 D101 D102 D103 D104 D105 D106 D107 D108 D109 D110 D111 D112 D113 D114 D115 D116 D117 D118 D119 D120 D121 D122 D123 D124 D125 D126 D127 D128 D129 D130 D131 D132 D133 D134 D135 D136 D137 D138 D139 D140 D141 D142 D143 D144 D145 D146 D147" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=$A$31:$A$41</formula1>
+    <dataValidation sqref="D46 D47 D48 D49 D50 D51 D52 D53 D54 D55 D56 D57 D58 D59 D60 D61 D62 D63 D64 D65 D66 D67 D68 D69 D70 D71 D72 D73 D74 D75 D76 D77 D78 D79 D80 D81 D82 D83 D84 D85 D86 D87 D88 D89 D90 D91 D92 D93 D94 D95 D96 D97 D98 D99 D100 D101 D102 D103 D104 D105 D106 D107 D108 D109 D110 D111 D112 D113 D114 D115 D116 D117 D118 D119 D120 D121 D122 D123 D124 D125 D126 D127 D128 D129 D130 D131 D132 D133 D134 D135 D136 D137 D138 D139 D140 D141 D142 D143 D144 D145" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=$A$30:$A$39</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7004,7 +6928,7 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>First project. Compare the 3 Floor &amp; Decor plank options (incl. underlayment, stair nose &amp; risers, 5% contractor discount, est. tax, and Footprints labor), pick one in 'Selected option' (yellow cell), and the budget fills in automatically. Log payments in the cost log at the bottom — actuals and the Basis Tracker update themselves.</t>
+          <t>First project. Compare the 3 Floor &amp; Decor plank options (incl. stair nose &amp; risers, 5% contractor discount, est. tax, and Footprints labor), pick one in 'Selected option' (yellow cell), and the budget fills in automatically. Log payments in the cost log at the bottom — actuals and the Basis Tracker update themselves.</t>
         </is>
       </c>
     </row>
@@ -7064,7 +6988,7 @@
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>For the next project: right-click the tab &gt; Duplicate, rename it, fill in your options/quotes, then add a row in the Basis Tracker improvements table pointing at the new tab's cell C43 (its Actual total).</t>
+          <t>For the next project: right-click the tab &gt; Duplicate, rename it, fill in your options/quotes, then add a row in the Basis Tracker improvements table pointing at the new tab's cell C41 (its Actual total).</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7000,7 @@
       </c>
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t>Labor: Footprints Floors of Central MA proposal #25584 (6/30/2026) — $9,057.60, materials excluded. Materials: Floor &amp; Decor Waltham cart (7/2026) — Sapelo Shore / Big Sur / Gunstock Oak + Sentinel underlayment (15 rolls), plus 7 stair noses @ $29.99 and 13 risers @ $20; 5% contractor discount on materials.</t>
+          <t>Labor: Footprints Floors of Central MA proposal #25584 (6/30/2026) — $9,057.60, materials excluded. Materials: Floor &amp; Decor Waltham cart (7/2026) — Sapelo Shore / Big Sur / Gunstock Oak (underlayment attached to plank), plus 7 stair noses @ $29.99 and 13 risers @ $20; 5% contractor discount on materials.</t>
         </is>
       </c>
     </row>

--- a/4-Indian-Brook-House-Tracker.xlsx
+++ b/4-Indian-Brook-House-Tracker.xlsx
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -214,14 +214,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -238,9 +242,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -632,12 +633,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -687,7 +688,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>ACQUISITION COSTS</t>
+          <t>CLOSING COSTS  (borrower-paid, per Closing Disclosure 7/13/2026)</t>
         </is>
       </c>
     </row>
@@ -704,342 +705,793 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
+          <t>Adds to basis? (Y/N)</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Purchase price</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>1060000</v>
-      </c>
-      <c r="C10" s="11" t="inlineStr"/>
-      <c r="D10" s="8" t="n"/>
+          <t>Loan underwriting fee</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>795</v>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Loan cost</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Attorney / legal fees</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="11" t="inlineStr"/>
-      <c r="D11" s="8" t="n"/>
+          <t>Appraisal fee</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>750</v>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Loan cost</t>
+        </is>
+      </c>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Owner's title insurance</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="11" t="inlineStr"/>
-      <c r="D12" s="8" t="n"/>
+          <t>Credit report</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>319</v>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Loan cost</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Recording fees</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="11" t="inlineStr"/>
-      <c r="D13" s="8" t="n"/>
+          <t>Flood certification</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Loan cost</t>
+        </is>
+      </c>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Survey / plot plan</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="11" t="inlineStr"/>
-      <c r="D14" s="8" t="n"/>
+          <t>Loan Safe report</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Loan cost</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Transfer taxes paid by buyer (if any)</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="11" t="inlineStr"/>
-      <c r="D15" s="8" t="n"/>
+          <t>Lender's title insurance</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>1988</v>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Loan cost — protects lender</t>
+        </is>
+      </c>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Other closing costs added to basis</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="11" t="inlineStr"/>
-      <c r="D16" s="8" t="n"/>
+          <t>Closing protection letter</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Title service</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="9" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Subtotal — acquisition basis</t>
-        </is>
-      </c>
-      <c r="B17" s="14">
-        <f>SUM(B10:B16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Courier fee (FedEx)</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Settlement service</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Document preparation fee</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Deed / document prep</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>E-recording fee</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Recording</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Municipal lien certificate</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Title — Town of Ashland</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Plot plan / survey</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Survey — Boston Survey</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Settlement fee</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>700</v>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Settlement / closing</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Title examination</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>325</v>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Recording fee — deed</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>155</v>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>Deed recording</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Recording fee — mortgage</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>205</v>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Loan cost</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Recording fee — additional</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Balance of the $480 gov't recording line</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Owner's title insurance</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>3222</v>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Owner's policy (optional)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Homeowner's insurance (12 mo, prepaid)</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>3951</v>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>Prepaid — not basis</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Prepaid interest (7/17–8/1)</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>2082.75</v>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Prepaid loan interest</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Property taxes (3 mo, prepaid)</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>2922.51</v>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Prepaid — not basis</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Property taxes escrow (2 mo)</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>1948.34</v>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Escrow deposit — not basis</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Total closing costs (borrower-paid)</t>
+        </is>
+      </c>
+      <c r="B32" s="11">
+        <f>SUM(B10:B31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Closing costs added to basis</t>
+        </is>
+      </c>
+      <c r="B33" s="15">
+        <f>SUMIF(C10:C31,"Y",B10:B31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>ACQUISITION BASIS  (purchase price + basis closing costs)</t>
+        </is>
+      </c>
+      <c r="B35" s="15">
+        <f>B5+B33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>CAPITAL IMPROVEMENTS</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Date completed</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Where tracked</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>Capital? (Y/N)</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>Second floor flooring</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Tab: 2nd Floor Flooring</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E21" s="12">
-        <f>'2nd Floor Flooring'!C41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="12" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="12" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="12" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="12" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="12" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="12" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="12" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="12" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="12" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="12" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="12" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="n"/>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="12" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="12" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="12" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="12" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="n"/>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="12" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="n"/>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="12" t="n"/>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Second floor flooring</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Tab: 2nd Floor Flooring</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E39" s="11">
+        <f>'2nd Floor Flooring'!C41</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="10" t="n"/>
       <c r="D40" s="10" t="n"/>
-      <c r="E40" s="12" t="n"/>
+      <c r="E40" s="11" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="6" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="11" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="11" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="11" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="11" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n"/>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="11" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="11" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n"/>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="11" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n"/>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="11" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="11" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n"/>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="11" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="11" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n"/>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="11" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n"/>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="11" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n"/>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="11" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n"/>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="11" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n"/>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="11" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n"/>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="11" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n"/>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="11" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>Subtotal — capital improvements</t>
         </is>
       </c>
-      <c r="E41" s="14">
-        <f>SUMIF(D21:D40,"Y",E21:E40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="E59" s="15">
+        <f>SUMIF(D39:D58,"Y",E39:E58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="16" t="inlineStr">
         <is>
           <t>ADJUSTED COST BASIS</t>
         </is>
       </c>
-      <c r="D43" s="16">
-        <f>B17+E41</f>
-        <v/>
-      </c>
-      <c r="E43" s="9" t="n"/>
+      <c r="D61" s="17">
+        <f>B35+E59</f>
+        <v/>
+      </c>
+      <c r="E61" s="9" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>Seller-paid items (MA deed excise $4,856.40, realtor commissions $63,900, attorney's fees, etc.) are excluded. The Adds-to-basis flags are a starting point — confirm with your tax preparer.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="C13:F13"/>
+  <mergeCells count="32">
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="A35"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D16:F16"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D31:F31"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D21:F21"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 D39 D40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 D52 D53 D54 D55 D56 D57 D58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1093,7 +1545,7 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Quoting</t>
         </is>
@@ -1105,7 +1557,7 @@
           <t>Contractor / quote</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Footprints Floors of Central MA (ACS Custom Solutions Inc.) — Proposal #25584, 6/30/2026. Labor only; 50% deposit ($4,528.80) before work, balance on completion.</t>
         </is>
@@ -1117,7 +1569,7 @@
           <t>Materials source</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Floor &amp; Decor, Waltham MA (cart re-priced 7/2026); 5% materials discount through flooring contractor</t>
         </is>
@@ -1129,7 +1581,7 @@
           <t>Selected option</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n"/>
+      <c r="B8" s="20" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1137,7 +1589,7 @@
           <t>Contingency %</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="21" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1147,7 +1599,7 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Labor quote excludes materials. Subfloor leveling/remediation not included and may add cost once carpet is removed. 3% fee on credit card payments (max $3,000/card per project).</t>
         </is>
@@ -1166,17 +1618,17 @@
           <t>Cost component</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>Sapelo Shore</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Big Sur</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>Gunstock Oak</t>
         </is>
@@ -1188,27 +1640,27 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Item # / SKU</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>101128890</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>101069698</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>101068104</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>All Floor &amp; Decor. Sapelo Shore &amp; Big Sur: waterproof hybrid resilient plank w/ cork pad, 8mm 7"x51". Gunstock Oak: waterproof rigid core LVP. Underlayment attached — no separate order.</t>
         </is>
@@ -1217,78 +1669,78 @@
       <c r="G14" s="9" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Price per box</t>
         </is>
       </c>
-      <c r="B15" s="25" t="n">
+      <c r="B15" s="26" t="n">
         <v>61.71</v>
       </c>
-      <c r="C15" s="25" t="n">
+      <c r="C15" s="26" t="n">
         <v>97.08</v>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="26" t="n">
         <v>75.56999999999999</v>
       </c>
       <c r="E15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>Boxes needed</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="27" t="n">
         <v>66</v>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="D16" s="26" t="n">
+      <c r="D16" s="27" t="n">
         <v>64</v>
       </c>
       <c r="E16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Flooring material</t>
         </is>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="26">
         <f>B15*B16</f>
         <v/>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="26">
         <f>C15*C16</f>
         <v/>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="26">
         <f>D15*D16</f>
         <v/>
       </c>
       <c r="E17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Stair nose trim</t>
         </is>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="26">
         <f>7*29.99</f>
         <v/>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="26">
         <f>7*29.99</f>
         <v/>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="26">
         <f>7*29.99</f>
         <v/>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>7 stair noses x $29.99.</t>
         </is>
@@ -1297,24 +1749,24 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>Stair risers</t>
         </is>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="26">
         <f>13*20</f>
         <v/>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="26">
         <f>13*20</f>
         <v/>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="26">
         <f>13*20</f>
         <v/>
       </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>13 risers x $20.00.</t>
         </is>
@@ -1323,24 +1775,24 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>Contractor discount on materials (5%)</t>
         </is>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="26">
         <f>-0.05*SUM(B17:B19)</f>
         <v/>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="26">
         <f>-0.05*SUM(C17:C19)</f>
         <v/>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="26">
         <f>-0.05*SUM(D17:D19)</f>
         <v/>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>5% off all materials through the flooring contractor.</t>
         </is>
@@ -1349,41 +1801,41 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Est. sales tax (6.25% MA, materials)</t>
         </is>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="26">
         <f>SUM(B17:B20)*0.0625</f>
         <v/>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="26">
         <f>SUM(C17:C20)*0.0625</f>
         <v/>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="26">
         <f>SUM(D17:D20)*0.0625</f>
         <v/>
       </c>
       <c r="E21" s="10" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>Labor — demo &amp; disposal</t>
         </is>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="26" t="n">
         <v>2642.3</v>
       </c>
-      <c r="C22" s="25" t="n">
+      <c r="C22" s="26" t="n">
         <v>2642.3</v>
       </c>
-      <c r="D22" s="25" t="n">
+      <c r="D22" s="26" t="n">
         <v>2642.3</v>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E22" s="25" t="inlineStr">
         <is>
           <t>Footprints: demo carpet, remove &amp; return baseboards, trash removal.</t>
         </is>
@@ -1392,21 +1844,21 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>Labor — install</t>
         </is>
       </c>
-      <c r="B23" s="25" t="n">
+      <c r="B23" s="26" t="n">
         <v>4535.3</v>
       </c>
-      <c r="C23" s="25" t="n">
+      <c r="C23" s="26" t="n">
         <v>4535.3</v>
       </c>
-      <c r="D23" s="25" t="n">
+      <c r="D23" s="26" t="n">
         <v>4535.3</v>
       </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>Footprints: install click-lock floating floor.</t>
         </is>
@@ -1415,57 +1867,57 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>Labor — stairs (treads &amp; risers)</t>
         </is>
       </c>
-      <c r="B24" s="25" t="n">
+      <c r="B24" s="26" t="n">
         <v>1880</v>
       </c>
-      <c r="C24" s="25" t="n">
+      <c r="C24" s="26" t="n">
         <v>1880</v>
       </c>
-      <c r="D24" s="25" t="n">
+      <c r="D24" s="26" t="n">
         <v>1880</v>
       </c>
       <c r="E24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>TOTAL ESTIMATED</t>
         </is>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="29">
         <f>SUM(B17:B24)</f>
         <v/>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="29">
         <f>SUM(C17:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="29">
         <f>SUM(D17:D24)</f>
         <v/>
       </c>
       <c r="E25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>Premium vs. cheapest option</t>
         </is>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="31">
         <f>B25-MIN($B$25:$D$25)</f>
         <v/>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="31">
         <f>C25-MIN($B$25:$D$25)</f>
         <v/>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="31">
         <f>D25-MIN($B$25:$D$25)</f>
         <v/>
       </c>
@@ -1506,15 +1958,15 @@
           <t>Flooring materials</t>
         </is>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="11">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,5,FALSE))</f>
         <v/>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="11">
         <f>SUMIF($D$46:$D$145,$A30,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="11">
         <f>IF(B30="","",B30-C30)</f>
         <v/>
       </c>
@@ -1525,15 +1977,15 @@
           <t>Stair nose trim</t>
         </is>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="11">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,6,FALSE))</f>
         <v/>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="11">
         <f>SUMIF($D$46:$D$145,$A31,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="11">
         <f>IF(B31="","",B31-C31)</f>
         <v/>
       </c>
@@ -1544,15 +1996,15 @@
           <t>Stair risers</t>
         </is>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="11">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,7,FALSE))</f>
         <v/>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="11">
         <f>SUMIF($D$46:$D$145,$A32,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="11">
         <f>IF(B32="","",B32-C32)</f>
         <v/>
       </c>
@@ -1563,15 +2015,15 @@
           <t>Contractor discount</t>
         </is>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="11">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,8,FALSE))</f>
         <v/>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="11">
         <f>SUMIF($D$46:$D$145,$A33,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="11">
         <f>IF(B33="","",B33-C33)</f>
         <v/>
       </c>
@@ -1582,15 +2034,15 @@
           <t>Sales tax</t>
         </is>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="11">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,9,FALSE))</f>
         <v/>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="11">
         <f>SUMIF($D$46:$D$145,$A34,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="11">
         <f>IF(B34="","",B34-C34)</f>
         <v/>
       </c>
@@ -1601,15 +2053,15 @@
           <t>Labor — demo &amp; disposal</t>
         </is>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="11">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,10,FALSE))</f>
         <v/>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="11">
         <f>SUMIF($D$46:$D$145,$A35,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="11">
         <f>IF(B35="","",B35-C35)</f>
         <v/>
       </c>
@@ -1620,15 +2072,15 @@
           <t>Labor — install</t>
         </is>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="11">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,11,FALSE))</f>
         <v/>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="11">
         <f>SUMIF($D$46:$D$145,$A36,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="11">
         <f>IF(B36="","",B36-C36)</f>
         <v/>
       </c>
@@ -1639,15 +2091,15 @@
           <t>Labor — stairs</t>
         </is>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="11">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,12,FALSE))</f>
         <v/>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="11">
         <f>SUMIF($D$46:$D$145,$A37,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="11">
         <f>IF(B37="","",B37-C37)</f>
         <v/>
       </c>
@@ -1658,12 +2110,12 @@
           <t>Permits &amp; fees</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12">
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11">
         <f>SUMIF($D$46:$D$145,$A38,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="11">
         <f>IF(B38="","",B38-C38)</f>
         <v/>
       </c>
@@ -1674,12 +2126,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12">
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11">
         <f>SUMIF($D$46:$D$145,$A39,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="11">
         <f>IF(B39="","",B39-C39)</f>
         <v/>
       </c>
@@ -1690,31 +2142,31 @@
           <t>Contingency</t>
         </is>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="11">
         <f>SUM(B30:B39)*$B$9</f>
         <v/>
       </c>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="12">
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11">
         <f>B40-C40</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="27" t="inlineStr">
+      <c r="A41" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B41" s="31">
+      <c r="B41" s="32">
         <f>SUM(B30:B40)</f>
         <v/>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="32">
         <f>SUM(C30:C40)</f>
         <v/>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="32">
         <f>B41-C41</f>
         <v/>
       </c>
@@ -1768,7 +2220,7 @@
       <c r="B46" s="10" t="n"/>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="10" t="n"/>
-      <c r="E46" s="12" t="n"/>
+      <c r="E46" s="11" t="n"/>
       <c r="F46" s="10" t="n"/>
       <c r="G46" s="10" t="n"/>
     </row>
@@ -1777,7 +2229,7 @@
       <c r="B47" s="10" t="n"/>
       <c r="C47" s="10" t="n"/>
       <c r="D47" s="10" t="n"/>
-      <c r="E47" s="12" t="n"/>
+      <c r="E47" s="11" t="n"/>
       <c r="F47" s="10" t="n"/>
       <c r="G47" s="10" t="n"/>
     </row>
@@ -1786,7 +2238,7 @@
       <c r="B48" s="10" t="n"/>
       <c r="C48" s="10" t="n"/>
       <c r="D48" s="10" t="n"/>
-      <c r="E48" s="12" t="n"/>
+      <c r="E48" s="11" t="n"/>
       <c r="F48" s="10" t="n"/>
       <c r="G48" s="10" t="n"/>
     </row>
@@ -1795,7 +2247,7 @@
       <c r="B49" s="10" t="n"/>
       <c r="C49" s="10" t="n"/>
       <c r="D49" s="10" t="n"/>
-      <c r="E49" s="12" t="n"/>
+      <c r="E49" s="11" t="n"/>
       <c r="F49" s="10" t="n"/>
       <c r="G49" s="10" t="n"/>
     </row>
@@ -1804,7 +2256,7 @@
       <c r="B50" s="10" t="n"/>
       <c r="C50" s="10" t="n"/>
       <c r="D50" s="10" t="n"/>
-      <c r="E50" s="12" t="n"/>
+      <c r="E50" s="11" t="n"/>
       <c r="F50" s="10" t="n"/>
       <c r="G50" s="10" t="n"/>
     </row>
@@ -1813,7 +2265,7 @@
       <c r="B51" s="10" t="n"/>
       <c r="C51" s="10" t="n"/>
       <c r="D51" s="10" t="n"/>
-      <c r="E51" s="12" t="n"/>
+      <c r="E51" s="11" t="n"/>
       <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
     </row>
@@ -1822,7 +2274,7 @@
       <c r="B52" s="10" t="n"/>
       <c r="C52" s="10" t="n"/>
       <c r="D52" s="10" t="n"/>
-      <c r="E52" s="12" t="n"/>
+      <c r="E52" s="11" t="n"/>
       <c r="F52" s="10" t="n"/>
       <c r="G52" s="10" t="n"/>
     </row>
@@ -1831,7 +2283,7 @@
       <c r="B53" s="10" t="n"/>
       <c r="C53" s="10" t="n"/>
       <c r="D53" s="10" t="n"/>
-      <c r="E53" s="12" t="n"/>
+      <c r="E53" s="11" t="n"/>
       <c r="F53" s="10" t="n"/>
       <c r="G53" s="10" t="n"/>
     </row>
@@ -1840,7 +2292,7 @@
       <c r="B54" s="10" t="n"/>
       <c r="C54" s="10" t="n"/>
       <c r="D54" s="10" t="n"/>
-      <c r="E54" s="12" t="n"/>
+      <c r="E54" s="11" t="n"/>
       <c r="F54" s="10" t="n"/>
       <c r="G54" s="10" t="n"/>
     </row>
@@ -1849,7 +2301,7 @@
       <c r="B55" s="10" t="n"/>
       <c r="C55" s="10" t="n"/>
       <c r="D55" s="10" t="n"/>
-      <c r="E55" s="12" t="n"/>
+      <c r="E55" s="11" t="n"/>
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
     </row>
@@ -1858,7 +2310,7 @@
       <c r="B56" s="10" t="n"/>
       <c r="C56" s="10" t="n"/>
       <c r="D56" s="10" t="n"/>
-      <c r="E56" s="12" t="n"/>
+      <c r="E56" s="11" t="n"/>
       <c r="F56" s="10" t="n"/>
       <c r="G56" s="10" t="n"/>
     </row>
@@ -1867,7 +2319,7 @@
       <c r="B57" s="10" t="n"/>
       <c r="C57" s="10" t="n"/>
       <c r="D57" s="10" t="n"/>
-      <c r="E57" s="12" t="n"/>
+      <c r="E57" s="11" t="n"/>
       <c r="F57" s="10" t="n"/>
       <c r="G57" s="10" t="n"/>
     </row>
@@ -1876,7 +2328,7 @@
       <c r="B58" s="10" t="n"/>
       <c r="C58" s="10" t="n"/>
       <c r="D58" s="10" t="n"/>
-      <c r="E58" s="12" t="n"/>
+      <c r="E58" s="11" t="n"/>
       <c r="F58" s="10" t="n"/>
       <c r="G58" s="10" t="n"/>
     </row>
@@ -1885,7 +2337,7 @@
       <c r="B59" s="10" t="n"/>
       <c r="C59" s="10" t="n"/>
       <c r="D59" s="10" t="n"/>
-      <c r="E59" s="12" t="n"/>
+      <c r="E59" s="11" t="n"/>
       <c r="F59" s="10" t="n"/>
       <c r="G59" s="10" t="n"/>
     </row>
@@ -1894,7 +2346,7 @@
       <c r="B60" s="10" t="n"/>
       <c r="C60" s="10" t="n"/>
       <c r="D60" s="10" t="n"/>
-      <c r="E60" s="12" t="n"/>
+      <c r="E60" s="11" t="n"/>
       <c r="F60" s="10" t="n"/>
       <c r="G60" s="10" t="n"/>
     </row>
@@ -1903,7 +2355,7 @@
       <c r="B61" s="10" t="n"/>
       <c r="C61" s="10" t="n"/>
       <c r="D61" s="10" t="n"/>
-      <c r="E61" s="12" t="n"/>
+      <c r="E61" s="11" t="n"/>
       <c r="F61" s="10" t="n"/>
       <c r="G61" s="10" t="n"/>
     </row>
@@ -1912,7 +2364,7 @@
       <c r="B62" s="10" t="n"/>
       <c r="C62" s="10" t="n"/>
       <c r="D62" s="10" t="n"/>
-      <c r="E62" s="12" t="n"/>
+      <c r="E62" s="11" t="n"/>
       <c r="F62" s="10" t="n"/>
       <c r="G62" s="10" t="n"/>
     </row>
@@ -1921,7 +2373,7 @@
       <c r="B63" s="10" t="n"/>
       <c r="C63" s="10" t="n"/>
       <c r="D63" s="10" t="n"/>
-      <c r="E63" s="12" t="n"/>
+      <c r="E63" s="11" t="n"/>
       <c r="F63" s="10" t="n"/>
       <c r="G63" s="10" t="n"/>
     </row>
@@ -1930,7 +2382,7 @@
       <c r="B64" s="10" t="n"/>
       <c r="C64" s="10" t="n"/>
       <c r="D64" s="10" t="n"/>
-      <c r="E64" s="12" t="n"/>
+      <c r="E64" s="11" t="n"/>
       <c r="F64" s="10" t="n"/>
       <c r="G64" s="10" t="n"/>
     </row>
@@ -1939,7 +2391,7 @@
       <c r="B65" s="10" t="n"/>
       <c r="C65" s="10" t="n"/>
       <c r="D65" s="10" t="n"/>
-      <c r="E65" s="12" t="n"/>
+      <c r="E65" s="11" t="n"/>
       <c r="F65" s="10" t="n"/>
       <c r="G65" s="10" t="n"/>
     </row>
@@ -1948,7 +2400,7 @@
       <c r="B66" s="10" t="n"/>
       <c r="C66" s="10" t="n"/>
       <c r="D66" s="10" t="n"/>
-      <c r="E66" s="12" t="n"/>
+      <c r="E66" s="11" t="n"/>
       <c r="F66" s="10" t="n"/>
       <c r="G66" s="10" t="n"/>
     </row>
@@ -1957,7 +2409,7 @@
       <c r="B67" s="10" t="n"/>
       <c r="C67" s="10" t="n"/>
       <c r="D67" s="10" t="n"/>
-      <c r="E67" s="12" t="n"/>
+      <c r="E67" s="11" t="n"/>
       <c r="F67" s="10" t="n"/>
       <c r="G67" s="10" t="n"/>
     </row>
@@ -1966,7 +2418,7 @@
       <c r="B68" s="10" t="n"/>
       <c r="C68" s="10" t="n"/>
       <c r="D68" s="10" t="n"/>
-      <c r="E68" s="12" t="n"/>
+      <c r="E68" s="11" t="n"/>
       <c r="F68" s="10" t="n"/>
       <c r="G68" s="10" t="n"/>
     </row>
@@ -1975,7 +2427,7 @@
       <c r="B69" s="10" t="n"/>
       <c r="C69" s="10" t="n"/>
       <c r="D69" s="10" t="n"/>
-      <c r="E69" s="12" t="n"/>
+      <c r="E69" s="11" t="n"/>
       <c r="F69" s="10" t="n"/>
       <c r="G69" s="10" t="n"/>
     </row>
@@ -1984,7 +2436,7 @@
       <c r="B70" s="10" t="n"/>
       <c r="C70" s="10" t="n"/>
       <c r="D70" s="10" t="n"/>
-      <c r="E70" s="12" t="n"/>
+      <c r="E70" s="11" t="n"/>
       <c r="F70" s="10" t="n"/>
       <c r="G70" s="10" t="n"/>
     </row>
@@ -1993,7 +2445,7 @@
       <c r="B71" s="10" t="n"/>
       <c r="C71" s="10" t="n"/>
       <c r="D71" s="10" t="n"/>
-      <c r="E71" s="12" t="n"/>
+      <c r="E71" s="11" t="n"/>
       <c r="F71" s="10" t="n"/>
       <c r="G71" s="10" t="n"/>
     </row>
@@ -2002,7 +2454,7 @@
       <c r="B72" s="10" t="n"/>
       <c r="C72" s="10" t="n"/>
       <c r="D72" s="10" t="n"/>
-      <c r="E72" s="12" t="n"/>
+      <c r="E72" s="11" t="n"/>
       <c r="F72" s="10" t="n"/>
       <c r="G72" s="10" t="n"/>
     </row>
@@ -2011,7 +2463,7 @@
       <c r="B73" s="10" t="n"/>
       <c r="C73" s="10" t="n"/>
       <c r="D73" s="10" t="n"/>
-      <c r="E73" s="12" t="n"/>
+      <c r="E73" s="11" t="n"/>
       <c r="F73" s="10" t="n"/>
       <c r="G73" s="10" t="n"/>
     </row>
@@ -2020,7 +2472,7 @@
       <c r="B74" s="10" t="n"/>
       <c r="C74" s="10" t="n"/>
       <c r="D74" s="10" t="n"/>
-      <c r="E74" s="12" t="n"/>
+      <c r="E74" s="11" t="n"/>
       <c r="F74" s="10" t="n"/>
       <c r="G74" s="10" t="n"/>
     </row>
@@ -2029,7 +2481,7 @@
       <c r="B75" s="10" t="n"/>
       <c r="C75" s="10" t="n"/>
       <c r="D75" s="10" t="n"/>
-      <c r="E75" s="12" t="n"/>
+      <c r="E75" s="11" t="n"/>
       <c r="F75" s="10" t="n"/>
       <c r="G75" s="10" t="n"/>
     </row>
@@ -2038,7 +2490,7 @@
       <c r="B76" s="10" t="n"/>
       <c r="C76" s="10" t="n"/>
       <c r="D76" s="10" t="n"/>
-      <c r="E76" s="12" t="n"/>
+      <c r="E76" s="11" t="n"/>
       <c r="F76" s="10" t="n"/>
       <c r="G76" s="10" t="n"/>
     </row>
@@ -2047,7 +2499,7 @@
       <c r="B77" s="10" t="n"/>
       <c r="C77" s="10" t="n"/>
       <c r="D77" s="10" t="n"/>
-      <c r="E77" s="12" t="n"/>
+      <c r="E77" s="11" t="n"/>
       <c r="F77" s="10" t="n"/>
       <c r="G77" s="10" t="n"/>
     </row>
@@ -2056,7 +2508,7 @@
       <c r="B78" s="10" t="n"/>
       <c r="C78" s="10" t="n"/>
       <c r="D78" s="10" t="n"/>
-      <c r="E78" s="12" t="n"/>
+      <c r="E78" s="11" t="n"/>
       <c r="F78" s="10" t="n"/>
       <c r="G78" s="10" t="n"/>
     </row>
@@ -2065,7 +2517,7 @@
       <c r="B79" s="10" t="n"/>
       <c r="C79" s="10" t="n"/>
       <c r="D79" s="10" t="n"/>
-      <c r="E79" s="12" t="n"/>
+      <c r="E79" s="11" t="n"/>
       <c r="F79" s="10" t="n"/>
       <c r="G79" s="10" t="n"/>
     </row>
@@ -2074,7 +2526,7 @@
       <c r="B80" s="10" t="n"/>
       <c r="C80" s="10" t="n"/>
       <c r="D80" s="10" t="n"/>
-      <c r="E80" s="12" t="n"/>
+      <c r="E80" s="11" t="n"/>
       <c r="F80" s="10" t="n"/>
       <c r="G80" s="10" t="n"/>
     </row>
@@ -2083,7 +2535,7 @@
       <c r="B81" s="10" t="n"/>
       <c r="C81" s="10" t="n"/>
       <c r="D81" s="10" t="n"/>
-      <c r="E81" s="12" t="n"/>
+      <c r="E81" s="11" t="n"/>
       <c r="F81" s="10" t="n"/>
       <c r="G81" s="10" t="n"/>
     </row>
@@ -2092,7 +2544,7 @@
       <c r="B82" s="10" t="n"/>
       <c r="C82" s="10" t="n"/>
       <c r="D82" s="10" t="n"/>
-      <c r="E82" s="12" t="n"/>
+      <c r="E82" s="11" t="n"/>
       <c r="F82" s="10" t="n"/>
       <c r="G82" s="10" t="n"/>
     </row>
@@ -2101,7 +2553,7 @@
       <c r="B83" s="10" t="n"/>
       <c r="C83" s="10" t="n"/>
       <c r="D83" s="10" t="n"/>
-      <c r="E83" s="12" t="n"/>
+      <c r="E83" s="11" t="n"/>
       <c r="F83" s="10" t="n"/>
       <c r="G83" s="10" t="n"/>
     </row>
@@ -2110,7 +2562,7 @@
       <c r="B84" s="10" t="n"/>
       <c r="C84" s="10" t="n"/>
       <c r="D84" s="10" t="n"/>
-      <c r="E84" s="12" t="n"/>
+      <c r="E84" s="11" t="n"/>
       <c r="F84" s="10" t="n"/>
       <c r="G84" s="10" t="n"/>
     </row>
@@ -2119,7 +2571,7 @@
       <c r="B85" s="10" t="n"/>
       <c r="C85" s="10" t="n"/>
       <c r="D85" s="10" t="n"/>
-      <c r="E85" s="12" t="n"/>
+      <c r="E85" s="11" t="n"/>
       <c r="F85" s="10" t="n"/>
       <c r="G85" s="10" t="n"/>
     </row>
@@ -2128,7 +2580,7 @@
       <c r="B86" s="10" t="n"/>
       <c r="C86" s="10" t="n"/>
       <c r="D86" s="10" t="n"/>
-      <c r="E86" s="12" t="n"/>
+      <c r="E86" s="11" t="n"/>
       <c r="F86" s="10" t="n"/>
       <c r="G86" s="10" t="n"/>
     </row>
@@ -2137,7 +2589,7 @@
       <c r="B87" s="10" t="n"/>
       <c r="C87" s="10" t="n"/>
       <c r="D87" s="10" t="n"/>
-      <c r="E87" s="12" t="n"/>
+      <c r="E87" s="11" t="n"/>
       <c r="F87" s="10" t="n"/>
       <c r="G87" s="10" t="n"/>
     </row>
@@ -2146,7 +2598,7 @@
       <c r="B88" s="10" t="n"/>
       <c r="C88" s="10" t="n"/>
       <c r="D88" s="10" t="n"/>
-      <c r="E88" s="12" t="n"/>
+      <c r="E88" s="11" t="n"/>
       <c r="F88" s="10" t="n"/>
       <c r="G88" s="10" t="n"/>
     </row>
@@ -2155,7 +2607,7 @@
       <c r="B89" s="10" t="n"/>
       <c r="C89" s="10" t="n"/>
       <c r="D89" s="10" t="n"/>
-      <c r="E89" s="12" t="n"/>
+      <c r="E89" s="11" t="n"/>
       <c r="F89" s="10" t="n"/>
       <c r="G89" s="10" t="n"/>
     </row>
@@ -2164,7 +2616,7 @@
       <c r="B90" s="10" t="n"/>
       <c r="C90" s="10" t="n"/>
       <c r="D90" s="10" t="n"/>
-      <c r="E90" s="12" t="n"/>
+      <c r="E90" s="11" t="n"/>
       <c r="F90" s="10" t="n"/>
       <c r="G90" s="10" t="n"/>
     </row>
@@ -2173,7 +2625,7 @@
       <c r="B91" s="10" t="n"/>
       <c r="C91" s="10" t="n"/>
       <c r="D91" s="10" t="n"/>
-      <c r="E91" s="12" t="n"/>
+      <c r="E91" s="11" t="n"/>
       <c r="F91" s="10" t="n"/>
       <c r="G91" s="10" t="n"/>
     </row>
@@ -2182,7 +2634,7 @@
       <c r="B92" s="10" t="n"/>
       <c r="C92" s="10" t="n"/>
       <c r="D92" s="10" t="n"/>
-      <c r="E92" s="12" t="n"/>
+      <c r="E92" s="11" t="n"/>
       <c r="F92" s="10" t="n"/>
       <c r="G92" s="10" t="n"/>
     </row>
@@ -2191,7 +2643,7 @@
       <c r="B93" s="10" t="n"/>
       <c r="C93" s="10" t="n"/>
       <c r="D93" s="10" t="n"/>
-      <c r="E93" s="12" t="n"/>
+      <c r="E93" s="11" t="n"/>
       <c r="F93" s="10" t="n"/>
       <c r="G93" s="10" t="n"/>
     </row>
@@ -2200,7 +2652,7 @@
       <c r="B94" s="10" t="n"/>
       <c r="C94" s="10" t="n"/>
       <c r="D94" s="10" t="n"/>
-      <c r="E94" s="12" t="n"/>
+      <c r="E94" s="11" t="n"/>
       <c r="F94" s="10" t="n"/>
       <c r="G94" s="10" t="n"/>
     </row>
@@ -2209,7 +2661,7 @@
       <c r="B95" s="10" t="n"/>
       <c r="C95" s="10" t="n"/>
       <c r="D95" s="10" t="n"/>
-      <c r="E95" s="12" t="n"/>
+      <c r="E95" s="11" t="n"/>
       <c r="F95" s="10" t="n"/>
       <c r="G95" s="10" t="n"/>
     </row>
@@ -2218,7 +2670,7 @@
       <c r="B96" s="10" t="n"/>
       <c r="C96" s="10" t="n"/>
       <c r="D96" s="10" t="n"/>
-      <c r="E96" s="12" t="n"/>
+      <c r="E96" s="11" t="n"/>
       <c r="F96" s="10" t="n"/>
       <c r="G96" s="10" t="n"/>
     </row>
@@ -2227,7 +2679,7 @@
       <c r="B97" s="10" t="n"/>
       <c r="C97" s="10" t="n"/>
       <c r="D97" s="10" t="n"/>
-      <c r="E97" s="12" t="n"/>
+      <c r="E97" s="11" t="n"/>
       <c r="F97" s="10" t="n"/>
       <c r="G97" s="10" t="n"/>
     </row>
@@ -2236,7 +2688,7 @@
       <c r="B98" s="10" t="n"/>
       <c r="C98" s="10" t="n"/>
       <c r="D98" s="10" t="n"/>
-      <c r="E98" s="12" t="n"/>
+      <c r="E98" s="11" t="n"/>
       <c r="F98" s="10" t="n"/>
       <c r="G98" s="10" t="n"/>
     </row>
@@ -2245,7 +2697,7 @@
       <c r="B99" s="10" t="n"/>
       <c r="C99" s="10" t="n"/>
       <c r="D99" s="10" t="n"/>
-      <c r="E99" s="12" t="n"/>
+      <c r="E99" s="11" t="n"/>
       <c r="F99" s="10" t="n"/>
       <c r="G99" s="10" t="n"/>
     </row>
@@ -2254,7 +2706,7 @@
       <c r="B100" s="10" t="n"/>
       <c r="C100" s="10" t="n"/>
       <c r="D100" s="10" t="n"/>
-      <c r="E100" s="12" t="n"/>
+      <c r="E100" s="11" t="n"/>
       <c r="F100" s="10" t="n"/>
       <c r="G100" s="10" t="n"/>
     </row>
@@ -2263,7 +2715,7 @@
       <c r="B101" s="10" t="n"/>
       <c r="C101" s="10" t="n"/>
       <c r="D101" s="10" t="n"/>
-      <c r="E101" s="12" t="n"/>
+      <c r="E101" s="11" t="n"/>
       <c r="F101" s="10" t="n"/>
       <c r="G101" s="10" t="n"/>
     </row>
@@ -2272,7 +2724,7 @@
       <c r="B102" s="10" t="n"/>
       <c r="C102" s="10" t="n"/>
       <c r="D102" s="10" t="n"/>
-      <c r="E102" s="12" t="n"/>
+      <c r="E102" s="11" t="n"/>
       <c r="F102" s="10" t="n"/>
       <c r="G102" s="10" t="n"/>
     </row>
@@ -2281,7 +2733,7 @@
       <c r="B103" s="10" t="n"/>
       <c r="C103" s="10" t="n"/>
       <c r="D103" s="10" t="n"/>
-      <c r="E103" s="12" t="n"/>
+      <c r="E103" s="11" t="n"/>
       <c r="F103" s="10" t="n"/>
       <c r="G103" s="10" t="n"/>
     </row>
@@ -2290,7 +2742,7 @@
       <c r="B104" s="10" t="n"/>
       <c r="C104" s="10" t="n"/>
       <c r="D104" s="10" t="n"/>
-      <c r="E104" s="12" t="n"/>
+      <c r="E104" s="11" t="n"/>
       <c r="F104" s="10" t="n"/>
       <c r="G104" s="10" t="n"/>
     </row>
@@ -2299,7 +2751,7 @@
       <c r="B105" s="10" t="n"/>
       <c r="C105" s="10" t="n"/>
       <c r="D105" s="10" t="n"/>
-      <c r="E105" s="12" t="n"/>
+      <c r="E105" s="11" t="n"/>
       <c r="F105" s="10" t="n"/>
       <c r="G105" s="10" t="n"/>
     </row>
@@ -2308,7 +2760,7 @@
       <c r="B106" s="10" t="n"/>
       <c r="C106" s="10" t="n"/>
       <c r="D106" s="10" t="n"/>
-      <c r="E106" s="12" t="n"/>
+      <c r="E106" s="11" t="n"/>
       <c r="F106" s="10" t="n"/>
       <c r="G106" s="10" t="n"/>
     </row>
@@ -2317,7 +2769,7 @@
       <c r="B107" s="10" t="n"/>
       <c r="C107" s="10" t="n"/>
       <c r="D107" s="10" t="n"/>
-      <c r="E107" s="12" t="n"/>
+      <c r="E107" s="11" t="n"/>
       <c r="F107" s="10" t="n"/>
       <c r="G107" s="10" t="n"/>
     </row>
@@ -2326,7 +2778,7 @@
       <c r="B108" s="10" t="n"/>
       <c r="C108" s="10" t="n"/>
       <c r="D108" s="10" t="n"/>
-      <c r="E108" s="12" t="n"/>
+      <c r="E108" s="11" t="n"/>
       <c r="F108" s="10" t="n"/>
       <c r="G108" s="10" t="n"/>
     </row>
@@ -2335,7 +2787,7 @@
       <c r="B109" s="10" t="n"/>
       <c r="C109" s="10" t="n"/>
       <c r="D109" s="10" t="n"/>
-      <c r="E109" s="12" t="n"/>
+      <c r="E109" s="11" t="n"/>
       <c r="F109" s="10" t="n"/>
       <c r="G109" s="10" t="n"/>
     </row>
@@ -2344,7 +2796,7 @@
       <c r="B110" s="10" t="n"/>
       <c r="C110" s="10" t="n"/>
       <c r="D110" s="10" t="n"/>
-      <c r="E110" s="12" t="n"/>
+      <c r="E110" s="11" t="n"/>
       <c r="F110" s="10" t="n"/>
       <c r="G110" s="10" t="n"/>
     </row>
@@ -2353,7 +2805,7 @@
       <c r="B111" s="10" t="n"/>
       <c r="C111" s="10" t="n"/>
       <c r="D111" s="10" t="n"/>
-      <c r="E111" s="12" t="n"/>
+      <c r="E111" s="11" t="n"/>
       <c r="F111" s="10" t="n"/>
       <c r="G111" s="10" t="n"/>
     </row>
@@ -2362,7 +2814,7 @@
       <c r="B112" s="10" t="n"/>
       <c r="C112" s="10" t="n"/>
       <c r="D112" s="10" t="n"/>
-      <c r="E112" s="12" t="n"/>
+      <c r="E112" s="11" t="n"/>
       <c r="F112" s="10" t="n"/>
       <c r="G112" s="10" t="n"/>
     </row>
@@ -2371,7 +2823,7 @@
       <c r="B113" s="10" t="n"/>
       <c r="C113" s="10" t="n"/>
       <c r="D113" s="10" t="n"/>
-      <c r="E113" s="12" t="n"/>
+      <c r="E113" s="11" t="n"/>
       <c r="F113" s="10" t="n"/>
       <c r="G113" s="10" t="n"/>
     </row>
@@ -2380,7 +2832,7 @@
       <c r="B114" s="10" t="n"/>
       <c r="C114" s="10" t="n"/>
       <c r="D114" s="10" t="n"/>
-      <c r="E114" s="12" t="n"/>
+      <c r="E114" s="11" t="n"/>
       <c r="F114" s="10" t="n"/>
       <c r="G114" s="10" t="n"/>
     </row>
@@ -2389,7 +2841,7 @@
       <c r="B115" s="10" t="n"/>
       <c r="C115" s="10" t="n"/>
       <c r="D115" s="10" t="n"/>
-      <c r="E115" s="12" t="n"/>
+      <c r="E115" s="11" t="n"/>
       <c r="F115" s="10" t="n"/>
       <c r="G115" s="10" t="n"/>
     </row>
@@ -2398,7 +2850,7 @@
       <c r="B116" s="10" t="n"/>
       <c r="C116" s="10" t="n"/>
       <c r="D116" s="10" t="n"/>
-      <c r="E116" s="12" t="n"/>
+      <c r="E116" s="11" t="n"/>
       <c r="F116" s="10" t="n"/>
       <c r="G116" s="10" t="n"/>
     </row>
@@ -2407,7 +2859,7 @@
       <c r="B117" s="10" t="n"/>
       <c r="C117" s="10" t="n"/>
       <c r="D117" s="10" t="n"/>
-      <c r="E117" s="12" t="n"/>
+      <c r="E117" s="11" t="n"/>
       <c r="F117" s="10" t="n"/>
       <c r="G117" s="10" t="n"/>
     </row>
@@ -2416,7 +2868,7 @@
       <c r="B118" s="10" t="n"/>
       <c r="C118" s="10" t="n"/>
       <c r="D118" s="10" t="n"/>
-      <c r="E118" s="12" t="n"/>
+      <c r="E118" s="11" t="n"/>
       <c r="F118" s="10" t="n"/>
       <c r="G118" s="10" t="n"/>
     </row>
@@ -2425,7 +2877,7 @@
       <c r="B119" s="10" t="n"/>
       <c r="C119" s="10" t="n"/>
       <c r="D119" s="10" t="n"/>
-      <c r="E119" s="12" t="n"/>
+      <c r="E119" s="11" t="n"/>
       <c r="F119" s="10" t="n"/>
       <c r="G119" s="10" t="n"/>
     </row>
@@ -2434,7 +2886,7 @@
       <c r="B120" s="10" t="n"/>
       <c r="C120" s="10" t="n"/>
       <c r="D120" s="10" t="n"/>
-      <c r="E120" s="12" t="n"/>
+      <c r="E120" s="11" t="n"/>
       <c r="F120" s="10" t="n"/>
       <c r="G120" s="10" t="n"/>
     </row>
@@ -2443,7 +2895,7 @@
       <c r="B121" s="10" t="n"/>
       <c r="C121" s="10" t="n"/>
       <c r="D121" s="10" t="n"/>
-      <c r="E121" s="12" t="n"/>
+      <c r="E121" s="11" t="n"/>
       <c r="F121" s="10" t="n"/>
       <c r="G121" s="10" t="n"/>
     </row>
@@ -2452,7 +2904,7 @@
       <c r="B122" s="10" t="n"/>
       <c r="C122" s="10" t="n"/>
       <c r="D122" s="10" t="n"/>
-      <c r="E122" s="12" t="n"/>
+      <c r="E122" s="11" t="n"/>
       <c r="F122" s="10" t="n"/>
       <c r="G122" s="10" t="n"/>
     </row>
@@ -2461,7 +2913,7 @@
       <c r="B123" s="10" t="n"/>
       <c r="C123" s="10" t="n"/>
       <c r="D123" s="10" t="n"/>
-      <c r="E123" s="12" t="n"/>
+      <c r="E123" s="11" t="n"/>
       <c r="F123" s="10" t="n"/>
       <c r="G123" s="10" t="n"/>
     </row>
@@ -2470,7 +2922,7 @@
       <c r="B124" s="10" t="n"/>
       <c r="C124" s="10" t="n"/>
       <c r="D124" s="10" t="n"/>
-      <c r="E124" s="12" t="n"/>
+      <c r="E124" s="11" t="n"/>
       <c r="F124" s="10" t="n"/>
       <c r="G124" s="10" t="n"/>
     </row>
@@ -2479,7 +2931,7 @@
       <c r="B125" s="10" t="n"/>
       <c r="C125" s="10" t="n"/>
       <c r="D125" s="10" t="n"/>
-      <c r="E125" s="12" t="n"/>
+      <c r="E125" s="11" t="n"/>
       <c r="F125" s="10" t="n"/>
       <c r="G125" s="10" t="n"/>
     </row>
@@ -2488,7 +2940,7 @@
       <c r="B126" s="10" t="n"/>
       <c r="C126" s="10" t="n"/>
       <c r="D126" s="10" t="n"/>
-      <c r="E126" s="12" t="n"/>
+      <c r="E126" s="11" t="n"/>
       <c r="F126" s="10" t="n"/>
       <c r="G126" s="10" t="n"/>
     </row>
@@ -2497,7 +2949,7 @@
       <c r="B127" s="10" t="n"/>
       <c r="C127" s="10" t="n"/>
       <c r="D127" s="10" t="n"/>
-      <c r="E127" s="12" t="n"/>
+      <c r="E127" s="11" t="n"/>
       <c r="F127" s="10" t="n"/>
       <c r="G127" s="10" t="n"/>
     </row>
@@ -2506,7 +2958,7 @@
       <c r="B128" s="10" t="n"/>
       <c r="C128" s="10" t="n"/>
       <c r="D128" s="10" t="n"/>
-      <c r="E128" s="12" t="n"/>
+      <c r="E128" s="11" t="n"/>
       <c r="F128" s="10" t="n"/>
       <c r="G128" s="10" t="n"/>
     </row>
@@ -2515,7 +2967,7 @@
       <c r="B129" s="10" t="n"/>
       <c r="C129" s="10" t="n"/>
       <c r="D129" s="10" t="n"/>
-      <c r="E129" s="12" t="n"/>
+      <c r="E129" s="11" t="n"/>
       <c r="F129" s="10" t="n"/>
       <c r="G129" s="10" t="n"/>
     </row>
@@ -2524,7 +2976,7 @@
       <c r="B130" s="10" t="n"/>
       <c r="C130" s="10" t="n"/>
       <c r="D130" s="10" t="n"/>
-      <c r="E130" s="12" t="n"/>
+      <c r="E130" s="11" t="n"/>
       <c r="F130" s="10" t="n"/>
       <c r="G130" s="10" t="n"/>
     </row>
@@ -2533,7 +2985,7 @@
       <c r="B131" s="10" t="n"/>
       <c r="C131" s="10" t="n"/>
       <c r="D131" s="10" t="n"/>
-      <c r="E131" s="12" t="n"/>
+      <c r="E131" s="11" t="n"/>
       <c r="F131" s="10" t="n"/>
       <c r="G131" s="10" t="n"/>
     </row>
@@ -2542,7 +2994,7 @@
       <c r="B132" s="10" t="n"/>
       <c r="C132" s="10" t="n"/>
       <c r="D132" s="10" t="n"/>
-      <c r="E132" s="12" t="n"/>
+      <c r="E132" s="11" t="n"/>
       <c r="F132" s="10" t="n"/>
       <c r="G132" s="10" t="n"/>
     </row>
@@ -2551,7 +3003,7 @@
       <c r="B133" s="10" t="n"/>
       <c r="C133" s="10" t="n"/>
       <c r="D133" s="10" t="n"/>
-      <c r="E133" s="12" t="n"/>
+      <c r="E133" s="11" t="n"/>
       <c r="F133" s="10" t="n"/>
       <c r="G133" s="10" t="n"/>
     </row>
@@ -2560,7 +3012,7 @@
       <c r="B134" s="10" t="n"/>
       <c r="C134" s="10" t="n"/>
       <c r="D134" s="10" t="n"/>
-      <c r="E134" s="12" t="n"/>
+      <c r="E134" s="11" t="n"/>
       <c r="F134" s="10" t="n"/>
       <c r="G134" s="10" t="n"/>
     </row>
@@ -2569,7 +3021,7 @@
       <c r="B135" s="10" t="n"/>
       <c r="C135" s="10" t="n"/>
       <c r="D135" s="10" t="n"/>
-      <c r="E135" s="12" t="n"/>
+      <c r="E135" s="11" t="n"/>
       <c r="F135" s="10" t="n"/>
       <c r="G135" s="10" t="n"/>
     </row>
@@ -2578,7 +3030,7 @@
       <c r="B136" s="10" t="n"/>
       <c r="C136" s="10" t="n"/>
       <c r="D136" s="10" t="n"/>
-      <c r="E136" s="12" t="n"/>
+      <c r="E136" s="11" t="n"/>
       <c r="F136" s="10" t="n"/>
       <c r="G136" s="10" t="n"/>
     </row>
@@ -2587,7 +3039,7 @@
       <c r="B137" s="10" t="n"/>
       <c r="C137" s="10" t="n"/>
       <c r="D137" s="10" t="n"/>
-      <c r="E137" s="12" t="n"/>
+      <c r="E137" s="11" t="n"/>
       <c r="F137" s="10" t="n"/>
       <c r="G137" s="10" t="n"/>
     </row>
@@ -2596,7 +3048,7 @@
       <c r="B138" s="10" t="n"/>
       <c r="C138" s="10" t="n"/>
       <c r="D138" s="10" t="n"/>
-      <c r="E138" s="12" t="n"/>
+      <c r="E138" s="11" t="n"/>
       <c r="F138" s="10" t="n"/>
       <c r="G138" s="10" t="n"/>
     </row>
@@ -2605,7 +3057,7 @@
       <c r="B139" s="10" t="n"/>
       <c r="C139" s="10" t="n"/>
       <c r="D139" s="10" t="n"/>
-      <c r="E139" s="12" t="n"/>
+      <c r="E139" s="11" t="n"/>
       <c r="F139" s="10" t="n"/>
       <c r="G139" s="10" t="n"/>
     </row>
@@ -2614,7 +3066,7 @@
       <c r="B140" s="10" t="n"/>
       <c r="C140" s="10" t="n"/>
       <c r="D140" s="10" t="n"/>
-      <c r="E140" s="12" t="n"/>
+      <c r="E140" s="11" t="n"/>
       <c r="F140" s="10" t="n"/>
       <c r="G140" s="10" t="n"/>
     </row>
@@ -2623,7 +3075,7 @@
       <c r="B141" s="10" t="n"/>
       <c r="C141" s="10" t="n"/>
       <c r="D141" s="10" t="n"/>
-      <c r="E141" s="12" t="n"/>
+      <c r="E141" s="11" t="n"/>
       <c r="F141" s="10" t="n"/>
       <c r="G141" s="10" t="n"/>
     </row>
@@ -2632,7 +3084,7 @@
       <c r="B142" s="10" t="n"/>
       <c r="C142" s="10" t="n"/>
       <c r="D142" s="10" t="n"/>
-      <c r="E142" s="12" t="n"/>
+      <c r="E142" s="11" t="n"/>
       <c r="F142" s="10" t="n"/>
       <c r="G142" s="10" t="n"/>
     </row>
@@ -2641,7 +3093,7 @@
       <c r="B143" s="10" t="n"/>
       <c r="C143" s="10" t="n"/>
       <c r="D143" s="10" t="n"/>
-      <c r="E143" s="12" t="n"/>
+      <c r="E143" s="11" t="n"/>
       <c r="F143" s="10" t="n"/>
       <c r="G143" s="10" t="n"/>
     </row>
@@ -2650,7 +3102,7 @@
       <c r="B144" s="10" t="n"/>
       <c r="C144" s="10" t="n"/>
       <c r="D144" s="10" t="n"/>
-      <c r="E144" s="12" t="n"/>
+      <c r="E144" s="11" t="n"/>
       <c r="F144" s="10" t="n"/>
       <c r="G144" s="10" t="n"/>
     </row>
@@ -2659,7 +3111,7 @@
       <c r="B145" s="10" t="n"/>
       <c r="C145" s="10" t="n"/>
       <c r="D145" s="10" t="n"/>
-      <c r="E145" s="12" t="n"/>
+      <c r="E145" s="11" t="n"/>
       <c r="F145" s="10" t="n"/>
       <c r="G145" s="10" t="n"/>
     </row>
@@ -2739,7 +3191,7 @@
           <t>Total estimated — counted quotes</t>
         </is>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <f>SUMIFS(E9:E58,G9:G58,"Y")</f>
         <v/>
       </c>
@@ -2750,7 +3202,7 @@
           <t>Total estimated — counted &amp; marked Now</t>
         </is>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <f>SUMIFS(E9:E58,G9:G58,"Y",F9:F58,"Now")</f>
         <v/>
       </c>
@@ -2817,9 +3269,9 @@
       </c>
       <c r="C9" s="10" t="n"/>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="12" t="n"/>
+      <c r="E9" s="11" t="n"/>
       <c r="F9" s="10" t="n"/>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2839,9 +3291,9 @@
       </c>
       <c r="C10" s="10" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="12" t="n"/>
+      <c r="E10" s="11" t="n"/>
       <c r="F10" s="10" t="n"/>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2853,9 +3305,9 @@
       <c r="B11" s="10" t="n"/>
       <c r="C11" s="10" t="n"/>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="12" t="n"/>
+      <c r="E11" s="11" t="n"/>
       <c r="F11" s="10" t="n"/>
-      <c r="G11" s="23" t="n"/>
+      <c r="G11" s="12" t="n"/>
       <c r="H11" s="10" t="n"/>
     </row>
     <row r="12">
@@ -2863,9 +3315,9 @@
       <c r="B12" s="10" t="n"/>
       <c r="C12" s="10" t="n"/>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="12" t="n"/>
+      <c r="E12" s="11" t="n"/>
       <c r="F12" s="10" t="n"/>
-      <c r="G12" s="23" t="n"/>
+      <c r="G12" s="12" t="n"/>
       <c r="H12" s="10" t="n"/>
     </row>
     <row r="13">
@@ -2873,9 +3325,9 @@
       <c r="B13" s="10" t="n"/>
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="12" t="n"/>
+      <c r="E13" s="11" t="n"/>
       <c r="F13" s="10" t="n"/>
-      <c r="G13" s="23" t="n"/>
+      <c r="G13" s="12" t="n"/>
       <c r="H13" s="10" t="n"/>
     </row>
     <row r="14">
@@ -2883,9 +3335,9 @@
       <c r="B14" s="10" t="n"/>
       <c r="C14" s="10" t="n"/>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="12" t="n"/>
+      <c r="E14" s="11" t="n"/>
       <c r="F14" s="10" t="n"/>
-      <c r="G14" s="23" t="n"/>
+      <c r="G14" s="12" t="n"/>
       <c r="H14" s="10" t="n"/>
     </row>
     <row r="15">
@@ -2893,9 +3345,9 @@
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="10" t="n"/>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="12" t="n"/>
+      <c r="E15" s="11" t="n"/>
       <c r="F15" s="10" t="n"/>
-      <c r="G15" s="23" t="n"/>
+      <c r="G15" s="12" t="n"/>
       <c r="H15" s="10" t="n"/>
     </row>
     <row r="16">
@@ -2903,9 +3355,9 @@
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="10" t="n"/>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="12" t="n"/>
+      <c r="E16" s="11" t="n"/>
       <c r="F16" s="10" t="n"/>
-      <c r="G16" s="23" t="n"/>
+      <c r="G16" s="12" t="n"/>
       <c r="H16" s="10" t="n"/>
     </row>
     <row r="17">
@@ -2913,9 +3365,9 @@
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="10" t="n"/>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="12" t="n"/>
+      <c r="E17" s="11" t="n"/>
       <c r="F17" s="10" t="n"/>
-      <c r="G17" s="23" t="n"/>
+      <c r="G17" s="12" t="n"/>
       <c r="H17" s="10" t="n"/>
     </row>
     <row r="18">
@@ -2923,9 +3375,9 @@
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="10" t="n"/>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="12" t="n"/>
+      <c r="E18" s="11" t="n"/>
       <c r="F18" s="10" t="n"/>
-      <c r="G18" s="23" t="n"/>
+      <c r="G18" s="12" t="n"/>
       <c r="H18" s="10" t="n"/>
     </row>
     <row r="19">
@@ -2933,9 +3385,9 @@
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="12" t="n"/>
+      <c r="E19" s="11" t="n"/>
       <c r="F19" s="10" t="n"/>
-      <c r="G19" s="23" t="n"/>
+      <c r="G19" s="12" t="n"/>
       <c r="H19" s="10" t="n"/>
     </row>
     <row r="20">
@@ -2943,9 +3395,9 @@
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="10" t="n"/>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="12" t="n"/>
+      <c r="E20" s="11" t="n"/>
       <c r="F20" s="10" t="n"/>
-      <c r="G20" s="23" t="n"/>
+      <c r="G20" s="12" t="n"/>
       <c r="H20" s="10" t="n"/>
     </row>
     <row r="21">
@@ -2953,9 +3405,9 @@
       <c r="B21" s="10" t="n"/>
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="12" t="n"/>
+      <c r="E21" s="11" t="n"/>
       <c r="F21" s="10" t="n"/>
-      <c r="G21" s="23" t="n"/>
+      <c r="G21" s="12" t="n"/>
       <c r="H21" s="10" t="n"/>
     </row>
     <row r="22">
@@ -2963,9 +3415,9 @@
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="12" t="n"/>
+      <c r="E22" s="11" t="n"/>
       <c r="F22" s="10" t="n"/>
-      <c r="G22" s="23" t="n"/>
+      <c r="G22" s="12" t="n"/>
       <c r="H22" s="10" t="n"/>
     </row>
     <row r="23">
@@ -2973,9 +3425,9 @@
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="10" t="n"/>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="12" t="n"/>
+      <c r="E23" s="11" t="n"/>
       <c r="F23" s="10" t="n"/>
-      <c r="G23" s="23" t="n"/>
+      <c r="G23" s="12" t="n"/>
       <c r="H23" s="10" t="n"/>
     </row>
     <row r="24">
@@ -2983,9 +3435,9 @@
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="12" t="n"/>
+      <c r="E24" s="11" t="n"/>
       <c r="F24" s="10" t="n"/>
-      <c r="G24" s="23" t="n"/>
+      <c r="G24" s="12" t="n"/>
       <c r="H24" s="10" t="n"/>
     </row>
     <row r="25">
@@ -2993,9 +3445,9 @@
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="12" t="n"/>
+      <c r="E25" s="11" t="n"/>
       <c r="F25" s="10" t="n"/>
-      <c r="G25" s="23" t="n"/>
+      <c r="G25" s="12" t="n"/>
       <c r="H25" s="10" t="n"/>
     </row>
     <row r="26">
@@ -3003,9 +3455,9 @@
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="10" t="n"/>
       <c r="D26" s="6" t="n"/>
-      <c r="E26" s="12" t="n"/>
+      <c r="E26" s="11" t="n"/>
       <c r="F26" s="10" t="n"/>
-      <c r="G26" s="23" t="n"/>
+      <c r="G26" s="12" t="n"/>
       <c r="H26" s="10" t="n"/>
     </row>
     <row r="27">
@@ -3013,9 +3465,9 @@
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="6" t="n"/>
-      <c r="E27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
       <c r="F27" s="10" t="n"/>
-      <c r="G27" s="23" t="n"/>
+      <c r="G27" s="12" t="n"/>
       <c r="H27" s="10" t="n"/>
     </row>
     <row r="28">
@@ -3023,9 +3475,9 @@
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="6" t="n"/>
-      <c r="E28" s="12" t="n"/>
+      <c r="E28" s="11" t="n"/>
       <c r="F28" s="10" t="n"/>
-      <c r="G28" s="23" t="n"/>
+      <c r="G28" s="12" t="n"/>
       <c r="H28" s="10" t="n"/>
     </row>
     <row r="29">
@@ -3033,9 +3485,9 @@
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="6" t="n"/>
-      <c r="E29" s="12" t="n"/>
+      <c r="E29" s="11" t="n"/>
       <c r="F29" s="10" t="n"/>
-      <c r="G29" s="23" t="n"/>
+      <c r="G29" s="12" t="n"/>
       <c r="H29" s="10" t="n"/>
     </row>
     <row r="30">
@@ -3043,9 +3495,9 @@
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="6" t="n"/>
-      <c r="E30" s="12" t="n"/>
+      <c r="E30" s="11" t="n"/>
       <c r="F30" s="10" t="n"/>
-      <c r="G30" s="23" t="n"/>
+      <c r="G30" s="12" t="n"/>
       <c r="H30" s="10" t="n"/>
     </row>
     <row r="31">
@@ -3053,9 +3505,9 @@
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="10" t="n"/>
       <c r="D31" s="6" t="n"/>
-      <c r="E31" s="12" t="n"/>
+      <c r="E31" s="11" t="n"/>
       <c r="F31" s="10" t="n"/>
-      <c r="G31" s="23" t="n"/>
+      <c r="G31" s="12" t="n"/>
       <c r="H31" s="10" t="n"/>
     </row>
     <row r="32">
@@ -3063,9 +3515,9 @@
       <c r="B32" s="10" t="n"/>
       <c r="C32" s="10" t="n"/>
       <c r="D32" s="6" t="n"/>
-      <c r="E32" s="12" t="n"/>
+      <c r="E32" s="11" t="n"/>
       <c r="F32" s="10" t="n"/>
-      <c r="G32" s="23" t="n"/>
+      <c r="G32" s="12" t="n"/>
       <c r="H32" s="10" t="n"/>
     </row>
     <row r="33">
@@ -3073,9 +3525,9 @@
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="6" t="n"/>
-      <c r="E33" s="12" t="n"/>
+      <c r="E33" s="11" t="n"/>
       <c r="F33" s="10" t="n"/>
-      <c r="G33" s="23" t="n"/>
+      <c r="G33" s="12" t="n"/>
       <c r="H33" s="10" t="n"/>
     </row>
     <row r="34">
@@ -3083,9 +3535,9 @@
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="10" t="n"/>
       <c r="D34" s="6" t="n"/>
-      <c r="E34" s="12" t="n"/>
+      <c r="E34" s="11" t="n"/>
       <c r="F34" s="10" t="n"/>
-      <c r="G34" s="23" t="n"/>
+      <c r="G34" s="12" t="n"/>
       <c r="H34" s="10" t="n"/>
     </row>
     <row r="35">
@@ -3093,9 +3545,9 @@
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="6" t="n"/>
-      <c r="E35" s="12" t="n"/>
+      <c r="E35" s="11" t="n"/>
       <c r="F35" s="10" t="n"/>
-      <c r="G35" s="23" t="n"/>
+      <c r="G35" s="12" t="n"/>
       <c r="H35" s="10" t="n"/>
     </row>
     <row r="36">
@@ -3103,9 +3555,9 @@
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="6" t="n"/>
-      <c r="E36" s="12" t="n"/>
+      <c r="E36" s="11" t="n"/>
       <c r="F36" s="10" t="n"/>
-      <c r="G36" s="23" t="n"/>
+      <c r="G36" s="12" t="n"/>
       <c r="H36" s="10" t="n"/>
     </row>
     <row r="37">
@@ -3113,9 +3565,9 @@
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="10" t="n"/>
       <c r="D37" s="6" t="n"/>
-      <c r="E37" s="12" t="n"/>
+      <c r="E37" s="11" t="n"/>
       <c r="F37" s="10" t="n"/>
-      <c r="G37" s="23" t="n"/>
+      <c r="G37" s="12" t="n"/>
       <c r="H37" s="10" t="n"/>
     </row>
     <row r="38">
@@ -3123,9 +3575,9 @@
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="10" t="n"/>
       <c r="D38" s="6" t="n"/>
-      <c r="E38" s="12" t="n"/>
+      <c r="E38" s="11" t="n"/>
       <c r="F38" s="10" t="n"/>
-      <c r="G38" s="23" t="n"/>
+      <c r="G38" s="12" t="n"/>
       <c r="H38" s="10" t="n"/>
     </row>
     <row r="39">
@@ -3133,9 +3585,9 @@
       <c r="B39" s="10" t="n"/>
       <c r="C39" s="10" t="n"/>
       <c r="D39" s="6" t="n"/>
-      <c r="E39" s="12" t="n"/>
+      <c r="E39" s="11" t="n"/>
       <c r="F39" s="10" t="n"/>
-      <c r="G39" s="23" t="n"/>
+      <c r="G39" s="12" t="n"/>
       <c r="H39" s="10" t="n"/>
     </row>
     <row r="40">
@@ -3143,9 +3595,9 @@
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="10" t="n"/>
       <c r="D40" s="6" t="n"/>
-      <c r="E40" s="12" t="n"/>
+      <c r="E40" s="11" t="n"/>
       <c r="F40" s="10" t="n"/>
-      <c r="G40" s="23" t="n"/>
+      <c r="G40" s="12" t="n"/>
       <c r="H40" s="10" t="n"/>
     </row>
     <row r="41">
@@ -3153,9 +3605,9 @@
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="10" t="n"/>
       <c r="D41" s="6" t="n"/>
-      <c r="E41" s="12" t="n"/>
+      <c r="E41" s="11" t="n"/>
       <c r="F41" s="10" t="n"/>
-      <c r="G41" s="23" t="n"/>
+      <c r="G41" s="12" t="n"/>
       <c r="H41" s="10" t="n"/>
     </row>
     <row r="42">
@@ -3163,9 +3615,9 @@
       <c r="B42" s="10" t="n"/>
       <c r="C42" s="10" t="n"/>
       <c r="D42" s="6" t="n"/>
-      <c r="E42" s="12" t="n"/>
+      <c r="E42" s="11" t="n"/>
       <c r="F42" s="10" t="n"/>
-      <c r="G42" s="23" t="n"/>
+      <c r="G42" s="12" t="n"/>
       <c r="H42" s="10" t="n"/>
     </row>
     <row r="43">
@@ -3173,9 +3625,9 @@
       <c r="B43" s="10" t="n"/>
       <c r="C43" s="10" t="n"/>
       <c r="D43" s="6" t="n"/>
-      <c r="E43" s="12" t="n"/>
+      <c r="E43" s="11" t="n"/>
       <c r="F43" s="10" t="n"/>
-      <c r="G43" s="23" t="n"/>
+      <c r="G43" s="12" t="n"/>
       <c r="H43" s="10" t="n"/>
     </row>
     <row r="44">
@@ -3183,9 +3635,9 @@
       <c r="B44" s="10" t="n"/>
       <c r="C44" s="10" t="n"/>
       <c r="D44" s="6" t="n"/>
-      <c r="E44" s="12" t="n"/>
+      <c r="E44" s="11" t="n"/>
       <c r="F44" s="10" t="n"/>
-      <c r="G44" s="23" t="n"/>
+      <c r="G44" s="12" t="n"/>
       <c r="H44" s="10" t="n"/>
     </row>
     <row r="45">
@@ -3193,9 +3645,9 @@
       <c r="B45" s="10" t="n"/>
       <c r="C45" s="10" t="n"/>
       <c r="D45" s="6" t="n"/>
-      <c r="E45" s="12" t="n"/>
+      <c r="E45" s="11" t="n"/>
       <c r="F45" s="10" t="n"/>
-      <c r="G45" s="23" t="n"/>
+      <c r="G45" s="12" t="n"/>
       <c r="H45" s="10" t="n"/>
     </row>
     <row r="46">
@@ -3203,9 +3655,9 @@
       <c r="B46" s="10" t="n"/>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="6" t="n"/>
-      <c r="E46" s="12" t="n"/>
+      <c r="E46" s="11" t="n"/>
       <c r="F46" s="10" t="n"/>
-      <c r="G46" s="23" t="n"/>
+      <c r="G46" s="12" t="n"/>
       <c r="H46" s="10" t="n"/>
     </row>
     <row r="47">
@@ -3213,9 +3665,9 @@
       <c r="B47" s="10" t="n"/>
       <c r="C47" s="10" t="n"/>
       <c r="D47" s="6" t="n"/>
-      <c r="E47" s="12" t="n"/>
+      <c r="E47" s="11" t="n"/>
       <c r="F47" s="10" t="n"/>
-      <c r="G47" s="23" t="n"/>
+      <c r="G47" s="12" t="n"/>
       <c r="H47" s="10" t="n"/>
     </row>
     <row r="48">
@@ -3223,9 +3675,9 @@
       <c r="B48" s="10" t="n"/>
       <c r="C48" s="10" t="n"/>
       <c r="D48" s="6" t="n"/>
-      <c r="E48" s="12" t="n"/>
+      <c r="E48" s="11" t="n"/>
       <c r="F48" s="10" t="n"/>
-      <c r="G48" s="23" t="n"/>
+      <c r="G48" s="12" t="n"/>
       <c r="H48" s="10" t="n"/>
     </row>
     <row r="49">
@@ -3233,9 +3685,9 @@
       <c r="B49" s="10" t="n"/>
       <c r="C49" s="10" t="n"/>
       <c r="D49" s="6" t="n"/>
-      <c r="E49" s="12" t="n"/>
+      <c r="E49" s="11" t="n"/>
       <c r="F49" s="10" t="n"/>
-      <c r="G49" s="23" t="n"/>
+      <c r="G49" s="12" t="n"/>
       <c r="H49" s="10" t="n"/>
     </row>
     <row r="50">
@@ -3243,9 +3695,9 @@
       <c r="B50" s="10" t="n"/>
       <c r="C50" s="10" t="n"/>
       <c r="D50" s="6" t="n"/>
-      <c r="E50" s="12" t="n"/>
+      <c r="E50" s="11" t="n"/>
       <c r="F50" s="10" t="n"/>
-      <c r="G50" s="23" t="n"/>
+      <c r="G50" s="12" t="n"/>
       <c r="H50" s="10" t="n"/>
     </row>
     <row r="51">
@@ -3253,9 +3705,9 @@
       <c r="B51" s="10" t="n"/>
       <c r="C51" s="10" t="n"/>
       <c r="D51" s="6" t="n"/>
-      <c r="E51" s="12" t="n"/>
+      <c r="E51" s="11" t="n"/>
       <c r="F51" s="10" t="n"/>
-      <c r="G51" s="23" t="n"/>
+      <c r="G51" s="12" t="n"/>
       <c r="H51" s="10" t="n"/>
     </row>
     <row r="52">
@@ -3263,9 +3715,9 @@
       <c r="B52" s="10" t="n"/>
       <c r="C52" s="10" t="n"/>
       <c r="D52" s="6" t="n"/>
-      <c r="E52" s="12" t="n"/>
+      <c r="E52" s="11" t="n"/>
       <c r="F52" s="10" t="n"/>
-      <c r="G52" s="23" t="n"/>
+      <c r="G52" s="12" t="n"/>
       <c r="H52" s="10" t="n"/>
     </row>
     <row r="53">
@@ -3273,9 +3725,9 @@
       <c r="B53" s="10" t="n"/>
       <c r="C53" s="10" t="n"/>
       <c r="D53" s="6" t="n"/>
-      <c r="E53" s="12" t="n"/>
+      <c r="E53" s="11" t="n"/>
       <c r="F53" s="10" t="n"/>
-      <c r="G53" s="23" t="n"/>
+      <c r="G53" s="12" t="n"/>
       <c r="H53" s="10" t="n"/>
     </row>
     <row r="54">
@@ -3283,9 +3735,9 @@
       <c r="B54" s="10" t="n"/>
       <c r="C54" s="10" t="n"/>
       <c r="D54" s="6" t="n"/>
-      <c r="E54" s="12" t="n"/>
+      <c r="E54" s="11" t="n"/>
       <c r="F54" s="10" t="n"/>
-      <c r="G54" s="23" t="n"/>
+      <c r="G54" s="12" t="n"/>
       <c r="H54" s="10" t="n"/>
     </row>
     <row r="55">
@@ -3293,9 +3745,9 @@
       <c r="B55" s="10" t="n"/>
       <c r="C55" s="10" t="n"/>
       <c r="D55" s="6" t="n"/>
-      <c r="E55" s="12" t="n"/>
+      <c r="E55" s="11" t="n"/>
       <c r="F55" s="10" t="n"/>
-      <c r="G55" s="23" t="n"/>
+      <c r="G55" s="12" t="n"/>
       <c r="H55" s="10" t="n"/>
     </row>
     <row r="56">
@@ -3303,9 +3755,9 @@
       <c r="B56" s="10" t="n"/>
       <c r="C56" s="10" t="n"/>
       <c r="D56" s="6" t="n"/>
-      <c r="E56" s="12" t="n"/>
+      <c r="E56" s="11" t="n"/>
       <c r="F56" s="10" t="n"/>
-      <c r="G56" s="23" t="n"/>
+      <c r="G56" s="12" t="n"/>
       <c r="H56" s="10" t="n"/>
     </row>
     <row r="57">
@@ -3313,9 +3765,9 @@
       <c r="B57" s="10" t="n"/>
       <c r="C57" s="10" t="n"/>
       <c r="D57" s="6" t="n"/>
-      <c r="E57" s="12" t="n"/>
+      <c r="E57" s="11" t="n"/>
       <c r="F57" s="10" t="n"/>
-      <c r="G57" s="23" t="n"/>
+      <c r="G57" s="12" t="n"/>
       <c r="H57" s="10" t="n"/>
     </row>
     <row r="58">
@@ -3323,9 +3775,9 @@
       <c r="B58" s="10" t="n"/>
       <c r="C58" s="10" t="n"/>
       <c r="D58" s="6" t="n"/>
-      <c r="E58" s="12" t="n"/>
+      <c r="E58" s="11" t="n"/>
       <c r="F58" s="10" t="n"/>
-      <c r="G58" s="23" t="n"/>
+      <c r="G58" s="12" t="n"/>
       <c r="H58" s="10" t="n"/>
     </row>
   </sheetData>
@@ -3388,7 +3840,7 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
@@ -3400,7 +3852,7 @@
           <t>Contractor / quote</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr"/>
+      <c r="B6" s="19" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -3408,7 +3860,7 @@
           <t>Materials source</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr"/>
+      <c r="B7" s="19" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -3416,7 +3868,7 @@
           <t>Selected option</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n"/>
+      <c r="B8" s="20" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -3424,7 +3876,7 @@
           <t>Contingency %</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="21" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3434,7 +3886,7 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr"/>
+      <c r="B10" s="22" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -3449,17 +3901,17 @@
           <t>Cost component</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>Option A</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Option B</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>Option C</t>
         </is>
@@ -3471,188 +3923,188 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Item # / SKU</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n"/>
-      <c r="C14" s="23" t="n"/>
-      <c r="D14" s="23" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
       <c r="E14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Unit price</t>
         </is>
       </c>
-      <c r="B15" s="25" t="n"/>
-      <c r="C15" s="25" t="n"/>
-      <c r="D15" s="25" t="n"/>
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
       <c r="E15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n"/>
-      <c r="C16" s="26" t="n"/>
-      <c r="D16" s="26" t="n"/>
+      <c r="B16" s="27" t="n"/>
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
       <c r="E16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Flooring material</t>
         </is>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="26">
         <f>B15*B16</f>
         <v/>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="26">
         <f>C15*C16</f>
         <v/>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="26">
         <f>D15*D16</f>
         <v/>
       </c>
       <c r="E17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Stair nose trim</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr"/>
-      <c r="C18" s="25" t="inlineStr"/>
-      <c r="D18" s="25" t="inlineStr"/>
+      <c r="B18" s="26" t="inlineStr"/>
+      <c r="C18" s="26" t="inlineStr"/>
+      <c r="D18" s="26" t="inlineStr"/>
       <c r="E18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>Stair risers</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr"/>
-      <c r="C19" s="25" t="inlineStr"/>
-      <c r="D19" s="25" t="inlineStr"/>
+      <c r="B19" s="26" t="inlineStr"/>
+      <c r="C19" s="26" t="inlineStr"/>
+      <c r="D19" s="26" t="inlineStr"/>
       <c r="E19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>Contractor discount on materials (0%)</t>
         </is>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="26">
         <f>-0.0*SUM(B17:B19)</f>
         <v/>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="26">
         <f>-0.0*SUM(C17:C19)</f>
         <v/>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="26">
         <f>-0.0*SUM(D17:D19)</f>
         <v/>
       </c>
       <c r="E20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Est. sales tax (6.25% MA, materials)</t>
         </is>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="26">
         <f>SUM(B17:B20)*0.0625</f>
         <v/>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="26">
         <f>SUM(C17:C20)*0.0625</f>
         <v/>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="26">
         <f>SUM(D17:D20)*0.0625</f>
         <v/>
       </c>
       <c r="E21" s="10" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>Labor — demo &amp; disposal</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr"/>
-      <c r="C22" s="25" t="inlineStr"/>
-      <c r="D22" s="25" t="inlineStr"/>
+      <c r="B22" s="26" t="inlineStr"/>
+      <c r="C22" s="26" t="inlineStr"/>
+      <c r="D22" s="26" t="inlineStr"/>
       <c r="E22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>Labor — install</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr"/>
-      <c r="C23" s="25" t="inlineStr"/>
-      <c r="D23" s="25" t="inlineStr"/>
+      <c r="B23" s="26" t="inlineStr"/>
+      <c r="C23" s="26" t="inlineStr"/>
+      <c r="D23" s="26" t="inlineStr"/>
       <c r="E23" s="10" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>Labor — stairs (treads &amp; risers)</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr"/>
-      <c r="C24" s="25" t="inlineStr"/>
-      <c r="D24" s="25" t="inlineStr"/>
+      <c r="B24" s="26" t="inlineStr"/>
+      <c r="C24" s="26" t="inlineStr"/>
+      <c r="D24" s="26" t="inlineStr"/>
       <c r="E24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>TOTAL ESTIMATED</t>
         </is>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="29">
         <f>SUM(B17:B24)</f>
         <v/>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="29">
         <f>SUM(C17:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="29">
         <f>SUM(D17:D24)</f>
         <v/>
       </c>
       <c r="E25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>Premium vs. cheapest option</t>
         </is>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="31">
         <f>B25-MIN($B$25:$D$25)</f>
         <v/>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="31">
         <f>C25-MIN($B$25:$D$25)</f>
         <v/>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="31">
         <f>D25-MIN($B$25:$D$25)</f>
         <v/>
       </c>
@@ -3693,15 +4145,15 @@
           <t>Flooring materials</t>
         </is>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="11">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,5,FALSE))</f>
         <v/>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="11">
         <f>SUMIF($D$46:$D$145,$A30,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="11">
         <f>IF(B30="","",B30-C30)</f>
         <v/>
       </c>
@@ -3712,15 +4164,15 @@
           <t>Stair nose trim</t>
         </is>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="11">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,6,FALSE))</f>
         <v/>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="11">
         <f>SUMIF($D$46:$D$145,$A31,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="11">
         <f>IF(B31="","",B31-C31)</f>
         <v/>
       </c>
@@ -3731,15 +4183,15 @@
           <t>Stair risers</t>
         </is>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="11">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,7,FALSE))</f>
         <v/>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="11">
         <f>SUMIF($D$46:$D$145,$A32,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="11">
         <f>IF(B32="","",B32-C32)</f>
         <v/>
       </c>
@@ -3750,15 +4202,15 @@
           <t>Contractor discount</t>
         </is>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="11">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,8,FALSE))</f>
         <v/>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="11">
         <f>SUMIF($D$46:$D$145,$A33,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="11">
         <f>IF(B33="","",B33-C33)</f>
         <v/>
       </c>
@@ -3769,15 +4221,15 @@
           <t>Sales tax</t>
         </is>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="11">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,9,FALSE))</f>
         <v/>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="11">
         <f>SUMIF($D$46:$D$145,$A34,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="11">
         <f>IF(B34="","",B34-C34)</f>
         <v/>
       </c>
@@ -3788,15 +4240,15 @@
           <t>Labor — demo &amp; disposal</t>
         </is>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="11">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,10,FALSE))</f>
         <v/>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="11">
         <f>SUMIF($D$46:$D$145,$A35,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="11">
         <f>IF(B35="","",B35-C35)</f>
         <v/>
       </c>
@@ -3807,15 +4259,15 @@
           <t>Labor — install</t>
         </is>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="11">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,11,FALSE))</f>
         <v/>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="11">
         <f>SUMIF($D$46:$D$145,$A36,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="11">
         <f>IF(B36="","",B36-C36)</f>
         <v/>
       </c>
@@ -3826,15 +4278,15 @@
           <t>Labor — stairs</t>
         </is>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="11">
         <f>IF($B$8="","",HLOOKUP($B$8,$B$13:$D$25,12,FALSE))</f>
         <v/>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="11">
         <f>SUMIF($D$46:$D$145,$A37,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="11">
         <f>IF(B37="","",B37-C37)</f>
         <v/>
       </c>
@@ -3845,12 +4297,12 @@
           <t>Permits &amp; fees</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12">
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11">
         <f>SUMIF($D$46:$D$145,$A38,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="11">
         <f>IF(B38="","",B38-C38)</f>
         <v/>
       </c>
@@ -3861,12 +4313,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12">
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11">
         <f>SUMIF($D$46:$D$145,$A39,$E$46:$E$145)</f>
         <v/>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="11">
         <f>IF(B39="","",B39-C39)</f>
         <v/>
       </c>
@@ -3877,31 +4329,31 @@
           <t>Contingency</t>
         </is>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="11">
         <f>SUM(B30:B39)*$B$9</f>
         <v/>
       </c>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="12">
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11">
         <f>B40-C40</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="27" t="inlineStr">
+      <c r="A41" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B41" s="31">
+      <c r="B41" s="32">
         <f>SUM(B30:B40)</f>
         <v/>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="32">
         <f>SUM(C30:C40)</f>
         <v/>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="32">
         <f>B41-C41</f>
         <v/>
       </c>
@@ -3955,7 +4407,7 @@
       <c r="B46" s="10" t="n"/>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="10" t="n"/>
-      <c r="E46" s="12" t="n"/>
+      <c r="E46" s="11" t="n"/>
       <c r="F46" s="10" t="n"/>
       <c r="G46" s="10" t="n"/>
     </row>
@@ -3964,7 +4416,7 @@
       <c r="B47" s="10" t="n"/>
       <c r="C47" s="10" t="n"/>
       <c r="D47" s="10" t="n"/>
-      <c r="E47" s="12" t="n"/>
+      <c r="E47" s="11" t="n"/>
       <c r="F47" s="10" t="n"/>
       <c r="G47" s="10" t="n"/>
     </row>
@@ -3973,7 +4425,7 @@
       <c r="B48" s="10" t="n"/>
       <c r="C48" s="10" t="n"/>
       <c r="D48" s="10" t="n"/>
-      <c r="E48" s="12" t="n"/>
+      <c r="E48" s="11" t="n"/>
       <c r="F48" s="10" t="n"/>
       <c r="G48" s="10" t="n"/>
     </row>
@@ -3982,7 +4434,7 @@
       <c r="B49" s="10" t="n"/>
       <c r="C49" s="10" t="n"/>
       <c r="D49" s="10" t="n"/>
-      <c r="E49" s="12" t="n"/>
+      <c r="E49" s="11" t="n"/>
       <c r="F49" s="10" t="n"/>
       <c r="G49" s="10" t="n"/>
     </row>
@@ -3991,7 +4443,7 @@
       <c r="B50" s="10" t="n"/>
       <c r="C50" s="10" t="n"/>
       <c r="D50" s="10" t="n"/>
-      <c r="E50" s="12" t="n"/>
+      <c r="E50" s="11" t="n"/>
       <c r="F50" s="10" t="n"/>
       <c r="G50" s="10" t="n"/>
     </row>
@@ -4000,7 +4452,7 @@
       <c r="B51" s="10" t="n"/>
       <c r="C51" s="10" t="n"/>
       <c r="D51" s="10" t="n"/>
-      <c r="E51" s="12" t="n"/>
+      <c r="E51" s="11" t="n"/>
       <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
     </row>
@@ -4009,7 +4461,7 @@
       <c r="B52" s="10" t="n"/>
       <c r="C52" s="10" t="n"/>
       <c r="D52" s="10" t="n"/>
-      <c r="E52" s="12" t="n"/>
+      <c r="E52" s="11" t="n"/>
       <c r="F52" s="10" t="n"/>
       <c r="G52" s="10" t="n"/>
     </row>
@@ -4018,7 +4470,7 @@
       <c r="B53" s="10" t="n"/>
       <c r="C53" s="10" t="n"/>
       <c r="D53" s="10" t="n"/>
-      <c r="E53" s="12" t="n"/>
+      <c r="E53" s="11" t="n"/>
       <c r="F53" s="10" t="n"/>
       <c r="G53" s="10" t="n"/>
     </row>
@@ -4027,7 +4479,7 @@
       <c r="B54" s="10" t="n"/>
       <c r="C54" s="10" t="n"/>
       <c r="D54" s="10" t="n"/>
-      <c r="E54" s="12" t="n"/>
+      <c r="E54" s="11" t="n"/>
       <c r="F54" s="10" t="n"/>
       <c r="G54" s="10" t="n"/>
     </row>
@@ -4036,7 +4488,7 @@
       <c r="B55" s="10" t="n"/>
       <c r="C55" s="10" t="n"/>
       <c r="D55" s="10" t="n"/>
-      <c r="E55" s="12" t="n"/>
+      <c r="E55" s="11" t="n"/>
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
     </row>
@@ -4045,7 +4497,7 @@
       <c r="B56" s="10" t="n"/>
       <c r="C56" s="10" t="n"/>
       <c r="D56" s="10" t="n"/>
-      <c r="E56" s="12" t="n"/>
+      <c r="E56" s="11" t="n"/>
       <c r="F56" s="10" t="n"/>
       <c r="G56" s="10" t="n"/>
     </row>
@@ -4054,7 +4506,7 @@
       <c r="B57" s="10" t="n"/>
       <c r="C57" s="10" t="n"/>
       <c r="D57" s="10" t="n"/>
-      <c r="E57" s="12" t="n"/>
+      <c r="E57" s="11" t="n"/>
       <c r="F57" s="10" t="n"/>
       <c r="G57" s="10" t="n"/>
     </row>
@@ -4063,7 +4515,7 @@
       <c r="B58" s="10" t="n"/>
       <c r="C58" s="10" t="n"/>
       <c r="D58" s="10" t="n"/>
-      <c r="E58" s="12" t="n"/>
+      <c r="E58" s="11" t="n"/>
       <c r="F58" s="10" t="n"/>
       <c r="G58" s="10" t="n"/>
     </row>
@@ -4072,7 +4524,7 @@
       <c r="B59" s="10" t="n"/>
       <c r="C59" s="10" t="n"/>
       <c r="D59" s="10" t="n"/>
-      <c r="E59" s="12" t="n"/>
+      <c r="E59" s="11" t="n"/>
       <c r="F59" s="10" t="n"/>
       <c r="G59" s="10" t="n"/>
     </row>
@@ -4081,7 +4533,7 @@
       <c r="B60" s="10" t="n"/>
       <c r="C60" s="10" t="n"/>
       <c r="D60" s="10" t="n"/>
-      <c r="E60" s="12" t="n"/>
+      <c r="E60" s="11" t="n"/>
       <c r="F60" s="10" t="n"/>
       <c r="G60" s="10" t="n"/>
     </row>
@@ -4090,7 +4542,7 @@
       <c r="B61" s="10" t="n"/>
       <c r="C61" s="10" t="n"/>
       <c r="D61" s="10" t="n"/>
-      <c r="E61" s="12" t="n"/>
+      <c r="E61" s="11" t="n"/>
       <c r="F61" s="10" t="n"/>
       <c r="G61" s="10" t="n"/>
     </row>
@@ -4099,7 +4551,7 @@
       <c r="B62" s="10" t="n"/>
       <c r="C62" s="10" t="n"/>
       <c r="D62" s="10" t="n"/>
-      <c r="E62" s="12" t="n"/>
+      <c r="E62" s="11" t="n"/>
       <c r="F62" s="10" t="n"/>
       <c r="G62" s="10" t="n"/>
     </row>
@@ -4108,7 +4560,7 @@
       <c r="B63" s="10" t="n"/>
       <c r="C63" s="10" t="n"/>
       <c r="D63" s="10" t="n"/>
-      <c r="E63" s="12" t="n"/>
+      <c r="E63" s="11" t="n"/>
       <c r="F63" s="10" t="n"/>
       <c r="G63" s="10" t="n"/>
     </row>
@@ -4117,7 +4569,7 @@
       <c r="B64" s="10" t="n"/>
       <c r="C64" s="10" t="n"/>
       <c r="D64" s="10" t="n"/>
-      <c r="E64" s="12" t="n"/>
+      <c r="E64" s="11" t="n"/>
       <c r="F64" s="10" t="n"/>
       <c r="G64" s="10" t="n"/>
     </row>
@@ -4126,7 +4578,7 @@
       <c r="B65" s="10" t="n"/>
       <c r="C65" s="10" t="n"/>
       <c r="D65" s="10" t="n"/>
-      <c r="E65" s="12" t="n"/>
+      <c r="E65" s="11" t="n"/>
       <c r="F65" s="10" t="n"/>
       <c r="G65" s="10" t="n"/>
     </row>
@@ -4135,7 +4587,7 @@
       <c r="B66" s="10" t="n"/>
       <c r="C66" s="10" t="n"/>
       <c r="D66" s="10" t="n"/>
-      <c r="E66" s="12" t="n"/>
+      <c r="E66" s="11" t="n"/>
       <c r="F66" s="10" t="n"/>
       <c r="G66" s="10" t="n"/>
     </row>
@@ -4144,7 +4596,7 @@
       <c r="B67" s="10" t="n"/>
       <c r="C67" s="10" t="n"/>
       <c r="D67" s="10" t="n"/>
-      <c r="E67" s="12" t="n"/>
+      <c r="E67" s="11" t="n"/>
       <c r="F67" s="10" t="n"/>
       <c r="G67" s="10" t="n"/>
     </row>
@@ -4153,7 +4605,7 @@
       <c r="B68" s="10" t="n"/>
       <c r="C68" s="10" t="n"/>
       <c r="D68" s="10" t="n"/>
-      <c r="E68" s="12" t="n"/>
+      <c r="E68" s="11" t="n"/>
       <c r="F68" s="10" t="n"/>
       <c r="G68" s="10" t="n"/>
     </row>
@@ -4162,7 +4614,7 @@
       <c r="B69" s="10" t="n"/>
       <c r="C69" s="10" t="n"/>
       <c r="D69" s="10" t="n"/>
-      <c r="E69" s="12" t="n"/>
+      <c r="E69" s="11" t="n"/>
       <c r="F69" s="10" t="n"/>
       <c r="G69" s="10" t="n"/>
     </row>
@@ -4171,7 +4623,7 @@
       <c r="B70" s="10" t="n"/>
       <c r="C70" s="10" t="n"/>
       <c r="D70" s="10" t="n"/>
-      <c r="E70" s="12" t="n"/>
+      <c r="E70" s="11" t="n"/>
       <c r="F70" s="10" t="n"/>
       <c r="G70" s="10" t="n"/>
     </row>
@@ -4180,7 +4632,7 @@
       <c r="B71" s="10" t="n"/>
       <c r="C71" s="10" t="n"/>
       <c r="D71" s="10" t="n"/>
-      <c r="E71" s="12" t="n"/>
+      <c r="E71" s="11" t="n"/>
       <c r="F71" s="10" t="n"/>
       <c r="G71" s="10" t="n"/>
     </row>
@@ -4189,7 +4641,7 @@
       <c r="B72" s="10" t="n"/>
       <c r="C72" s="10" t="n"/>
       <c r="D72" s="10" t="n"/>
-      <c r="E72" s="12" t="n"/>
+      <c r="E72" s="11" t="n"/>
       <c r="F72" s="10" t="n"/>
       <c r="G72" s="10" t="n"/>
     </row>
@@ -4198,7 +4650,7 @@
       <c r="B73" s="10" t="n"/>
       <c r="C73" s="10" t="n"/>
       <c r="D73" s="10" t="n"/>
-      <c r="E73" s="12" t="n"/>
+      <c r="E73" s="11" t="n"/>
       <c r="F73" s="10" t="n"/>
       <c r="G73" s="10" t="n"/>
     </row>
@@ -4207,7 +4659,7 @@
       <c r="B74" s="10" t="n"/>
       <c r="C74" s="10" t="n"/>
       <c r="D74" s="10" t="n"/>
-      <c r="E74" s="12" t="n"/>
+      <c r="E74" s="11" t="n"/>
       <c r="F74" s="10" t="n"/>
       <c r="G74" s="10" t="n"/>
     </row>
@@ -4216,7 +4668,7 @@
       <c r="B75" s="10" t="n"/>
       <c r="C75" s="10" t="n"/>
       <c r="D75" s="10" t="n"/>
-      <c r="E75" s="12" t="n"/>
+      <c r="E75" s="11" t="n"/>
       <c r="F75" s="10" t="n"/>
       <c r="G75" s="10" t="n"/>
     </row>
@@ -4225,7 +4677,7 @@
       <c r="B76" s="10" t="n"/>
       <c r="C76" s="10" t="n"/>
       <c r="D76" s="10" t="n"/>
-      <c r="E76" s="12" t="n"/>
+      <c r="E76" s="11" t="n"/>
       <c r="F76" s="10" t="n"/>
       <c r="G76" s="10" t="n"/>
     </row>
@@ -4234,7 +4686,7 @@
       <c r="B77" s="10" t="n"/>
       <c r="C77" s="10" t="n"/>
       <c r="D77" s="10" t="n"/>
-      <c r="E77" s="12" t="n"/>
+      <c r="E77" s="11" t="n"/>
       <c r="F77" s="10" t="n"/>
       <c r="G77" s="10" t="n"/>
     </row>
@@ -4243,7 +4695,7 @@
       <c r="B78" s="10" t="n"/>
       <c r="C78" s="10" t="n"/>
       <c r="D78" s="10" t="n"/>
-      <c r="E78" s="12" t="n"/>
+      <c r="E78" s="11" t="n"/>
       <c r="F78" s="10" t="n"/>
       <c r="G78" s="10" t="n"/>
     </row>
@@ -4252,7 +4704,7 @@
       <c r="B79" s="10" t="n"/>
       <c r="C79" s="10" t="n"/>
       <c r="D79" s="10" t="n"/>
-      <c r="E79" s="12" t="n"/>
+      <c r="E79" s="11" t="n"/>
       <c r="F79" s="10" t="n"/>
       <c r="G79" s="10" t="n"/>
     </row>
@@ -4261,7 +4713,7 @@
       <c r="B80" s="10" t="n"/>
       <c r="C80" s="10" t="n"/>
       <c r="D80" s="10" t="n"/>
-      <c r="E80" s="12" t="n"/>
+      <c r="E80" s="11" t="n"/>
       <c r="F80" s="10" t="n"/>
       <c r="G80" s="10" t="n"/>
     </row>
@@ -4270,7 +4722,7 @@
       <c r="B81" s="10" t="n"/>
       <c r="C81" s="10" t="n"/>
       <c r="D81" s="10" t="n"/>
-      <c r="E81" s="12" t="n"/>
+      <c r="E81" s="11" t="n"/>
       <c r="F81" s="10" t="n"/>
       <c r="G81" s="10" t="n"/>
     </row>
@@ -4279,7 +4731,7 @@
       <c r="B82" s="10" t="n"/>
       <c r="C82" s="10" t="n"/>
       <c r="D82" s="10" t="n"/>
-      <c r="E82" s="12" t="n"/>
+      <c r="E82" s="11" t="n"/>
       <c r="F82" s="10" t="n"/>
       <c r="G82" s="10" t="n"/>
     </row>
@@ -4288,7 +4740,7 @@
       <c r="B83" s="10" t="n"/>
       <c r="C83" s="10" t="n"/>
       <c r="D83" s="10" t="n"/>
-      <c r="E83" s="12" t="n"/>
+      <c r="E83" s="11" t="n"/>
       <c r="F83" s="10" t="n"/>
       <c r="G83" s="10" t="n"/>
     </row>
@@ -4297,7 +4749,7 @@
       <c r="B84" s="10" t="n"/>
       <c r="C84" s="10" t="n"/>
       <c r="D84" s="10" t="n"/>
-      <c r="E84" s="12" t="n"/>
+      <c r="E84" s="11" t="n"/>
       <c r="F84" s="10" t="n"/>
       <c r="G84" s="10" t="n"/>
     </row>
@@ -4306,7 +4758,7 @@
       <c r="B85" s="10" t="n"/>
       <c r="C85" s="10" t="n"/>
       <c r="D85" s="10" t="n"/>
-      <c r="E85" s="12" t="n"/>
+      <c r="E85" s="11" t="n"/>
       <c r="F85" s="10" t="n"/>
       <c r="G85" s="10" t="n"/>
     </row>
@@ -4315,7 +4767,7 @@
       <c r="B86" s="10" t="n"/>
       <c r="C86" s="10" t="n"/>
       <c r="D86" s="10" t="n"/>
-      <c r="E86" s="12" t="n"/>
+      <c r="E86" s="11" t="n"/>
       <c r="F86" s="10" t="n"/>
       <c r="G86" s="10" t="n"/>
     </row>
@@ -4324,7 +4776,7 @@
       <c r="B87" s="10" t="n"/>
       <c r="C87" s="10" t="n"/>
       <c r="D87" s="10" t="n"/>
-      <c r="E87" s="12" t="n"/>
+      <c r="E87" s="11" t="n"/>
       <c r="F87" s="10" t="n"/>
       <c r="G87" s="10" t="n"/>
     </row>
@@ -4333,7 +4785,7 @@
       <c r="B88" s="10" t="n"/>
       <c r="C88" s="10" t="n"/>
       <c r="D88" s="10" t="n"/>
-      <c r="E88" s="12" t="n"/>
+      <c r="E88" s="11" t="n"/>
       <c r="F88" s="10" t="n"/>
       <c r="G88" s="10" t="n"/>
     </row>
@@ -4342,7 +4794,7 @@
       <c r="B89" s="10" t="n"/>
       <c r="C89" s="10" t="n"/>
       <c r="D89" s="10" t="n"/>
-      <c r="E89" s="12" t="n"/>
+      <c r="E89" s="11" t="n"/>
       <c r="F89" s="10" t="n"/>
       <c r="G89" s="10" t="n"/>
     </row>
@@ -4351,7 +4803,7 @@
       <c r="B90" s="10" t="n"/>
       <c r="C90" s="10" t="n"/>
       <c r="D90" s="10" t="n"/>
-      <c r="E90" s="12" t="n"/>
+      <c r="E90" s="11" t="n"/>
       <c r="F90" s="10" t="n"/>
       <c r="G90" s="10" t="n"/>
     </row>
@@ -4360,7 +4812,7 @@
       <c r="B91" s="10" t="n"/>
       <c r="C91" s="10" t="n"/>
       <c r="D91" s="10" t="n"/>
-      <c r="E91" s="12" t="n"/>
+      <c r="E91" s="11" t="n"/>
       <c r="F91" s="10" t="n"/>
       <c r="G91" s="10" t="n"/>
     </row>
@@ -4369,7 +4821,7 @@
       <c r="B92" s="10" t="n"/>
       <c r="C92" s="10" t="n"/>
       <c r="D92" s="10" t="n"/>
-      <c r="E92" s="12" t="n"/>
+      <c r="E92" s="11" t="n"/>
       <c r="F92" s="10" t="n"/>
       <c r="G92" s="10" t="n"/>
     </row>
@@ -4378,7 +4830,7 @@
       <c r="B93" s="10" t="n"/>
       <c r="C93" s="10" t="n"/>
       <c r="D93" s="10" t="n"/>
-      <c r="E93" s="12" t="n"/>
+      <c r="E93" s="11" t="n"/>
       <c r="F93" s="10" t="n"/>
       <c r="G93" s="10" t="n"/>
     </row>
@@ -4387,7 +4839,7 @@
       <c r="B94" s="10" t="n"/>
       <c r="C94" s="10" t="n"/>
       <c r="D94" s="10" t="n"/>
-      <c r="E94" s="12" t="n"/>
+      <c r="E94" s="11" t="n"/>
       <c r="F94" s="10" t="n"/>
       <c r="G94" s="10" t="n"/>
     </row>
@@ -4396,7 +4848,7 @@
       <c r="B95" s="10" t="n"/>
       <c r="C95" s="10" t="n"/>
       <c r="D95" s="10" t="n"/>
-      <c r="E95" s="12" t="n"/>
+      <c r="E95" s="11" t="n"/>
       <c r="F95" s="10" t="n"/>
       <c r="G95" s="10" t="n"/>
     </row>
@@ -4405,7 +4857,7 @@
       <c r="B96" s="10" t="n"/>
       <c r="C96" s="10" t="n"/>
       <c r="D96" s="10" t="n"/>
-      <c r="E96" s="12" t="n"/>
+      <c r="E96" s="11" t="n"/>
       <c r="F96" s="10" t="n"/>
       <c r="G96" s="10" t="n"/>
     </row>
@@ -4414,7 +4866,7 @@
       <c r="B97" s="10" t="n"/>
       <c r="C97" s="10" t="n"/>
       <c r="D97" s="10" t="n"/>
-      <c r="E97" s="12" t="n"/>
+      <c r="E97" s="11" t="n"/>
       <c r="F97" s="10" t="n"/>
       <c r="G97" s="10" t="n"/>
     </row>
@@ -4423,7 +4875,7 @@
       <c r="B98" s="10" t="n"/>
       <c r="C98" s="10" t="n"/>
       <c r="D98" s="10" t="n"/>
-      <c r="E98" s="12" t="n"/>
+      <c r="E98" s="11" t="n"/>
       <c r="F98" s="10" t="n"/>
       <c r="G98" s="10" t="n"/>
     </row>
@@ -4432,7 +4884,7 @@
       <c r="B99" s="10" t="n"/>
       <c r="C99" s="10" t="n"/>
       <c r="D99" s="10" t="n"/>
-      <c r="E99" s="12" t="n"/>
+      <c r="E99" s="11" t="n"/>
       <c r="F99" s="10" t="n"/>
       <c r="G99" s="10" t="n"/>
     </row>
@@ -4441,7 +4893,7 @@
       <c r="B100" s="10" t="n"/>
       <c r="C100" s="10" t="n"/>
       <c r="D100" s="10" t="n"/>
-      <c r="E100" s="12" t="n"/>
+      <c r="E100" s="11" t="n"/>
       <c r="F100" s="10" t="n"/>
       <c r="G100" s="10" t="n"/>
     </row>
@@ -4450,7 +4902,7 @@
       <c r="B101" s="10" t="n"/>
       <c r="C101" s="10" t="n"/>
       <c r="D101" s="10" t="n"/>
-      <c r="E101" s="12" t="n"/>
+      <c r="E101" s="11" t="n"/>
       <c r="F101" s="10" t="n"/>
       <c r="G101" s="10" t="n"/>
     </row>
@@ -4459,7 +4911,7 @@
       <c r="B102" s="10" t="n"/>
       <c r="C102" s="10" t="n"/>
       <c r="D102" s="10" t="n"/>
-      <c r="E102" s="12" t="n"/>
+      <c r="E102" s="11" t="n"/>
       <c r="F102" s="10" t="n"/>
       <c r="G102" s="10" t="n"/>
     </row>
@@ -4468,7 +4920,7 @@
       <c r="B103" s="10" t="n"/>
       <c r="C103" s="10" t="n"/>
       <c r="D103" s="10" t="n"/>
-      <c r="E103" s="12" t="n"/>
+      <c r="E103" s="11" t="n"/>
       <c r="F103" s="10" t="n"/>
       <c r="G103" s="10" t="n"/>
     </row>
@@ -4477,7 +4929,7 @@
       <c r="B104" s="10" t="n"/>
       <c r="C104" s="10" t="n"/>
       <c r="D104" s="10" t="n"/>
-      <c r="E104" s="12" t="n"/>
+      <c r="E104" s="11" t="n"/>
       <c r="F104" s="10" t="n"/>
       <c r="G104" s="10" t="n"/>
     </row>
@@ -4486,7 +4938,7 @@
       <c r="B105" s="10" t="n"/>
       <c r="C105" s="10" t="n"/>
       <c r="D105" s="10" t="n"/>
-      <c r="E105" s="12" t="n"/>
+      <c r="E105" s="11" t="n"/>
       <c r="F105" s="10" t="n"/>
       <c r="G105" s="10" t="n"/>
     </row>
@@ -4495,7 +4947,7 @@
       <c r="B106" s="10" t="n"/>
       <c r="C106" s="10" t="n"/>
       <c r="D106" s="10" t="n"/>
-      <c r="E106" s="12" t="n"/>
+      <c r="E106" s="11" t="n"/>
       <c r="F106" s="10" t="n"/>
       <c r="G106" s="10" t="n"/>
     </row>
@@ -4504,7 +4956,7 @@
       <c r="B107" s="10" t="n"/>
       <c r="C107" s="10" t="n"/>
       <c r="D107" s="10" t="n"/>
-      <c r="E107" s="12" t="n"/>
+      <c r="E107" s="11" t="n"/>
       <c r="F107" s="10" t="n"/>
       <c r="G107" s="10" t="n"/>
     </row>
@@ -4513,7 +4965,7 @@
       <c r="B108" s="10" t="n"/>
       <c r="C108" s="10" t="n"/>
       <c r="D108" s="10" t="n"/>
-      <c r="E108" s="12" t="n"/>
+      <c r="E108" s="11" t="n"/>
       <c r="F108" s="10" t="n"/>
       <c r="G108" s="10" t="n"/>
     </row>
@@ -4522,7 +4974,7 @@
       <c r="B109" s="10" t="n"/>
       <c r="C109" s="10" t="n"/>
       <c r="D109" s="10" t="n"/>
-      <c r="E109" s="12" t="n"/>
+      <c r="E109" s="11" t="n"/>
       <c r="F109" s="10" t="n"/>
       <c r="G109" s="10" t="n"/>
     </row>
@@ -4531,7 +4983,7 @@
       <c r="B110" s="10" t="n"/>
       <c r="C110" s="10" t="n"/>
       <c r="D110" s="10" t="n"/>
-      <c r="E110" s="12" t="n"/>
+      <c r="E110" s="11" t="n"/>
       <c r="F110" s="10" t="n"/>
       <c r="G110" s="10" t="n"/>
     </row>
@@ -4540,7 +4992,7 @@
       <c r="B111" s="10" t="n"/>
       <c r="C111" s="10" t="n"/>
       <c r="D111" s="10" t="n"/>
-      <c r="E111" s="12" t="n"/>
+      <c r="E111" s="11" t="n"/>
       <c r="F111" s="10" t="n"/>
       <c r="G111" s="10" t="n"/>
     </row>
@@ -4549,7 +5001,7 @@
       <c r="B112" s="10" t="n"/>
       <c r="C112" s="10" t="n"/>
       <c r="D112" s="10" t="n"/>
-      <c r="E112" s="12" t="n"/>
+      <c r="E112" s="11" t="n"/>
       <c r="F112" s="10" t="n"/>
       <c r="G112" s="10" t="n"/>
     </row>
@@ -4558,7 +5010,7 @@
       <c r="B113" s="10" t="n"/>
       <c r="C113" s="10" t="n"/>
       <c r="D113" s="10" t="n"/>
-      <c r="E113" s="12" t="n"/>
+      <c r="E113" s="11" t="n"/>
       <c r="F113" s="10" t="n"/>
       <c r="G113" s="10" t="n"/>
     </row>
@@ -4567,7 +5019,7 @@
       <c r="B114" s="10" t="n"/>
       <c r="C114" s="10" t="n"/>
       <c r="D114" s="10" t="n"/>
-      <c r="E114" s="12" t="n"/>
+      <c r="E114" s="11" t="n"/>
       <c r="F114" s="10" t="n"/>
       <c r="G114" s="10" t="n"/>
     </row>
@@ -4576,7 +5028,7 @@
       <c r="B115" s="10" t="n"/>
       <c r="C115" s="10" t="n"/>
       <c r="D115" s="10" t="n"/>
-      <c r="E115" s="12" t="n"/>
+      <c r="E115" s="11" t="n"/>
       <c r="F115" s="10" t="n"/>
       <c r="G115" s="10" t="n"/>
     </row>
@@ -4585,7 +5037,7 @@
       <c r="B116" s="10" t="n"/>
       <c r="C116" s="10" t="n"/>
       <c r="D116" s="10" t="n"/>
-      <c r="E116" s="12" t="n"/>
+      <c r="E116" s="11" t="n"/>
       <c r="F116" s="10" t="n"/>
       <c r="G116" s="10" t="n"/>
     </row>
@@ -4594,7 +5046,7 @@
       <c r="B117" s="10" t="n"/>
       <c r="C117" s="10" t="n"/>
       <c r="D117" s="10" t="n"/>
-      <c r="E117" s="12" t="n"/>
+      <c r="E117" s="11" t="n"/>
       <c r="F117" s="10" t="n"/>
       <c r="G117" s="10" t="n"/>
     </row>
@@ -4603,7 +5055,7 @@
       <c r="B118" s="10" t="n"/>
       <c r="C118" s="10" t="n"/>
       <c r="D118" s="10" t="n"/>
-      <c r="E118" s="12" t="n"/>
+      <c r="E118" s="11" t="n"/>
       <c r="F118" s="10" t="n"/>
       <c r="G118" s="10" t="n"/>
     </row>
@@ -4612,7 +5064,7 @@
       <c r="B119" s="10" t="n"/>
       <c r="C119" s="10" t="n"/>
       <c r="D119" s="10" t="n"/>
-      <c r="E119" s="12" t="n"/>
+      <c r="E119" s="11" t="n"/>
       <c r="F119" s="10" t="n"/>
       <c r="G119" s="10" t="n"/>
     </row>
@@ -4621,7 +5073,7 @@
       <c r="B120" s="10" t="n"/>
       <c r="C120" s="10" t="n"/>
       <c r="D120" s="10" t="n"/>
-      <c r="E120" s="12" t="n"/>
+      <c r="E120" s="11" t="n"/>
       <c r="F120" s="10" t="n"/>
       <c r="G120" s="10" t="n"/>
     </row>
@@ -4630,7 +5082,7 @@
       <c r="B121" s="10" t="n"/>
       <c r="C121" s="10" t="n"/>
       <c r="D121" s="10" t="n"/>
-      <c r="E121" s="12" t="n"/>
+      <c r="E121" s="11" t="n"/>
       <c r="F121" s="10" t="n"/>
       <c r="G121" s="10" t="n"/>
     </row>
@@ -4639,7 +5091,7 @@
       <c r="B122" s="10" t="n"/>
       <c r="C122" s="10" t="n"/>
       <c r="D122" s="10" t="n"/>
-      <c r="E122" s="12" t="n"/>
+      <c r="E122" s="11" t="n"/>
       <c r="F122" s="10" t="n"/>
       <c r="G122" s="10" t="n"/>
     </row>
@@ -4648,7 +5100,7 @@
       <c r="B123" s="10" t="n"/>
       <c r="C123" s="10" t="n"/>
       <c r="D123" s="10" t="n"/>
-      <c r="E123" s="12" t="n"/>
+      <c r="E123" s="11" t="n"/>
       <c r="F123" s="10" t="n"/>
       <c r="G123" s="10" t="n"/>
     </row>
@@ -4657,7 +5109,7 @@
       <c r="B124" s="10" t="n"/>
       <c r="C124" s="10" t="n"/>
       <c r="D124" s="10" t="n"/>
-      <c r="E124" s="12" t="n"/>
+      <c r="E124" s="11" t="n"/>
       <c r="F124" s="10" t="n"/>
       <c r="G124" s="10" t="n"/>
     </row>
@@ -4666,7 +5118,7 @@
       <c r="B125" s="10" t="n"/>
       <c r="C125" s="10" t="n"/>
       <c r="D125" s="10" t="n"/>
-      <c r="E125" s="12" t="n"/>
+      <c r="E125" s="11" t="n"/>
       <c r="F125" s="10" t="n"/>
       <c r="G125" s="10" t="n"/>
     </row>
@@ -4675,7 +5127,7 @@
       <c r="B126" s="10" t="n"/>
       <c r="C126" s="10" t="n"/>
       <c r="D126" s="10" t="n"/>
-      <c r="E126" s="12" t="n"/>
+      <c r="E126" s="11" t="n"/>
       <c r="F126" s="10" t="n"/>
       <c r="G126" s="10" t="n"/>
     </row>
@@ -4684,7 +5136,7 @@
       <c r="B127" s="10" t="n"/>
       <c r="C127" s="10" t="n"/>
       <c r="D127" s="10" t="n"/>
-      <c r="E127" s="12" t="n"/>
+      <c r="E127" s="11" t="n"/>
       <c r="F127" s="10" t="n"/>
       <c r="G127" s="10" t="n"/>
     </row>
@@ -4693,7 +5145,7 @@
       <c r="B128" s="10" t="n"/>
       <c r="C128" s="10" t="n"/>
       <c r="D128" s="10" t="n"/>
-      <c r="E128" s="12" t="n"/>
+      <c r="E128" s="11" t="n"/>
       <c r="F128" s="10" t="n"/>
       <c r="G128" s="10" t="n"/>
     </row>
@@ -4702,7 +5154,7 @@
       <c r="B129" s="10" t="n"/>
       <c r="C129" s="10" t="n"/>
       <c r="D129" s="10" t="n"/>
-      <c r="E129" s="12" t="n"/>
+      <c r="E129" s="11" t="n"/>
       <c r="F129" s="10" t="n"/>
       <c r="G129" s="10" t="n"/>
     </row>
@@ -4711,7 +5163,7 @@
       <c r="B130" s="10" t="n"/>
       <c r="C130" s="10" t="n"/>
       <c r="D130" s="10" t="n"/>
-      <c r="E130" s="12" t="n"/>
+      <c r="E130" s="11" t="n"/>
       <c r="F130" s="10" t="n"/>
       <c r="G130" s="10" t="n"/>
     </row>
@@ -4720,7 +5172,7 @@
       <c r="B131" s="10" t="n"/>
       <c r="C131" s="10" t="n"/>
       <c r="D131" s="10" t="n"/>
-      <c r="E131" s="12" t="n"/>
+      <c r="E131" s="11" t="n"/>
       <c r="F131" s="10" t="n"/>
       <c r="G131" s="10" t="n"/>
     </row>
@@ -4729,7 +5181,7 @@
       <c r="B132" s="10" t="n"/>
       <c r="C132" s="10" t="n"/>
       <c r="D132" s="10" t="n"/>
-      <c r="E132" s="12" t="n"/>
+      <c r="E132" s="11" t="n"/>
       <c r="F132" s="10" t="n"/>
       <c r="G132" s="10" t="n"/>
     </row>
@@ -4738,7 +5190,7 @@
       <c r="B133" s="10" t="n"/>
       <c r="C133" s="10" t="n"/>
       <c r="D133" s="10" t="n"/>
-      <c r="E133" s="12" t="n"/>
+      <c r="E133" s="11" t="n"/>
       <c r="F133" s="10" t="n"/>
       <c r="G133" s="10" t="n"/>
     </row>
@@ -4747,7 +5199,7 @@
       <c r="B134" s="10" t="n"/>
       <c r="C134" s="10" t="n"/>
       <c r="D134" s="10" t="n"/>
-      <c r="E134" s="12" t="n"/>
+      <c r="E134" s="11" t="n"/>
       <c r="F134" s="10" t="n"/>
       <c r="G134" s="10" t="n"/>
     </row>
@@ -4756,7 +5208,7 @@
       <c r="B135" s="10" t="n"/>
       <c r="C135" s="10" t="n"/>
       <c r="D135" s="10" t="n"/>
-      <c r="E135" s="12" t="n"/>
+      <c r="E135" s="11" t="n"/>
       <c r="F135" s="10" t="n"/>
       <c r="G135" s="10" t="n"/>
     </row>
@@ -4765,7 +5217,7 @@
       <c r="B136" s="10" t="n"/>
       <c r="C136" s="10" t="n"/>
       <c r="D136" s="10" t="n"/>
-      <c r="E136" s="12" t="n"/>
+      <c r="E136" s="11" t="n"/>
       <c r="F136" s="10" t="n"/>
       <c r="G136" s="10" t="n"/>
     </row>
@@ -4774,7 +5226,7 @@
       <c r="B137" s="10" t="n"/>
       <c r="C137" s="10" t="n"/>
       <c r="D137" s="10" t="n"/>
-      <c r="E137" s="12" t="n"/>
+      <c r="E137" s="11" t="n"/>
       <c r="F137" s="10" t="n"/>
       <c r="G137" s="10" t="n"/>
     </row>
@@ -4783,7 +5235,7 @@
       <c r="B138" s="10" t="n"/>
       <c r="C138" s="10" t="n"/>
       <c r="D138" s="10" t="n"/>
-      <c r="E138" s="12" t="n"/>
+      <c r="E138" s="11" t="n"/>
       <c r="F138" s="10" t="n"/>
       <c r="G138" s="10" t="n"/>
     </row>
@@ -4792,7 +5244,7 @@
       <c r="B139" s="10" t="n"/>
       <c r="C139" s="10" t="n"/>
       <c r="D139" s="10" t="n"/>
-      <c r="E139" s="12" t="n"/>
+      <c r="E139" s="11" t="n"/>
       <c r="F139" s="10" t="n"/>
       <c r="G139" s="10" t="n"/>
     </row>
@@ -4801,7 +5253,7 @@
       <c r="B140" s="10" t="n"/>
       <c r="C140" s="10" t="n"/>
       <c r="D140" s="10" t="n"/>
-      <c r="E140" s="12" t="n"/>
+      <c r="E140" s="11" t="n"/>
       <c r="F140" s="10" t="n"/>
       <c r="G140" s="10" t="n"/>
     </row>
@@ -4810,7 +5262,7 @@
       <c r="B141" s="10" t="n"/>
       <c r="C141" s="10" t="n"/>
       <c r="D141" s="10" t="n"/>
-      <c r="E141" s="12" t="n"/>
+      <c r="E141" s="11" t="n"/>
       <c r="F141" s="10" t="n"/>
       <c r="G141" s="10" t="n"/>
     </row>
@@ -4819,7 +5271,7 @@
       <c r="B142" s="10" t="n"/>
       <c r="C142" s="10" t="n"/>
       <c r="D142" s="10" t="n"/>
-      <c r="E142" s="12" t="n"/>
+      <c r="E142" s="11" t="n"/>
       <c r="F142" s="10" t="n"/>
       <c r="G142" s="10" t="n"/>
     </row>
@@ -4828,7 +5280,7 @@
       <c r="B143" s="10" t="n"/>
       <c r="C143" s="10" t="n"/>
       <c r="D143" s="10" t="n"/>
-      <c r="E143" s="12" t="n"/>
+      <c r="E143" s="11" t="n"/>
       <c r="F143" s="10" t="n"/>
       <c r="G143" s="10" t="n"/>
     </row>
@@ -4837,7 +5289,7 @@
       <c r="B144" s="10" t="n"/>
       <c r="C144" s="10" t="n"/>
       <c r="D144" s="10" t="n"/>
-      <c r="E144" s="12" t="n"/>
+      <c r="E144" s="11" t="n"/>
       <c r="F144" s="10" t="n"/>
       <c r="G144" s="10" t="n"/>
     </row>
@@ -4846,7 +5298,7 @@
       <c r="B145" s="10" t="n"/>
       <c r="C145" s="10" t="n"/>
       <c r="D145" s="10" t="n"/>
-      <c r="E145" s="12" t="n"/>
+      <c r="E145" s="11" t="n"/>
       <c r="F145" s="10" t="n"/>
       <c r="G145" s="10" t="n"/>
     </row>
@@ -4994,7 +5446,7 @@
           <t>2nd floor flooring</t>
         </is>
       </c>
-      <c r="G6" s="23" t="n"/>
+      <c r="G6" s="12" t="n"/>
       <c r="H6" s="10" t="inlineStr">
         <is>
           <t>ACS Custom Solutions Inc.; proposal #25584</t>
@@ -5020,7 +5472,7 @@
           <t>2nd floor flooring materials</t>
         </is>
       </c>
-      <c r="G7" s="23" t="n"/>
+      <c r="G7" s="12" t="n"/>
       <c r="H7" s="10" t="n"/>
     </row>
     <row r="8">
@@ -5030,7 +5482,7 @@
       <c r="D8" s="10" t="n"/>
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="n"/>
-      <c r="G8" s="23" t="n"/>
+      <c r="G8" s="12" t="n"/>
       <c r="H8" s="10" t="n"/>
     </row>
     <row r="9">
@@ -5040,7 +5492,7 @@
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n"/>
-      <c r="G9" s="23" t="n"/>
+      <c r="G9" s="12" t="n"/>
       <c r="H9" s="10" t="n"/>
     </row>
     <row r="10">
@@ -5050,7 +5502,7 @@
       <c r="D10" s="10" t="n"/>
       <c r="E10" s="10" t="n"/>
       <c r="F10" s="10" t="n"/>
-      <c r="G10" s="23" t="n"/>
+      <c r="G10" s="12" t="n"/>
       <c r="H10" s="10" t="n"/>
     </row>
     <row r="11">
@@ -5060,7 +5512,7 @@
       <c r="D11" s="10" t="n"/>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
-      <c r="G11" s="23" t="n"/>
+      <c r="G11" s="12" t="n"/>
       <c r="H11" s="10" t="n"/>
     </row>
     <row r="12">
@@ -5070,7 +5522,7 @@
       <c r="D12" s="10" t="n"/>
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="n"/>
-      <c r="G12" s="23" t="n"/>
+      <c r="G12" s="12" t="n"/>
       <c r="H12" s="10" t="n"/>
     </row>
     <row r="13">
@@ -5080,7 +5532,7 @@
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="n"/>
-      <c r="G13" s="23" t="n"/>
+      <c r="G13" s="12" t="n"/>
       <c r="H13" s="10" t="n"/>
     </row>
     <row r="14">
@@ -5090,7 +5542,7 @@
       <c r="D14" s="10" t="n"/>
       <c r="E14" s="10" t="n"/>
       <c r="F14" s="10" t="n"/>
-      <c r="G14" s="23" t="n"/>
+      <c r="G14" s="12" t="n"/>
       <c r="H14" s="10" t="n"/>
     </row>
     <row r="15">
@@ -5100,7 +5552,7 @@
       <c r="D15" s="10" t="n"/>
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="10" t="n"/>
-      <c r="G15" s="23" t="n"/>
+      <c r="G15" s="12" t="n"/>
       <c r="H15" s="10" t="n"/>
     </row>
     <row r="16">
@@ -5110,7 +5562,7 @@
       <c r="D16" s="10" t="n"/>
       <c r="E16" s="10" t="n"/>
       <c r="F16" s="10" t="n"/>
-      <c r="G16" s="23" t="n"/>
+      <c r="G16" s="12" t="n"/>
       <c r="H16" s="10" t="n"/>
     </row>
     <row r="17">
@@ -5120,7 +5572,7 @@
       <c r="D17" s="10" t="n"/>
       <c r="E17" s="10" t="n"/>
       <c r="F17" s="10" t="n"/>
-      <c r="G17" s="23" t="n"/>
+      <c r="G17" s="12" t="n"/>
       <c r="H17" s="10" t="n"/>
     </row>
     <row r="18">
@@ -5130,7 +5582,7 @@
       <c r="D18" s="10" t="n"/>
       <c r="E18" s="10" t="n"/>
       <c r="F18" s="10" t="n"/>
-      <c r="G18" s="23" t="n"/>
+      <c r="G18" s="12" t="n"/>
       <c r="H18" s="10" t="n"/>
     </row>
     <row r="19">
@@ -5140,7 +5592,7 @@
       <c r="D19" s="10" t="n"/>
       <c r="E19" s="10" t="n"/>
       <c r="F19" s="10" t="n"/>
-      <c r="G19" s="23" t="n"/>
+      <c r="G19" s="12" t="n"/>
       <c r="H19" s="10" t="n"/>
     </row>
     <row r="20">
@@ -5150,7 +5602,7 @@
       <c r="D20" s="10" t="n"/>
       <c r="E20" s="10" t="n"/>
       <c r="F20" s="10" t="n"/>
-      <c r="G20" s="23" t="n"/>
+      <c r="G20" s="12" t="n"/>
       <c r="H20" s="10" t="n"/>
     </row>
     <row r="21">
@@ -5160,7 +5612,7 @@
       <c r="D21" s="10" t="n"/>
       <c r="E21" s="10" t="n"/>
       <c r="F21" s="10" t="n"/>
-      <c r="G21" s="23" t="n"/>
+      <c r="G21" s="12" t="n"/>
       <c r="H21" s="10" t="n"/>
     </row>
     <row r="22">
@@ -5170,7 +5622,7 @@
       <c r="D22" s="10" t="n"/>
       <c r="E22" s="10" t="n"/>
       <c r="F22" s="10" t="n"/>
-      <c r="G22" s="23" t="n"/>
+      <c r="G22" s="12" t="n"/>
       <c r="H22" s="10" t="n"/>
     </row>
     <row r="23">
@@ -5180,7 +5632,7 @@
       <c r="D23" s="10" t="n"/>
       <c r="E23" s="10" t="n"/>
       <c r="F23" s="10" t="n"/>
-      <c r="G23" s="23" t="n"/>
+      <c r="G23" s="12" t="n"/>
       <c r="H23" s="10" t="n"/>
     </row>
     <row r="24">
@@ -5190,7 +5642,7 @@
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
       <c r="F24" s="10" t="n"/>
-      <c r="G24" s="23" t="n"/>
+      <c r="G24" s="12" t="n"/>
       <c r="H24" s="10" t="n"/>
     </row>
     <row r="25">
@@ -5200,7 +5652,7 @@
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
       <c r="F25" s="10" t="n"/>
-      <c r="G25" s="23" t="n"/>
+      <c r="G25" s="12" t="n"/>
       <c r="H25" s="10" t="n"/>
     </row>
     <row r="26">
@@ -5210,7 +5662,7 @@
       <c r="D26" s="10" t="n"/>
       <c r="E26" s="10" t="n"/>
       <c r="F26" s="10" t="n"/>
-      <c r="G26" s="23" t="n"/>
+      <c r="G26" s="12" t="n"/>
       <c r="H26" s="10" t="n"/>
     </row>
     <row r="27">
@@ -5220,7 +5672,7 @@
       <c r="D27" s="10" t="n"/>
       <c r="E27" s="10" t="n"/>
       <c r="F27" s="10" t="n"/>
-      <c r="G27" s="23" t="n"/>
+      <c r="G27" s="12" t="n"/>
       <c r="H27" s="10" t="n"/>
     </row>
     <row r="28">
@@ -5230,7 +5682,7 @@
       <c r="D28" s="10" t="n"/>
       <c r="E28" s="10" t="n"/>
       <c r="F28" s="10" t="n"/>
-      <c r="G28" s="23" t="n"/>
+      <c r="G28" s="12" t="n"/>
       <c r="H28" s="10" t="n"/>
     </row>
     <row r="29">
@@ -5240,7 +5692,7 @@
       <c r="D29" s="10" t="n"/>
       <c r="E29" s="10" t="n"/>
       <c r="F29" s="10" t="n"/>
-      <c r="G29" s="23" t="n"/>
+      <c r="G29" s="12" t="n"/>
       <c r="H29" s="10" t="n"/>
     </row>
     <row r="30">
@@ -5250,7 +5702,7 @@
       <c r="D30" s="10" t="n"/>
       <c r="E30" s="10" t="n"/>
       <c r="F30" s="10" t="n"/>
-      <c r="G30" s="23" t="n"/>
+      <c r="G30" s="12" t="n"/>
       <c r="H30" s="10" t="n"/>
     </row>
     <row r="31">
@@ -5260,7 +5712,7 @@
       <c r="D31" s="10" t="n"/>
       <c r="E31" s="10" t="n"/>
       <c r="F31" s="10" t="n"/>
-      <c r="G31" s="23" t="n"/>
+      <c r="G31" s="12" t="n"/>
       <c r="H31" s="10" t="n"/>
     </row>
     <row r="32">
@@ -5270,7 +5722,7 @@
       <c r="D32" s="10" t="n"/>
       <c r="E32" s="10" t="n"/>
       <c r="F32" s="10" t="n"/>
-      <c r="G32" s="23" t="n"/>
+      <c r="G32" s="12" t="n"/>
       <c r="H32" s="10" t="n"/>
     </row>
     <row r="33">
@@ -5280,7 +5732,7 @@
       <c r="D33" s="10" t="n"/>
       <c r="E33" s="10" t="n"/>
       <c r="F33" s="10" t="n"/>
-      <c r="G33" s="23" t="n"/>
+      <c r="G33" s="12" t="n"/>
       <c r="H33" s="10" t="n"/>
     </row>
     <row r="34">
@@ -5290,7 +5742,7 @@
       <c r="D34" s="10" t="n"/>
       <c r="E34" s="10" t="n"/>
       <c r="F34" s="10" t="n"/>
-      <c r="G34" s="23" t="n"/>
+      <c r="G34" s="12" t="n"/>
       <c r="H34" s="10" t="n"/>
     </row>
     <row r="35">
@@ -5300,7 +5752,7 @@
       <c r="D35" s="10" t="n"/>
       <c r="E35" s="10" t="n"/>
       <c r="F35" s="10" t="n"/>
-      <c r="G35" s="23" t="n"/>
+      <c r="G35" s="12" t="n"/>
       <c r="H35" s="10" t="n"/>
     </row>
     <row r="36">
@@ -5310,7 +5762,7 @@
       <c r="D36" s="10" t="n"/>
       <c r="E36" s="10" t="n"/>
       <c r="F36" s="10" t="n"/>
-      <c r="G36" s="23" t="n"/>
+      <c r="G36" s="12" t="n"/>
       <c r="H36" s="10" t="n"/>
     </row>
     <row r="37">
@@ -5320,7 +5772,7 @@
       <c r="D37" s="10" t="n"/>
       <c r="E37" s="10" t="n"/>
       <c r="F37" s="10" t="n"/>
-      <c r="G37" s="23" t="n"/>
+      <c r="G37" s="12" t="n"/>
       <c r="H37" s="10" t="n"/>
     </row>
     <row r="38">
@@ -5330,7 +5782,7 @@
       <c r="D38" s="10" t="n"/>
       <c r="E38" s="10" t="n"/>
       <c r="F38" s="10" t="n"/>
-      <c r="G38" s="23" t="n"/>
+      <c r="G38" s="12" t="n"/>
       <c r="H38" s="10" t="n"/>
     </row>
     <row r="39">
@@ -5340,7 +5792,7 @@
       <c r="D39" s="10" t="n"/>
       <c r="E39" s="10" t="n"/>
       <c r="F39" s="10" t="n"/>
-      <c r="G39" s="23" t="n"/>
+      <c r="G39" s="12" t="n"/>
       <c r="H39" s="10" t="n"/>
     </row>
     <row r="40">
@@ -5350,7 +5802,7 @@
       <c r="D40" s="10" t="n"/>
       <c r="E40" s="10" t="n"/>
       <c r="F40" s="10" t="n"/>
-      <c r="G40" s="23" t="n"/>
+      <c r="G40" s="12" t="n"/>
       <c r="H40" s="10" t="n"/>
     </row>
     <row r="41">
@@ -5360,7 +5812,7 @@
       <c r="D41" s="10" t="n"/>
       <c r="E41" s="10" t="n"/>
       <c r="F41" s="10" t="n"/>
-      <c r="G41" s="23" t="n"/>
+      <c r="G41" s="12" t="n"/>
       <c r="H41" s="10" t="n"/>
     </row>
     <row r="42">
@@ -5370,7 +5822,7 @@
       <c r="D42" s="10" t="n"/>
       <c r="E42" s="10" t="n"/>
       <c r="F42" s="10" t="n"/>
-      <c r="G42" s="23" t="n"/>
+      <c r="G42" s="12" t="n"/>
       <c r="H42" s="10" t="n"/>
     </row>
     <row r="43">
@@ -5380,7 +5832,7 @@
       <c r="D43" s="10" t="n"/>
       <c r="E43" s="10" t="n"/>
       <c r="F43" s="10" t="n"/>
-      <c r="G43" s="23" t="n"/>
+      <c r="G43" s="12" t="n"/>
       <c r="H43" s="10" t="n"/>
     </row>
     <row r="44">
@@ -5390,7 +5842,7 @@
       <c r="D44" s="10" t="n"/>
       <c r="E44" s="10" t="n"/>
       <c r="F44" s="10" t="n"/>
-      <c r="G44" s="23" t="n"/>
+      <c r="G44" s="12" t="n"/>
       <c r="H44" s="10" t="n"/>
     </row>
     <row r="45">
@@ -5400,7 +5852,7 @@
       <c r="D45" s="10" t="n"/>
       <c r="E45" s="10" t="n"/>
       <c r="F45" s="10" t="n"/>
-      <c r="G45" s="23" t="n"/>
+      <c r="G45" s="12" t="n"/>
       <c r="H45" s="10" t="n"/>
     </row>
   </sheetData>
@@ -6139,14 +6591,14 @@
       <c r="D6" s="10" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="23" t="n">
+      <c r="G6" s="12" t="n">
         <v>20</v>
       </c>
       <c r="H6" s="6">
         <f>IF(OR(E6="",G6=""),"",EDATE(E6,12*G6))</f>
         <v/>
       </c>
-      <c r="I6" s="32" t="inlineStr">
+      <c r="I6" s="33" t="inlineStr">
         <is>
           <t>Annual tune-up; replace filters every 1-3 months (forced air)</t>
         </is>
@@ -6169,14 +6621,14 @@
       <c r="D7" s="10" t="n"/>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="23" t="n">
+      <c r="G7" s="12" t="n">
         <v>15</v>
       </c>
       <c r="H7" s="6">
         <f>IF(OR(E7="",G7=""),"",EDATE(E7,12*G7))</f>
         <v/>
       </c>
-      <c r="I7" s="32" t="inlineStr">
+      <c r="I7" s="33" t="inlineStr">
         <is>
           <t>Annual tune-up; keep outdoor unit clear</t>
         </is>
@@ -6199,14 +6651,14 @@
       <c r="D8" s="10" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
-      <c r="G8" s="23" t="n">
+      <c r="G8" s="12" t="n">
         <v>12</v>
       </c>
       <c r="H8" s="6">
         <f>IF(OR(E8="",G8=""),"",EDATE(E8,12*G8))</f>
         <v/>
       </c>
-      <c r="I8" s="32" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t>Flush tank annually; test T&amp;P valve</t>
         </is>
@@ -6229,14 +6681,14 @@
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="12" t="n">
         <v>13</v>
       </c>
       <c r="H9" s="6">
         <f>IF(OR(E9="",G9=""),"",EDATE(E9,12*G9))</f>
         <v/>
       </c>
-      <c r="I9" s="32" t="inlineStr">
+      <c r="I9" s="33" t="inlineStr">
         <is>
           <t>Vacuum coils annually</t>
         </is>
@@ -6259,14 +6711,14 @@
       <c r="D10" s="10" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="12" t="n">
         <v>15</v>
       </c>
       <c r="H10" s="6">
         <f>IF(OR(E10="",G10=""),"",EDATE(E10,12*G10))</f>
         <v/>
       </c>
-      <c r="I10" s="32" t="n"/>
+      <c r="I10" s="33" t="n"/>
       <c r="J10" s="6" t="n"/>
       <c r="K10" s="10" t="n"/>
     </row>
@@ -6285,14 +6737,14 @@
       <c r="D11" s="10" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
-      <c r="G11" s="23" t="n">
+      <c r="G11" s="12" t="n">
         <v>10</v>
       </c>
       <c r="H11" s="6">
         <f>IF(OR(E11="",G11=""),"",EDATE(E11,12*G11))</f>
         <v/>
       </c>
-      <c r="I11" s="32" t="inlineStr">
+      <c r="I11" s="33" t="inlineStr">
         <is>
           <t>Clean filter quarterly</t>
         </is>
@@ -6315,14 +6767,14 @@
       <c r="D12" s="10" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
-      <c r="G12" s="23" t="n">
+      <c r="G12" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H12" s="6">
         <f>IF(OR(E12="",G12=""),"",EDATE(E12,12*G12))</f>
         <v/>
       </c>
-      <c r="I12" s="32" t="n"/>
+      <c r="I12" s="33" t="n"/>
       <c r="J12" s="6" t="n"/>
       <c r="K12" s="10" t="n"/>
     </row>
@@ -6341,14 +6793,14 @@
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
-      <c r="G13" s="23" t="n">
+      <c r="G13" s="12" t="n">
         <v>11</v>
       </c>
       <c r="H13" s="6">
         <f>IF(OR(E13="",G13=""),"",EDATE(E13,12*G13))</f>
         <v/>
       </c>
-      <c r="I13" s="32" t="inlineStr">
+      <c r="I13" s="33" t="inlineStr">
         <is>
           <t>Inspect supply hoses annually</t>
         </is>
@@ -6371,14 +6823,14 @@
       <c r="D14" s="10" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="23" t="n">
+      <c r="G14" s="12" t="n">
         <v>13</v>
       </c>
       <c r="H14" s="6">
         <f>IF(OR(E14="",G14=""),"",EDATE(E14,12*G14))</f>
         <v/>
       </c>
-      <c r="I14" s="32" t="inlineStr">
+      <c r="I14" s="33" t="inlineStr">
         <is>
           <t>Clean vent duct annually; lint trap every load</t>
         </is>
@@ -6401,14 +6853,14 @@
       <c r="D15" s="10" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
-      <c r="G15" s="23" t="n">
+      <c r="G15" s="12" t="n">
         <v>10</v>
       </c>
       <c r="H15" s="6">
         <f>IF(OR(E15="",G15=""),"",EDATE(E15,12*G15))</f>
         <v/>
       </c>
-      <c r="I15" s="32" t="n"/>
+      <c r="I15" s="33" t="n"/>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="10" t="n"/>
     </row>
@@ -6427,14 +6879,14 @@
       <c r="D16" s="10" t="n"/>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
-      <c r="G16" s="23" t="n">
+      <c r="G16" s="12" t="n">
         <v>10</v>
       </c>
       <c r="H16" s="6">
         <f>IF(OR(E16="",G16=""),"",EDATE(E16,12*G16))</f>
         <v/>
       </c>
-      <c r="I16" s="32" t="inlineStr">
+      <c r="I16" s="33" t="inlineStr">
         <is>
           <t>Test quarterly; check before spring thaw</t>
         </is>
@@ -6457,14 +6909,14 @@
       <c r="D17" s="10" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
-      <c r="G17" s="23" t="n">
+      <c r="G17" s="12" t="n">
         <v>25</v>
       </c>
       <c r="H17" s="6">
         <f>IF(OR(E17="",G17=""),"",EDATE(E17,12*G17))</f>
         <v/>
       </c>
-      <c r="I17" s="32" t="inlineStr">
+      <c r="I17" s="33" t="inlineStr">
         <is>
           <t>Inspect annually and after major storms</t>
         </is>
@@ -6487,14 +6939,14 @@
       <c r="D18" s="10" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="23" t="n">
+      <c r="G18" s="12" t="n">
         <v>20</v>
       </c>
       <c r="H18" s="6">
         <f>IF(OR(E18="",G18=""),"",EDATE(E18,12*G18))</f>
         <v/>
       </c>
-      <c r="I18" s="32" t="inlineStr">
+      <c r="I18" s="33" t="inlineStr">
         <is>
           <t>Clean spring and fall</t>
         </is>
@@ -6517,14 +6969,14 @@
       <c r="D19" s="10" t="n"/>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
-      <c r="G19" s="23" t="n">
+      <c r="G19" s="12" t="n">
         <v>25</v>
       </c>
       <c r="H19" s="6">
         <f>IF(OR(E19="",G19=""),"",EDATE(E19,12*G19))</f>
         <v/>
       </c>
-      <c r="I19" s="32" t="inlineStr">
+      <c r="I19" s="33" t="inlineStr">
         <is>
           <t>Check seals/caulk annually</t>
         </is>
@@ -6547,14 +6999,14 @@
       <c r="D20" s="10" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
-      <c r="G20" s="23" t="n">
+      <c r="G20" s="12" t="n">
         <v>20</v>
       </c>
       <c r="H20" s="6">
         <f>IF(OR(E20="",G20=""),"",EDATE(E20,12*G20))</f>
         <v/>
       </c>
-      <c r="I20" s="32" t="inlineStr">
+      <c r="I20" s="33" t="inlineStr">
         <is>
           <t>Reseal or restain every 2-3 years</t>
         </is>
@@ -6577,14 +7029,14 @@
       <c r="D21" s="10" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
-      <c r="G21" s="23" t="n">
+      <c r="G21" s="12" t="n">
         <v>12</v>
       </c>
       <c r="H21" s="6">
         <f>IF(OR(E21="",G21=""),"",EDATE(E21,12*G21))</f>
         <v/>
       </c>
-      <c r="I21" s="32" t="inlineStr">
+      <c r="I21" s="33" t="inlineStr">
         <is>
           <t>Lubricate tracks/rollers annually</t>
         </is>
@@ -6607,14 +7059,14 @@
       <c r="D22" s="10" t="n"/>
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
-      <c r="G22" s="23" t="n">
+      <c r="G22" s="12" t="n">
         <v>10</v>
       </c>
       <c r="H22" s="6">
         <f>IF(OR(E22="",G22=""),"",EDATE(E22,12*G22))</f>
         <v/>
       </c>
-      <c r="I22" s="32" t="inlineStr">
+      <c r="I22" s="33" t="inlineStr">
         <is>
           <t>Test monthly; replace batteries annually</t>
         </is>
@@ -6637,14 +7089,14 @@
       <c r="D23" s="10" t="n"/>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
-      <c r="G23" s="23" t="n">
+      <c r="G23" s="12" t="n">
         <v>30</v>
       </c>
       <c r="H23" s="6">
         <f>IF(OR(E23="",G23=""),"",EDATE(E23,12*G23))</f>
         <v/>
       </c>
-      <c r="I23" s="32" t="inlineStr">
+      <c r="I23" s="33" t="inlineStr">
         <is>
           <t>Pump every 2-3 years; Title 5 inspection at sale</t>
         </is>
@@ -6667,14 +7119,14 @@
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
-      <c r="G24" s="23" t="n">
+      <c r="G24" s="12" t="n">
         <v>20</v>
       </c>
       <c r="H24" s="6">
         <f>IF(OR(E24="",G24=""),"",EDATE(E24,12*G24))</f>
         <v/>
       </c>
-      <c r="I24" s="32" t="inlineStr">
+      <c r="I24" s="33" t="inlineStr">
         <is>
           <t>Winterize every fall; startup check in spring</t>
         </is>
@@ -6689,12 +7141,12 @@
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
-      <c r="G25" s="23" t="n"/>
+      <c r="G25" s="12" t="n"/>
       <c r="H25" s="6">
         <f>IF(OR(E25="",G25=""),"",EDATE(E25,12*G25))</f>
         <v/>
       </c>
-      <c r="I25" s="32" t="n"/>
+      <c r="I25" s="33" t="n"/>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="10" t="n"/>
     </row>
@@ -6705,12 +7157,12 @@
       <c r="D26" s="10" t="n"/>
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
-      <c r="G26" s="23" t="n"/>
+      <c r="G26" s="12" t="n"/>
       <c r="H26" s="6">
         <f>IF(OR(E26="",G26=""),"",EDATE(E26,12*G26))</f>
         <v/>
       </c>
-      <c r="I26" s="32" t="n"/>
+      <c r="I26" s="33" t="n"/>
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="10" t="n"/>
     </row>
@@ -6721,12 +7173,12 @@
       <c r="D27" s="10" t="n"/>
       <c r="E27" s="6" t="n"/>
       <c r="F27" s="6" t="n"/>
-      <c r="G27" s="23" t="n"/>
+      <c r="G27" s="12" t="n"/>
       <c r="H27" s="6">
         <f>IF(OR(E27="",G27=""),"",EDATE(E27,12*G27))</f>
         <v/>
       </c>
-      <c r="I27" s="32" t="n"/>
+      <c r="I27" s="33" t="n"/>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="10" t="n"/>
     </row>
@@ -6737,12 +7189,12 @@
       <c r="D28" s="10" t="n"/>
       <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="n"/>
-      <c r="G28" s="23" t="n"/>
+      <c r="G28" s="12" t="n"/>
       <c r="H28" s="6">
         <f>IF(OR(E28="",G28=""),"",EDATE(E28,12*G28))</f>
         <v/>
       </c>
-      <c r="I28" s="32" t="n"/>
+      <c r="I28" s="33" t="n"/>
       <c r="J28" s="6" t="n"/>
       <c r="K28" s="10" t="n"/>
     </row>
@@ -6753,12 +7205,12 @@
       <c r="D29" s="10" t="n"/>
       <c r="E29" s="6" t="n"/>
       <c r="F29" s="6" t="n"/>
-      <c r="G29" s="23" t="n"/>
+      <c r="G29" s="12" t="n"/>
       <c r="H29" s="6">
         <f>IF(OR(E29="",G29=""),"",EDATE(E29,12*G29))</f>
         <v/>
       </c>
-      <c r="I29" s="32" t="n"/>
+      <c r="I29" s="33" t="n"/>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="10" t="n"/>
     </row>
@@ -6769,12 +7221,12 @@
       <c r="D30" s="10" t="n"/>
       <c r="E30" s="6" t="n"/>
       <c r="F30" s="6" t="n"/>
-      <c r="G30" s="23" t="n"/>
+      <c r="G30" s="12" t="n"/>
       <c r="H30" s="6">
         <f>IF(OR(E30="",G30=""),"",EDATE(E30,12*G30))</f>
         <v/>
       </c>
-      <c r="I30" s="32" t="n"/>
+      <c r="I30" s="33" t="n"/>
       <c r="J30" s="6" t="n"/>
       <c r="K30" s="10" t="n"/>
     </row>
@@ -6785,12 +7237,12 @@
       <c r="D31" s="10" t="n"/>
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="6" t="n"/>
-      <c r="G31" s="23" t="n"/>
+      <c r="G31" s="12" t="n"/>
       <c r="H31" s="6">
         <f>IF(OR(E31="",G31=""),"",EDATE(E31,12*G31))</f>
         <v/>
       </c>
-      <c r="I31" s="32" t="n"/>
+      <c r="I31" s="33" t="n"/>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="10" t="n"/>
     </row>
@@ -6801,12 +7253,12 @@
       <c r="D32" s="10" t="n"/>
       <c r="E32" s="6" t="n"/>
       <c r="F32" s="6" t="n"/>
-      <c r="G32" s="23" t="n"/>
+      <c r="G32" s="12" t="n"/>
       <c r="H32" s="6">
         <f>IF(OR(E32="",G32=""),"",EDATE(E32,12*G32))</f>
         <v/>
       </c>
-      <c r="I32" s="32" t="n"/>
+      <c r="I32" s="33" t="n"/>
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="10" t="n"/>
     </row>
@@ -6817,12 +7269,12 @@
       <c r="D33" s="10" t="n"/>
       <c r="E33" s="6" t="n"/>
       <c r="F33" s="6" t="n"/>
-      <c r="G33" s="23" t="n"/>
+      <c r="G33" s="12" t="n"/>
       <c r="H33" s="6">
         <f>IF(OR(E33="",G33=""),"",EDATE(E33,12*G33))</f>
         <v/>
       </c>
-      <c r="I33" s="32" t="n"/>
+      <c r="I33" s="33" t="n"/>
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="10" t="n"/>
     </row>
@@ -6833,12 +7285,12 @@
       <c r="D34" s="10" t="n"/>
       <c r="E34" s="6" t="n"/>
       <c r="F34" s="6" t="n"/>
-      <c r="G34" s="23" t="n"/>
+      <c r="G34" s="12" t="n"/>
       <c r="H34" s="6">
         <f>IF(OR(E34="",G34=""),"",EDATE(E34,12*G34))</f>
         <v/>
       </c>
-      <c r="I34" s="32" t="n"/>
+      <c r="I34" s="33" t="n"/>
       <c r="J34" s="6" t="n"/>
       <c r="K34" s="10" t="n"/>
     </row>
@@ -6849,12 +7301,12 @@
       <c r="D35" s="10" t="n"/>
       <c r="E35" s="6" t="n"/>
       <c r="F35" s="6" t="n"/>
-      <c r="G35" s="23" t="n"/>
+      <c r="G35" s="12" t="n"/>
       <c r="H35" s="6">
         <f>IF(OR(E35="",G35=""),"",EDATE(E35,12*G35))</f>
         <v/>
       </c>
-      <c r="I35" s="32" t="n"/>
+      <c r="I35" s="33" t="n"/>
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="10" t="n"/>
     </row>
@@ -6897,120 +7349,120 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>What this is</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>One workbook that tracks what the house cost and every project that adds to it. Share it in Google Drive so both of you can edit.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="33" t="inlineStr">
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Basis Tracker</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
-        <is>
-          <t>Purchase price ($1,060,000, closing 7/17/2026) + closing costs + capital improvements = adjusted cost basis. Each project tab feeds one row of the improvements table.</t>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Purchase price ($1,060,000, closing 7/17/2026) + basis-adding closing costs + capital improvements = adjusted cost basis. Closing costs are itemized from the Closing Disclosure with an Adds-to-basis flag; each project tab feeds one row of the improvements table.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>2nd Floor Flooring</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>First project. Compare the 3 Floor &amp; Decor plank options (incl. stair nose &amp; risers, 5% contractor discount, est. tax, and Footprints labor), pick one in 'Selected option' (yellow cell), and the budget fills in automatically. Log payments in the cost log at the bottom — actuals and the Basis Tracker update themselves.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="75" customHeight="1">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Project Estimates</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Preliminary phase: log each quote you collect (HVAC, carpentry, etc.) with its estimated cost, and mark Timing (Now / Later / Undecided / Passed) to decide what to take on. Set Count? to Y on the one quote per project you'd actually use — competing quotes marked N stay listed but don't double-count in the totals. When a project is a go, give it its own tab from the template.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Vendors &amp; Contacts</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Directory of contractors, suppliers, and service companies used on the house.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Finishes &amp; Materials</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Room-by-room record of paint colors, flooring, fixtures, and their SKUs — for touch-ups and matching repairs later.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Appliances &amp; Systems</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>Inventory of the house's equipment with make/model/serial, warranty dates, and service cadence. Enter an install date and the suggested replacement date computes from the typical lifespan.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Project Template</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>For the next project: right-click the tab &gt; Duplicate, rename it, fill in your options/quotes, then add a row in the Basis Tracker improvements table pointing at the new tab's cell C41 (its Actual total).</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Labor: Footprints Floors of Central MA proposal #25584 (6/30/2026) — $9,057.60, materials excluded. Materials: Floor &amp; Decor Waltham cart (7/2026) — Sapelo Shore / Big Sur / Gunstock Oak (underlayment attached to plank), plus 7 stair noses @ $29.99 and 13 risers @ $20; 5% contractor discount on materials.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>In Google Sheets everything here — dropdowns, cross-tab formulas, formatting — survives File &gt; Import. Use 'Replace spreadsheet' when importing so tab references stay intact.</t>
         </is>
